--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbs80020\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C091B7-6C5C-4987-BA6E-C95912DF72FB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="102">
   <si>
     <t>Table Name</t>
   </si>
@@ -65,12 +65,6 @@
     <t/>
   </si>
   <si>
-    <t>DataUpload</t>
-  </si>
-  <si>
-    <t>Data Upload</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -201,21 +195,6 @@
   </si>
   <si>
     <t>Boolean</t>
-  </si>
-  <si>
-    <t>FilePath</t>
-  </si>
-  <si>
-    <t>Uploaded File</t>
-  </si>
-  <si>
-    <t>FileUpload</t>
-  </si>
-  <si>
-    <t>FileType</t>
-  </si>
-  <si>
-    <t>CSV, XLSX, or JSON</t>
   </si>
   <si>
     <t>ProjectName</t>
@@ -751,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -816,23 +795,23 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
@@ -850,13 +829,13 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
@@ -864,13 +843,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
@@ -880,34 +859,34 @@
         <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -915,7 +894,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
@@ -928,10 +907,10 @@
         <v>11</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -939,46 +918,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -989,7 +944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1014,46 +969,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>7</v>
@@ -1064,13 +1019,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E2" s="2">
         <v>150</v>
@@ -1091,14 +1046,14 @@
         <v>12</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O2" s="2">
         <v>12</v>
@@ -1112,22 +1067,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2">
         <v>200</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
@@ -1136,17 +1091,17 @@
         <v>12</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O3" s="2">
         <v>12</v>
@@ -1160,22 +1115,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2">
         <v>150</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -1184,17 +1139,17 @@
         <v>12</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O4" s="2">
         <v>12</v>
@@ -1208,22 +1163,22 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2">
         <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>12</v>
@@ -1232,17 +1187,17 @@
         <v>12</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O5" s="2">
         <v>12</v>
@@ -1256,22 +1211,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>12</v>
@@ -1280,17 +1235,17 @@
         <v>12</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O6" s="2">
         <v>12</v>
@@ -1304,41 +1259,41 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2">
         <v>450</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O7" s="2">
         <v>12</v>
@@ -1352,41 +1307,41 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2">
         <v>450</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O8" s="2">
         <v>12</v>
@@ -1406,16 +1361,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2">
         <v>450</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>12</v>
@@ -1424,17 +1379,17 @@
         <v>12</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O9" s="2">
         <v>12</v>
@@ -1448,22 +1403,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>12</v>
@@ -1472,17 +1427,17 @@
         <v>12</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O10" s="2">
         <v>12</v>
@@ -1493,25 +1448,25 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>12</v>
@@ -1523,14 +1478,14 @@
         <v>12</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O11" s="2">
         <v>12</v>
@@ -1541,19 +1496,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>12</v>
@@ -1568,17 +1523,17 @@
         <v>12</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O12" s="2">
         <v>12</v>
@@ -1589,19 +1544,19 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>12</v>
@@ -1616,20 +1571,22 @@
         <v>12</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O13" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>13</v>
@@ -1640,16 +1597,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="2">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -1664,20 +1621,20 @@
         <v>12</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O14" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>13</v>
@@ -1685,7 +1642,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>65</v>
@@ -1694,16 +1651,16 @@
         <v>66</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E15" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>12</v>
@@ -1712,20 +1669,20 @@
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O15" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>13</v>
@@ -1733,16 +1690,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -1751,7 +1708,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>12</v>
@@ -1760,19 +1717,17 @@
         <v>12</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O16" s="2">
         <v>6</v>
@@ -1783,7 +1738,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>70</v>
@@ -1792,16 +1747,16 @@
         <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>12</v>
@@ -1810,20 +1765,20 @@
         <v>12</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O17" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>13</v>
@@ -1831,47 +1786,47 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O18" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>13</v>
@@ -1879,7 +1834,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>75</v>
@@ -1888,7 +1843,7 @@
         <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1897,7 +1852,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>12</v>
@@ -1906,20 +1861,22 @@
         <v>12</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N19" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O19" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>13</v>
@@ -1927,7 +1884,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>77</v>
@@ -1936,16 +1893,16 @@
         <v>78</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>12</v>
@@ -1954,20 +1911,20 @@
         <v>12</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O20" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>13</v>
@@ -1975,47 +1932,47 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O21" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>13</v>
@@ -2023,25 +1980,25 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>12</v>
@@ -2050,22 +2007,20 @@
         <v>12</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O22" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>13</v>
@@ -2073,25 +2028,25 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>12</v>
@@ -2100,17 +2055,17 @@
         <v>12</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2">
         <v>6</v>
@@ -2121,25 +2076,25 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>12</v>
@@ -2148,17 +2103,17 @@
         <v>12</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O24" s="2">
         <v>6</v>
@@ -2169,47 +2124,49 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="N25" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O25" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>13</v>
@@ -2217,25 +2174,25 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
@@ -2244,17 +2201,17 @@
         <v>12</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O26" s="2">
         <v>6</v>
@@ -2265,25 +2222,25 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>12</v>
@@ -2292,17 +2249,17 @@
         <v>12</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O27" s="2">
         <v>6</v>
@@ -2313,16 +2270,16 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2331,28 +2288,28 @@
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O28" s="2">
         <v>12</v>
@@ -2363,16 +2320,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2">
         <v>255</v>
@@ -2381,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>12</v>
@@ -2390,20 +2347,20 @@
         <v>12</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O29" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>13</v>
@@ -2411,25 +2368,25 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>12</v>
@@ -2438,17 +2395,19 @@
         <v>12</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O30" s="2">
         <v>6</v>
@@ -2459,49 +2418,47 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O31" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>13</v>
@@ -2509,7 +2466,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>65</v>
@@ -2518,16 +2475,16 @@
         <v>66</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>12</v>
@@ -2536,20 +2493,20 @@
         <v>12</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O32" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>13</v>
@@ -2557,16 +2514,16 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
@@ -2575,7 +2532,7 @@
         <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>12</v>
@@ -2584,19 +2541,17 @@
         <v>12</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O33" s="2">
         <v>6</v>
@@ -2607,7 +2562,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>70</v>
@@ -2616,16 +2571,16 @@
         <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>12</v>
@@ -2634,20 +2589,20 @@
         <v>12</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O34" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>13</v>
@@ -2655,47 +2610,47 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O35" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>13</v>
@@ -2703,7 +2658,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>75</v>
@@ -2712,7 +2667,7 @@
         <v>76</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -2721,7 +2676,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>12</v>
@@ -2730,20 +2685,22 @@
         <v>12</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M36" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O36" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>13</v>
@@ -2751,7 +2708,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>77</v>
@@ -2760,16 +2717,16 @@
         <v>78</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>12</v>
@@ -2778,20 +2735,20 @@
         <v>12</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O37" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>13</v>
@@ -2799,47 +2756,47 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O38" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>13</v>
@@ -2847,25 +2804,25 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>12</v>
@@ -2874,22 +2831,20 @@
         <v>12</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O39" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>13</v>
@@ -2897,25 +2852,25 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>12</v>
@@ -2924,17 +2879,17 @@
         <v>12</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O40" s="2">
         <v>6</v>
@@ -2945,25 +2900,25 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E41" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>12</v>
@@ -2972,17 +2927,17 @@
         <v>12</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O41" s="2">
         <v>6</v>
@@ -2996,44 +2951,46 @@
         <v>23</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="N42" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O42" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>13</v>
@@ -3044,22 +3001,22 @@
         <v>23</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>12</v>
@@ -3068,17 +3025,17 @@
         <v>12</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O43" s="2">
         <v>6</v>
@@ -3092,22 +3049,22 @@
         <v>23</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>12</v>
@@ -3116,17 +3073,17 @@
         <v>12</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O44" s="2">
         <v>6</v>
@@ -3140,43 +3097,41 @@
         <v>25</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O45" s="2">
         <v>12</v>
@@ -3190,13 +3145,13 @@
         <v>25</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E46" s="2">
         <v>255</v>
@@ -3205,7 +3160,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>12</v>
@@ -3214,20 +3169,20 @@
         <v>12</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O46" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>13</v>
@@ -3238,22 +3193,22 @@
         <v>25</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>12</v>
@@ -3262,20 +3217,20 @@
         <v>12</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O47" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>13</v>
@@ -3283,25 +3238,25 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>12</v>
@@ -3310,17 +3265,17 @@
         <v>12</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O48" s="2">
         <v>12</v>
@@ -3331,25 +3286,25 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E49" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>12</v>
@@ -3358,17 +3313,17 @@
         <v>12</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O49" s="2">
         <v>12</v>
@@ -3379,25 +3334,25 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E50" s="2">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>12</v>
@@ -3406,170 +3361,32 @@
         <v>12</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O50" s="2">
         <v>12</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E51" s="2">
-        <v>255</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O51" s="2">
-        <v>12</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O52" s="2">
-        <v>12</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="2">
-        <v>36</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O53" s="2">
-        <v>12</v>
-      </c>
-      <c r="P53" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{cdb710b6-7041-4093-8e6f-80ac01d6c65a}" enabled="0" method="" siteId="{cdb710b6-7041-4093-8e6f-80ac01d6c65a}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C091B7-6C5C-4987-BA6E-C95912DF72FB}"/>
+  <xr:revisionPtr revIDLastSave="1462" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F499AA-C15B-4946-B735-895B831081B9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="170">
   <si>
     <t>Table Name</t>
   </si>
@@ -326,7 +326,211 @@
     <t>User Id</t>
   </si>
   <si>
-    <t>Sub-detail list</t>
+    <t>Sub-detail / list</t>
+  </si>
+  <si>
+    <t>StatusReport</t>
+  </si>
+  <si>
+    <t>Weekly Project Status Report</t>
+  </si>
+  <si>
+    <t>StatusReportHealthIndicator</t>
+  </si>
+  <si>
+    <t>Status Report Health Indicators</t>
+  </si>
+  <si>
+    <t>Milestone</t>
+  </si>
+  <si>
+    <t>Project Milestones</t>
+  </si>
+  <si>
+    <t>RiskIssue</t>
+  </si>
+  <si>
+    <t>Project Risks And Issues Register</t>
+  </si>
+  <si>
+    <t>ProjectCode</t>
+  </si>
+  <si>
+    <t>Project Code (e.g. CPE-001)</t>
+  </si>
+  <si>
+    <t>DeliveryTower</t>
+  </si>
+  <si>
+    <t>Delivery Tower (Infrastructure, Application, Smart City)</t>
+  </si>
+  <si>
+    <t>DemandType</t>
+  </si>
+  <si>
+    <t>Demand Type (e.g. AI Solution, Data &amp; Analytics)</t>
+  </si>
+  <si>
+    <t>TechnologyBusinessPartner</t>
+  </si>
+  <si>
+    <t>Technology Business Partner (Auto-assigned from BU)</t>
+  </si>
+  <si>
+    <t>DeputyProjectManagerId</t>
+  </si>
+  <si>
+    <t>Assigned Deputy Project Manager</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Project Status (e.g. Active)</t>
+  </si>
+  <si>
+    <t>BudgetStatus</t>
+  </si>
+  <si>
+    <t>Budget Status (On Track, At Risk, Overbudget)</t>
+  </si>
+  <si>
+    <t>SOWFileName</t>
+  </si>
+  <si>
+    <t>Statement of Work Attachment (PDF, DOC, DOCX)</t>
+  </si>
+  <si>
+    <t>MemberLevel</t>
+  </si>
+  <si>
+    <t>Member Level (Rank &amp; File, Supervisor, Manager)</t>
+  </si>
+  <si>
+    <t>ReportWeekStart</t>
+  </si>
+  <si>
+    <t>Report Period Start Date</t>
+  </si>
+  <si>
+    <t>ReportWeekEnd</t>
+  </si>
+  <si>
+    <t>Report Period End Date</t>
+  </si>
+  <si>
+    <t>SubmissionDate</t>
+  </si>
+  <si>
+    <t>Date Report Was Submitted</t>
+  </si>
+  <si>
+    <t>OverallHealth</t>
+  </si>
+  <si>
+    <t>Overall RAG Status (Red, Amber, Green)</t>
+  </si>
+  <si>
+    <t>Report Status (Not Submitted, Pending Review, Approved)</t>
+  </si>
+  <si>
+    <t>Accomplishments</t>
+  </si>
+  <si>
+    <t>Accomplishments This Week</t>
+  </si>
+  <si>
+    <t>NextSteps</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>BaselineBudget</t>
+  </si>
+  <si>
+    <t>Baseline Budget in Currency</t>
+  </si>
+  <si>
+    <t>ActualSpend</t>
+  </si>
+  <si>
+    <t>Actual Spend in Currency</t>
+  </si>
+  <si>
+    <t>ScheduleVarianceWeeks</t>
+  </si>
+  <si>
+    <t>Schedule Variance in Weeks</t>
+  </si>
+  <si>
+    <t>StatusReportId</t>
+  </si>
+  <si>
+    <t>Reference to Status Report</t>
+  </si>
+  <si>
+    <t>Health Area (Scope, Schedule, Budget, Quality, Risks, Issues)</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Milestone Name</t>
+  </si>
+  <si>
+    <t>Milestone Start Date</t>
+  </si>
+  <si>
+    <t>Milestone Target End Date</t>
+  </si>
+  <si>
+    <t>Milestone Status (Not Started, In Progress, Completed)</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Risk / Issue Code (e.g. R-001, I-001)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Type (Risk or Issue)</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Risk / Issue Title</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Severity (High, Medium, Low)</t>
+  </si>
+  <si>
+    <t>Status (Open, In Progress, Closed)</t>
+  </si>
+  <si>
+    <t>DateRaised</t>
+  </si>
+  <si>
+    <t>Date Raised</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Notes / Remarks</t>
+  </si>
+  <si>
+    <t>OwnerId</t>
+  </si>
+  <si>
+    <t>Risk / Issue Owner</t>
   </si>
 </sst>
 </file>
@@ -730,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -861,9 +1065,7 @@
       <c r="G5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -935,6 +1137,86 @@
       </c>
       <c r="H8" s="3" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1058,9 +1340,7 @@
       <c r="O2" s="2">
         <v>12</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1106,9 +1386,7 @@
       <c r="O3" s="2">
         <v>12</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1154,9 +1432,7 @@
       <c r="O4" s="2">
         <v>12</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -1202,9 +1478,7 @@
       <c r="O5" s="2">
         <v>12</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -1250,9 +1524,7 @@
       <c r="O6" s="2">
         <v>12</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -1298,9 +1570,7 @@
       <c r="O7" s="2">
         <v>12</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -1346,9 +1616,7 @@
       <c r="O8" s="2">
         <v>12</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -1394,9 +1662,7 @@
       <c r="O9" s="2">
         <v>12</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P9" s="3"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
@@ -1442,9 +1708,7 @@
       <c r="O10" s="2">
         <v>12</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -1490,9 +1754,7 @@
       <c r="O11" s="2">
         <v>12</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
@@ -1538,9 +1800,7 @@
       <c r="O12" s="2">
         <v>12</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -1588,9 +1848,7 @@
       <c r="O13" s="2">
         <v>6</v>
       </c>
-      <c r="P13" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -1636,9 +1894,7 @@
       <c r="O14" s="2">
         <v>6</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -1684,9 +1940,7 @@
       <c r="O15" s="2">
         <v>6</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P15" s="3"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
@@ -1732,9 +1986,7 @@
       <c r="O16" s="2">
         <v>6</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1780,9 +2032,7 @@
       <c r="O17" s="2">
         <v>12</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
@@ -1828,9 +2078,7 @@
       <c r="O18" s="2">
         <v>12</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P18" s="3"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1878,9 +2126,7 @@
       <c r="O19" s="2">
         <v>12</v>
       </c>
-      <c r="P19" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P19" s="3"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
@@ -1926,9 +2172,7 @@
       <c r="O20" s="2">
         <v>6</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
@@ -1974,9 +2218,7 @@
       <c r="O21" s="2">
         <v>6</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P21" s="3"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
@@ -2022,9 +2264,7 @@
       <c r="O22" s="2">
         <v>6</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P22" s="3"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -2070,9 +2310,7 @@
       <c r="O23" s="2">
         <v>6</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
@@ -2118,40 +2356,38 @@
       <c r="O24" s="2">
         <v>6</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P24" s="3"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>14</v>
@@ -2159,40 +2395,36 @@
       <c r="L25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O25" s="2">
-        <v>12</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P25" s="3"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E26" s="2">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
@@ -2216,19 +2448,17 @@
       <c r="O26" s="2">
         <v>6</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P26" s="3"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>41</v>
@@ -2240,7 +2470,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>12</v>
@@ -2264,78 +2494,72 @@
       <c r="O27" s="2">
         <v>6</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P27" s="3"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O28" s="2">
-        <v>12</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P28" s="3"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>12</v>
@@ -2355,35 +2579,35 @@
       <c r="L29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M29" s="2"/>
+      <c r="M29" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O29" s="2">
-        <v>12</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P29" s="3"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>12</v>
@@ -2403,28 +2627,24 @@
       <c r="L30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O30" s="2">
         <v>6</v>
       </c>
-      <c r="P30" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P30" s="3"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>41</v>
@@ -2433,10 +2653,10 @@
         <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>12</v>
@@ -2460,25 +2680,23 @@
       <c r="O31" s="2">
         <v>6</v>
       </c>
-      <c r="P31" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P31" s="3"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
@@ -2487,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>12</v>
@@ -2506,24 +2724,22 @@
         <v>42</v>
       </c>
       <c r="O32" s="2">
-        <v>6</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P32" s="3"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
@@ -2535,10 +2751,10 @@
         <v>14</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>14</v>
@@ -2549,35 +2765,35 @@
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="M33" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="N33" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O33" s="2">
-        <v>6</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P33" s="3"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>14</v>
@@ -2602,36 +2818,34 @@
         <v>42</v>
       </c>
       <c r="O34" s="2">
-        <v>12</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P34" s="3"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>12</v>
@@ -2650,33 +2864,31 @@
         <v>42</v>
       </c>
       <c r="O35" s="2">
-        <v>12</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P35" s="3"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>12</v>
@@ -2693,46 +2905,42 @@
       <c r="L36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M36" s="2"/>
       <c r="N36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O36" s="2">
-        <v>12</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P36" s="3"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>14</v>
@@ -2743,38 +2951,38 @@
       <c r="L37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="2"/>
+      <c r="M37" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="N37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O37" s="2">
-        <v>6</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P37" s="3"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>12</v>
@@ -2796,33 +3004,31 @@
         <v>42</v>
       </c>
       <c r="O38" s="2">
-        <v>6</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P38" s="3"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>12</v>
@@ -2839,38 +3045,38 @@
       <c r="L39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M39" s="2"/>
+      <c r="M39" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O39" s="2">
         <v>6</v>
       </c>
-      <c r="P39" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P39" s="3"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>12</v>
@@ -2894,19 +3100,17 @@
       <c r="O40" s="2">
         <v>6</v>
       </c>
-      <c r="P40" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P40" s="3"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>67</v>
@@ -2915,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>14</v>
@@ -2942,22 +3146,20 @@
       <c r="O41" s="2">
         <v>6</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P41" s="3"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2969,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>14</v>
@@ -2983,37 +3185,33 @@
       <c r="L42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="M42" s="2"/>
       <c r="N42" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O42" s="2">
-        <v>12</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P42" s="3"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>14</v>
@@ -3038,36 +3236,34 @@
         <v>42</v>
       </c>
       <c r="O43" s="2">
-        <v>6</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P43" s="3"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>12</v>
@@ -3086,33 +3282,31 @@
         <v>42</v>
       </c>
       <c r="O44" s="2">
-        <v>6</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P44" s="3"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>12</v>
@@ -3129,35 +3323,35 @@
       <c r="L45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M45" s="2"/>
+      <c r="M45" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N45" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O45" s="2">
         <v>12</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="P45" s="3"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E46" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>14</v>
@@ -3182,30 +3376,28 @@
         <v>42</v>
       </c>
       <c r="O46" s="2">
-        <v>12</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P46" s="3"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>14</v>
@@ -3230,30 +3422,28 @@
         <v>42</v>
       </c>
       <c r="O47" s="2">
-        <v>12</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P47" s="3"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>14</v>
@@ -3278,30 +3468,28 @@
         <v>42</v>
       </c>
       <c r="O48" s="2">
-        <v>12</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P48" s="3"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -3326,27 +3514,25 @@
         <v>42</v>
       </c>
       <c r="O49" s="2">
-        <v>12</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P49" s="3"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E50" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>14</v>
@@ -3374,10 +3560,2097 @@
         <v>42</v>
       </c>
       <c r="O50" s="2">
-        <v>12</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" t="s">
+        <v>14</v>
+      </c>
+      <c r="N51" t="s">
+        <v>42</v>
+      </c>
+      <c r="O51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52">
+        <v>50</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N52" t="s">
+        <v>42</v>
+      </c>
+      <c r="O52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53">
+        <v>100</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" t="s">
+        <v>14</v>
+      </c>
+      <c r="N53" t="s">
+        <v>42</v>
+      </c>
+      <c r="O53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54">
+        <v>150</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L54" t="s">
+        <v>14</v>
+      </c>
+      <c r="N54" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" t="s">
+        <v>25</v>
+      </c>
+      <c r="N55" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56">
+        <v>50</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" t="s">
+        <v>14</v>
+      </c>
+      <c r="N56" t="s">
+        <v>42</v>
+      </c>
+      <c r="O56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57">
+        <v>50</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" t="s">
+        <v>14</v>
+      </c>
+      <c r="N57" t="s">
+        <v>42</v>
+      </c>
+      <c r="O57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58">
+        <v>255</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" t="s">
+        <v>14</v>
+      </c>
+      <c r="K58" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" t="s">
+        <v>14</v>
+      </c>
+      <c r="N58" t="s">
+        <v>42</v>
+      </c>
+      <c r="O58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" t="s">
+        <v>14</v>
+      </c>
+      <c r="M59" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60">
+        <v>255</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" t="s">
+        <v>14</v>
+      </c>
+      <c r="L60" t="s">
+        <v>14</v>
+      </c>
+      <c r="N60" t="s">
+        <v>42</v>
+      </c>
+      <c r="O60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61">
+        <v>100</v>
+      </c>
+      <c r="F61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K61" t="s">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
+        <v>42</v>
+      </c>
+      <c r="O61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62">
+        <v>50</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J62" t="s">
+        <v>14</v>
+      </c>
+      <c r="K62" t="s">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>14</v>
+      </c>
+      <c r="N62" t="s">
+        <v>42</v>
+      </c>
+      <c r="O62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J63" t="s">
+        <v>14</v>
+      </c>
+      <c r="K63" t="s">
+        <v>14</v>
+      </c>
+      <c r="L63" t="s">
+        <v>14</v>
+      </c>
+      <c r="N63" t="s">
+        <v>42</v>
+      </c>
+      <c r="O63">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64">
+        <v>255</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J64" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" t="s">
+        <v>14</v>
+      </c>
+      <c r="L64" t="s">
+        <v>14</v>
+      </c>
+      <c r="N64" t="s">
+        <v>42</v>
+      </c>
+      <c r="O64">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65">
+        <v>450</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J65" t="s">
+        <v>14</v>
+      </c>
+      <c r="K65" t="s">
+        <v>14</v>
+      </c>
+      <c r="L65" t="s">
+        <v>14</v>
+      </c>
+      <c r="N65" t="s">
+        <v>42</v>
+      </c>
+      <c r="O65">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66">
+        <v>255</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s">
+        <v>12</v>
+      </c>
+      <c r="I66" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" t="s">
+        <v>14</v>
+      </c>
+      <c r="K66" t="s">
+        <v>14</v>
+      </c>
+      <c r="L66" t="s">
+        <v>14</v>
+      </c>
+      <c r="N66" t="s">
+        <v>42</v>
+      </c>
+      <c r="O66">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s">
+        <v>12</v>
+      </c>
+      <c r="I67" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" t="s">
+        <v>14</v>
+      </c>
+      <c r="L67" t="s">
+        <v>14</v>
+      </c>
+      <c r="N67" t="s">
+        <v>42</v>
+      </c>
+      <c r="O67">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68">
+        <v>36</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" t="s">
+        <v>12</v>
+      </c>
+      <c r="J68" t="s">
+        <v>14</v>
+      </c>
+      <c r="K68" t="s">
+        <v>14</v>
+      </c>
+      <c r="L68" t="s">
+        <v>14</v>
+      </c>
+      <c r="N68" t="s">
+        <v>42</v>
+      </c>
+      <c r="O68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69" t="s">
+        <v>14</v>
+      </c>
+      <c r="K69" t="s">
+        <v>14</v>
+      </c>
+      <c r="L69" t="s">
+        <v>14</v>
+      </c>
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>42</v>
+      </c>
+      <c r="O69">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>102</v>
+      </c>
+      <c r="B70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" t="s">
+        <v>14</v>
+      </c>
+      <c r="L70" t="s">
+        <v>14</v>
+      </c>
+      <c r="N70" t="s">
+        <v>42</v>
+      </c>
+      <c r="O70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" t="s">
+        <v>130</v>
+      </c>
+      <c r="C71" t="s">
+        <v>131</v>
+      </c>
+      <c r="D71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71" t="s">
+        <v>14</v>
+      </c>
+      <c r="K71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L71" t="s">
+        <v>14</v>
+      </c>
+      <c r="N71" t="s">
+        <v>42</v>
+      </c>
+      <c r="O71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s">
+        <v>14</v>
+      </c>
+      <c r="L72" t="s">
+        <v>14</v>
+      </c>
+      <c r="N72" t="s">
+        <v>42</v>
+      </c>
+      <c r="O72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" t="s">
+        <v>135</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73">
+        <v>20</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73" t="s">
+        <v>14</v>
+      </c>
+      <c r="K73" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" t="s">
+        <v>14</v>
+      </c>
+      <c r="N73" t="s">
+        <v>42</v>
+      </c>
+      <c r="O73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>102</v>
+      </c>
+      <c r="B74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74">
+        <v>50</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" t="s">
+        <v>14</v>
+      </c>
+      <c r="K74" t="s">
+        <v>14</v>
+      </c>
+      <c r="L74" t="s">
+        <v>14</v>
+      </c>
+      <c r="N74" t="s">
+        <v>42</v>
+      </c>
+      <c r="O74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>102</v>
+      </c>
+      <c r="B75" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75">
+        <v>2000</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" t="s">
+        <v>14</v>
+      </c>
+      <c r="K75" t="s">
+        <v>14</v>
+      </c>
+      <c r="L75" t="s">
+        <v>14</v>
+      </c>
+      <c r="N75" t="s">
+        <v>42</v>
+      </c>
+      <c r="O75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" t="s">
+        <v>140</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76">
+        <v>2000</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" t="s">
+        <v>14</v>
+      </c>
+      <c r="K76" t="s">
+        <v>14</v>
+      </c>
+      <c r="L76" t="s">
+        <v>14</v>
+      </c>
+      <c r="N76" t="s">
+        <v>42</v>
+      </c>
+      <c r="O76">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" t="s">
+        <v>142</v>
+      </c>
+      <c r="D77" t="s">
+        <v>72</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" t="s">
+        <v>14</v>
+      </c>
+      <c r="K77" t="s">
+        <v>14</v>
+      </c>
+      <c r="L77" t="s">
+        <v>14</v>
+      </c>
+      <c r="N77" t="s">
+        <v>42</v>
+      </c>
+      <c r="O77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" t="s">
+        <v>72</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" t="s">
+        <v>14</v>
+      </c>
+      <c r="K78" t="s">
+        <v>14</v>
+      </c>
+      <c r="L78" t="s">
+        <v>14</v>
+      </c>
+      <c r="N78" t="s">
+        <v>42</v>
+      </c>
+      <c r="O78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" t="s">
+        <v>146</v>
+      </c>
+      <c r="D79" t="s">
+        <v>62</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" t="s">
+        <v>12</v>
+      </c>
+      <c r="J79" t="s">
+        <v>14</v>
+      </c>
+      <c r="K79" t="s">
+        <v>14</v>
+      </c>
+      <c r="L79" t="s">
+        <v>14</v>
+      </c>
+      <c r="N79" t="s">
+        <v>42</v>
+      </c>
+      <c r="O79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" t="s">
+        <v>147</v>
+      </c>
+      <c r="C80" t="s">
+        <v>148</v>
+      </c>
+      <c r="D80" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" t="s">
+        <v>14</v>
+      </c>
+      <c r="J80" t="s">
+        <v>14</v>
+      </c>
+      <c r="K80" t="s">
+        <v>14</v>
+      </c>
+      <c r="L80" t="s">
+        <v>14</v>
+      </c>
+      <c r="M80" t="s">
+        <v>102</v>
+      </c>
+      <c r="N80" t="s">
+        <v>42</v>
+      </c>
+      <c r="O80">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81">
+        <v>50</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" t="s">
+        <v>12</v>
+      </c>
+      <c r="J81" t="s">
+        <v>14</v>
+      </c>
+      <c r="K81" t="s">
+        <v>14</v>
+      </c>
+      <c r="L81" t="s">
+        <v>14</v>
+      </c>
+      <c r="N81" t="s">
+        <v>42</v>
+      </c>
+      <c r="O81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>104</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82">
+        <v>20</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" t="s">
+        <v>12</v>
+      </c>
+      <c r="J82" t="s">
+        <v>14</v>
+      </c>
+      <c r="K82" t="s">
+        <v>14</v>
+      </c>
+      <c r="L82" t="s">
+        <v>14</v>
+      </c>
+      <c r="N82" t="s">
+        <v>42</v>
+      </c>
+      <c r="O82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>104</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" t="s">
+        <v>150</v>
+      </c>
+      <c r="D83" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83">
+        <v>500</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" t="s">
+        <v>14</v>
+      </c>
+      <c r="K83" t="s">
+        <v>14</v>
+      </c>
+      <c r="L83" t="s">
+        <v>14</v>
+      </c>
+      <c r="N83" t="s">
+        <v>42</v>
+      </c>
+      <c r="O83">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>106</v>
+      </c>
+      <c r="B84" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" t="s">
+        <v>14</v>
+      </c>
+      <c r="J84" t="s">
+        <v>14</v>
+      </c>
+      <c r="K84" t="s">
+        <v>14</v>
+      </c>
+      <c r="L84" t="s">
+        <v>14</v>
+      </c>
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>42</v>
+      </c>
+      <c r="O84">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85" t="s">
+        <v>151</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85">
+        <v>255</v>
+      </c>
+      <c r="F85" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" t="s">
+        <v>12</v>
+      </c>
+      <c r="H85" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" t="s">
+        <v>12</v>
+      </c>
+      <c r="J85" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" t="s">
+        <v>14</v>
+      </c>
+      <c r="L85" t="s">
+        <v>14</v>
+      </c>
+      <c r="N85" t="s">
+        <v>42</v>
+      </c>
+      <c r="O85">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" t="s">
+        <v>65</v>
+      </c>
+      <c r="C86" t="s">
+        <v>152</v>
+      </c>
+      <c r="D86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" t="s">
+        <v>14</v>
+      </c>
+      <c r="K86" t="s">
+        <v>14</v>
+      </c>
+      <c r="L86" t="s">
+        <v>14</v>
+      </c>
+      <c r="N86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" t="s">
+        <v>14</v>
+      </c>
+      <c r="K87" t="s">
+        <v>14</v>
+      </c>
+      <c r="L87" t="s">
+        <v>14</v>
+      </c>
+      <c r="N87" t="s">
+        <v>42</v>
+      </c>
+      <c r="O87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>106</v>
+      </c>
+      <c r="B88" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" t="s">
+        <v>154</v>
+      </c>
+      <c r="D88" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88">
+        <v>50</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" t="s">
+        <v>12</v>
+      </c>
+      <c r="J88" t="s">
+        <v>14</v>
+      </c>
+      <c r="K88" t="s">
+        <v>14</v>
+      </c>
+      <c r="L88" t="s">
+        <v>14</v>
+      </c>
+      <c r="N88" t="s">
+        <v>42</v>
+      </c>
+      <c r="O88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+      <c r="B89" t="s">
+        <v>87</v>
+      </c>
+      <c r="C89" t="s">
+        <v>88</v>
+      </c>
+      <c r="D89" t="s">
+        <v>62</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" t="s">
+        <v>14</v>
+      </c>
+      <c r="J89" t="s">
+        <v>14</v>
+      </c>
+      <c r="K89" t="s">
+        <v>14</v>
+      </c>
+      <c r="L89" t="s">
+        <v>14</v>
+      </c>
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>42</v>
+      </c>
+      <c r="O89">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" t="s">
+        <v>156</v>
+      </c>
+      <c r="D90" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90">
+        <v>20</v>
+      </c>
+      <c r="F90" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90" t="s">
+        <v>14</v>
+      </c>
+      <c r="K90" t="s">
+        <v>14</v>
+      </c>
+      <c r="L90" t="s">
+        <v>14</v>
+      </c>
+      <c r="N90" t="s">
+        <v>42</v>
+      </c>
+      <c r="O90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" t="s">
+        <v>158</v>
+      </c>
+      <c r="D91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" t="s">
+        <v>14</v>
+      </c>
+      <c r="K91" t="s">
+        <v>14</v>
+      </c>
+      <c r="L91" t="s">
+        <v>14</v>
+      </c>
+      <c r="N91" t="s">
+        <v>42</v>
+      </c>
+      <c r="O91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" t="s">
+        <v>159</v>
+      </c>
+      <c r="C92" t="s">
+        <v>160</v>
+      </c>
+      <c r="D92" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92">
+        <v>255</v>
+      </c>
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" t="s">
+        <v>14</v>
+      </c>
+      <c r="K92" t="s">
+        <v>14</v>
+      </c>
+      <c r="L92" t="s">
+        <v>14</v>
+      </c>
+      <c r="N92" t="s">
+        <v>42</v>
+      </c>
+      <c r="O92">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93" t="s">
+        <v>162</v>
+      </c>
+      <c r="D93" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93">
+        <v>20</v>
+      </c>
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>12</v>
+      </c>
+      <c r="J93" t="s">
+        <v>14</v>
+      </c>
+      <c r="K93" t="s">
+        <v>14</v>
+      </c>
+      <c r="L93" t="s">
+        <v>14</v>
+      </c>
+      <c r="N93" t="s">
+        <v>42</v>
+      </c>
+      <c r="O93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" t="s">
+        <v>120</v>
+      </c>
+      <c r="C94" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94">
+        <v>50</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" t="s">
+        <v>14</v>
+      </c>
+      <c r="K94" t="s">
+        <v>14</v>
+      </c>
+      <c r="L94" t="s">
+        <v>14</v>
+      </c>
+      <c r="N94" t="s">
+        <v>42</v>
+      </c>
+      <c r="O94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" t="s">
+        <v>168</v>
+      </c>
+      <c r="C95" t="s">
+        <v>169</v>
+      </c>
+      <c r="D95" t="s">
+        <v>62</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" t="s">
+        <v>12</v>
+      </c>
+      <c r="J95" t="s">
+        <v>14</v>
+      </c>
+      <c r="K95" t="s">
+        <v>14</v>
+      </c>
+      <c r="L95" t="s">
+        <v>14</v>
+      </c>
+      <c r="M95" t="s">
+        <v>25</v>
+      </c>
+      <c r="N95" t="s">
+        <v>42</v>
+      </c>
+      <c r="O95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>108</v>
+      </c>
+      <c r="B96" t="s">
+        <v>164</v>
+      </c>
+      <c r="C96" t="s">
+        <v>165</v>
+      </c>
+      <c r="D96" t="s">
+        <v>67</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" t="s">
+        <v>14</v>
+      </c>
+      <c r="K96" t="s">
+        <v>14</v>
+      </c>
+      <c r="L96" t="s">
+        <v>14</v>
+      </c>
+      <c r="N96" t="s">
+        <v>42</v>
+      </c>
+      <c r="O96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>108</v>
+      </c>
+      <c r="B97" t="s">
+        <v>166</v>
+      </c>
+      <c r="C97" t="s">
+        <v>167</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97">
+        <v>1000</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" t="s">
+        <v>14</v>
+      </c>
+      <c r="H97" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" t="s">
+        <v>14</v>
+      </c>
+      <c r="L97" t="s">
+        <v>14</v>
+      </c>
+      <c r="N97" t="s">
+        <v>42</v>
+      </c>
+      <c r="O97">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1462" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F499AA-C15B-4946-B735-895B831081B9}"/>
+  <xr:revisionPtr revIDLastSave="1846" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2169B82-A6E7-4710-BEFD-D779E8E2BCB7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,15 @@
     <sheet name="Table" sheetId="1" r:id="rId1"/>
     <sheet name="Column" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$120</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="188">
   <si>
     <t>Table Name</t>
   </si>
@@ -407,18 +410,6 @@
     <t>Member Level (Rank &amp; File, Supervisor, Manager)</t>
   </si>
   <si>
-    <t>ReportWeekStart</t>
-  </si>
-  <si>
-    <t>Report Period Start Date</t>
-  </si>
-  <si>
-    <t>ReportWeekEnd</t>
-  </si>
-  <si>
-    <t>Report Period End Date</t>
-  </si>
-  <si>
     <t>SubmissionDate</t>
   </si>
   <si>
@@ -431,9 +422,6 @@
     <t>Overall RAG Status (Red, Amber, Green)</t>
   </si>
   <si>
-    <t>Report Status (Not Submitted, Pending Review, Approved)</t>
-  </si>
-  <si>
     <t>Accomplishments</t>
   </si>
   <si>
@@ -531,6 +519,75 @@
   </si>
   <si>
     <t>Risk / Issue Owner</t>
+  </si>
+  <si>
+    <t>ReportingWeekId</t>
+  </si>
+  <si>
+    <t>Reference to Reporting Week</t>
+  </si>
+  <si>
+    <t>ReportingWeek</t>
+  </si>
+  <si>
+    <t>Report Status (Pending Review, Approved, Changes Requested)</t>
+  </si>
+  <si>
+    <t>ReviewComments</t>
+  </si>
+  <si>
+    <t>Review Comments</t>
+  </si>
+  <si>
+    <t>ReviewedDate</t>
+  </si>
+  <si>
+    <t>Date Reviewed</t>
+  </si>
+  <si>
+    <t>ReviewedById</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Schedule Status (On Track, Delayed)</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Reporting Year (e.g. 2026)</t>
+  </si>
+  <si>
+    <t>WeekNumber</t>
+  </si>
+  <si>
+    <t>Work Week Number (e.g. 29)</t>
+  </si>
+  <si>
+    <t>Week Start Date</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>Week End Date</t>
+  </si>
+  <si>
+    <t>StatusReportMilestone</t>
+  </si>
+  <si>
+    <t>StatusReportRiskIssue</t>
+  </si>
+  <si>
+    <t>Reporting Week</t>
+  </si>
+  <si>
+    <t>Status Report Milestone Snapshot</t>
+  </si>
+  <si>
+    <t>Status Report Risk And Issue Snapshot</t>
   </si>
 </sst>
 </file>
@@ -934,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1219,6 +1276,66 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1226,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -4414,13 +4531,13 @@
         <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4429,7 +4546,7 @@
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
         <v>12</v>
@@ -4445,6 +4562,9 @@
       </c>
       <c r="L70" t="s">
         <v>14</v>
+      </c>
+      <c r="M70" t="s">
+        <v>167</v>
       </c>
       <c r="N70" t="s">
         <v>42</v>
@@ -4458,10 +4578,10 @@
         <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D71" t="s">
         <v>67</v>
@@ -4470,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
@@ -4502,22 +4622,22 @@
         <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C72" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -4546,19 +4666,19 @@
         <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C73" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="D73" t="s">
         <v>41</v>
       </c>
       <c r="E73">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G73" t="s">
         <v>12</v>
@@ -4590,25 +4710,25 @@
         <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
       </c>
       <c r="E74">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="F74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
         <v>12</v>
@@ -4626,7 +4746,7 @@
         <v>42</v>
       </c>
       <c r="O74">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
@@ -4634,10 +4754,10 @@
         <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
         <v>41</v>
@@ -4678,16 +4798,16 @@
         <v>102</v>
       </c>
       <c r="B76" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C76" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E76">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
@@ -4696,7 +4816,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I76" t="s">
         <v>12</v>
@@ -4714,7 +4834,7 @@
         <v>42</v>
       </c>
       <c r="O76">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -4722,10 +4842,10 @@
         <v>102</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D77" t="s">
         <v>72</v>
@@ -4766,13 +4886,13 @@
         <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D78" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4810,16 +4930,16 @@
         <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D79" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
@@ -4851,31 +4971,31 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
         <v>14</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J80" t="s">
         <v>14</v>
@@ -4886,34 +5006,31 @@
       <c r="L80" t="s">
         <v>14</v>
       </c>
-      <c r="M80" t="s">
-        <v>102</v>
-      </c>
       <c r="N80" t="s">
         <v>42</v>
       </c>
       <c r="O80">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
         <v>41</v>
       </c>
       <c r="E81">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F81" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
         <v>14</v>
@@ -4942,25 +5059,25 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E82">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -4976,6 +5093,9 @@
       </c>
       <c r="L82" t="s">
         <v>14</v>
+      </c>
+      <c r="M82" t="s">
+        <v>25</v>
       </c>
       <c r="N82" t="s">
         <v>42</v>
@@ -4986,19 +5106,19 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E83">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
@@ -5025,27 +5145,27 @@
         <v>42</v>
       </c>
       <c r="O83">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -5054,7 +5174,7 @@
         <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J84" t="s">
         <v>14</v>
@@ -5064,9 +5184,6 @@
       </c>
       <c r="L84" t="s">
         <v>14</v>
-      </c>
-      <c r="M84" t="s">
-        <v>17</v>
       </c>
       <c r="N84" t="s">
         <v>42</v>
@@ -5077,31 +5194,31 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B85" t="s">
-        <v>39</v>
+        <v>142</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E85">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
       </c>
       <c r="G85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J85" t="s">
         <v>14</v>
@@ -5111,6 +5228,9 @@
       </c>
       <c r="L85" t="s">
         <v>14</v>
+      </c>
+      <c r="M85" t="s">
+        <v>102</v>
       </c>
       <c r="N85" t="s">
         <v>42</v>
@@ -5121,19 +5241,19 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D86" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
@@ -5165,19 +5285,19 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B87" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="D87" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
@@ -5209,22 +5329,22 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B88" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
         <v>41</v>
       </c>
       <c r="E88">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F88" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
@@ -5248,12 +5368,12 @@
         <v>42</v>
       </c>
       <c r="O88">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B89" t="s">
         <v>87</v>
@@ -5300,19 +5420,19 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
         <v>41</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
@@ -5339,30 +5459,30 @@
         <v>42</v>
       </c>
       <c r="O90">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
       </c>
       <c r="G91" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -5388,25 +5508,25 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E92">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s">
         <v>12</v>
@@ -5427,30 +5547,30 @@
         <v>42</v>
       </c>
       <c r="O92">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D93" t="s">
         <v>41</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -5479,28 +5599,28 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C94" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E94">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J94" t="s">
         <v>14</v>
@@ -5511,11 +5631,14 @@
       <c r="L94" t="s">
         <v>14</v>
       </c>
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
       <c r="N94" t="s">
         <v>42</v>
       </c>
       <c r="O94">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
@@ -5523,16 +5646,16 @@
         <v>108</v>
       </c>
       <c r="B95" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C95" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -5554,9 +5677,6 @@
       </c>
       <c r="L95" t="s">
         <v>14</v>
-      </c>
-      <c r="M95" t="s">
-        <v>25</v>
       </c>
       <c r="N95" t="s">
         <v>42</v>
@@ -5570,22 +5690,22 @@
         <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C96" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D96" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -5614,46 +5734,1071 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C97" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97">
+        <v>255</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" t="s">
+        <v>14</v>
+      </c>
+      <c r="L97" t="s">
+        <v>14</v>
+      </c>
+      <c r="N97" t="s">
+        <v>42</v>
+      </c>
+      <c r="O97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" t="s">
+        <v>156</v>
+      </c>
+      <c r="C98" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98">
+        <v>20</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" t="s">
+        <v>12</v>
+      </c>
+      <c r="J98" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" t="s">
+        <v>14</v>
+      </c>
+      <c r="L98" t="s">
+        <v>14</v>
+      </c>
+      <c r="N98" t="s">
+        <v>42</v>
+      </c>
+      <c r="O98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>120</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99">
+        <v>50</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" t="s">
+        <v>12</v>
+      </c>
+      <c r="J99" t="s">
+        <v>14</v>
+      </c>
+      <c r="K99" t="s">
+        <v>14</v>
+      </c>
+      <c r="L99" t="s">
+        <v>14</v>
+      </c>
+      <c r="N99" t="s">
+        <v>42</v>
+      </c>
+      <c r="O99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" t="s">
+        <v>164</v>
+      </c>
+      <c r="D100" t="s">
+        <v>62</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" t="s">
+        <v>14</v>
+      </c>
+      <c r="K100" t="s">
+        <v>14</v>
+      </c>
+      <c r="L100" t="s">
+        <v>14</v>
+      </c>
+      <c r="M100" t="s">
+        <v>25</v>
+      </c>
+      <c r="N100" t="s">
+        <v>42</v>
+      </c>
+      <c r="O100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" t="s">
+        <v>159</v>
+      </c>
+      <c r="C101" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" t="s">
+        <v>67</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" t="s">
+        <v>14</v>
+      </c>
+      <c r="K101" t="s">
+        <v>14</v>
+      </c>
+      <c r="L101" t="s">
+        <v>14</v>
+      </c>
+      <c r="N101" t="s">
+        <v>42</v>
+      </c>
+      <c r="O101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>161</v>
+      </c>
+      <c r="C102" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102">
+        <v>1000</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" t="s">
+        <v>14</v>
+      </c>
+      <c r="H102" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102" t="s">
+        <v>14</v>
+      </c>
+      <c r="K102" t="s">
+        <v>14</v>
+      </c>
+      <c r="L102" t="s">
+        <v>14</v>
+      </c>
+      <c r="N102" t="s">
+        <v>42</v>
+      </c>
+      <c r="O102">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>167</v>
       </c>
-      <c r="D97" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97">
+      <c r="B103" t="s">
+        <v>176</v>
+      </c>
+      <c r="C103" t="s">
+        <v>177</v>
+      </c>
+      <c r="D103" t="s">
+        <v>62</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" t="s">
+        <v>12</v>
+      </c>
+      <c r="J103" t="s">
+        <v>14</v>
+      </c>
+      <c r="K103" t="s">
+        <v>14</v>
+      </c>
+      <c r="L103" t="s">
+        <v>14</v>
+      </c>
+      <c r="N103" t="s">
+        <v>42</v>
+      </c>
+      <c r="O103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" t="s">
+        <v>178</v>
+      </c>
+      <c r="C104" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" t="s">
+        <v>62</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" t="s">
+        <v>12</v>
+      </c>
+      <c r="H104" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" t="s">
+        <v>12</v>
+      </c>
+      <c r="J104" t="s">
+        <v>14</v>
+      </c>
+      <c r="K104" t="s">
+        <v>14</v>
+      </c>
+      <c r="L104" t="s">
+        <v>14</v>
+      </c>
+      <c r="N104" t="s">
+        <v>42</v>
+      </c>
+      <c r="O104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>167</v>
+      </c>
+      <c r="B105" t="s">
+        <v>65</v>
+      </c>
+      <c r="C105" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" t="s">
+        <v>67</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" t="s">
+        <v>12</v>
+      </c>
+      <c r="J105" t="s">
+        <v>14</v>
+      </c>
+      <c r="K105" t="s">
+        <v>14</v>
+      </c>
+      <c r="L105" t="s">
+        <v>14</v>
+      </c>
+      <c r="N105" t="s">
+        <v>42</v>
+      </c>
+      <c r="O105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" t="s">
+        <v>67</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" t="s">
+        <v>12</v>
+      </c>
+      <c r="I106" t="s">
+        <v>12</v>
+      </c>
+      <c r="J106" t="s">
+        <v>14</v>
+      </c>
+      <c r="K106" t="s">
+        <v>14</v>
+      </c>
+      <c r="L106" t="s">
+        <v>14</v>
+      </c>
+      <c r="N106" t="s">
+        <v>42</v>
+      </c>
+      <c r="O106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>183</v>
+      </c>
+      <c r="B107" t="s">
+        <v>142</v>
+      </c>
+      <c r="C107" t="s">
+        <v>143</v>
+      </c>
+      <c r="D107" t="s">
+        <v>62</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" t="s">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" t="s">
+        <v>14</v>
+      </c>
+      <c r="J107" t="s">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s">
+        <v>14</v>
+      </c>
+      <c r="L107" t="s">
+        <v>14</v>
+      </c>
+      <c r="M107" t="s">
+        <v>102</v>
+      </c>
+      <c r="N107" t="s">
+        <v>42</v>
+      </c>
+      <c r="O107">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>183</v>
+      </c>
+      <c r="B108" t="s">
+        <v>39</v>
+      </c>
+      <c r="C108" t="s">
+        <v>146</v>
+      </c>
+      <c r="D108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108">
+        <v>255</v>
+      </c>
+      <c r="F108" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" t="s">
+        <v>12</v>
+      </c>
+      <c r="J108" t="s">
+        <v>14</v>
+      </c>
+      <c r="K108" t="s">
+        <v>14</v>
+      </c>
+      <c r="L108" t="s">
+        <v>14</v>
+      </c>
+      <c r="N108" t="s">
+        <v>42</v>
+      </c>
+      <c r="O108">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109" t="s">
+        <v>65</v>
+      </c>
+      <c r="C109" t="s">
+        <v>147</v>
+      </c>
+      <c r="D109" t="s">
+        <v>67</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s">
+        <v>14</v>
+      </c>
+      <c r="L109" t="s">
+        <v>14</v>
+      </c>
+      <c r="N109" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>183</v>
+      </c>
+      <c r="B110" t="s">
+        <v>68</v>
+      </c>
+      <c r="C110" t="s">
+        <v>148</v>
+      </c>
+      <c r="D110" t="s">
+        <v>67</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" t="s">
+        <v>12</v>
+      </c>
+      <c r="J110" t="s">
+        <v>14</v>
+      </c>
+      <c r="K110" t="s">
+        <v>14</v>
+      </c>
+      <c r="L110" t="s">
+        <v>14</v>
+      </c>
+      <c r="N110" t="s">
+        <v>42</v>
+      </c>
+      <c r="O110">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" t="s">
+        <v>149</v>
+      </c>
+      <c r="D111" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111">
+        <v>50</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" t="s">
+        <v>12</v>
+      </c>
+      <c r="J111" t="s">
+        <v>14</v>
+      </c>
+      <c r="K111" t="s">
+        <v>14</v>
+      </c>
+      <c r="L111" t="s">
+        <v>14</v>
+      </c>
+      <c r="N111" t="s">
+        <v>42</v>
+      </c>
+      <c r="O111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>184</v>
+      </c>
+      <c r="B112" t="s">
+        <v>142</v>
+      </c>
+      <c r="C112" t="s">
+        <v>143</v>
+      </c>
+      <c r="D112" t="s">
+        <v>62</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" t="s">
+        <v>14</v>
+      </c>
+      <c r="J112" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" t="s">
+        <v>14</v>
+      </c>
+      <c r="L112" t="s">
+        <v>14</v>
+      </c>
+      <c r="M112" t="s">
+        <v>102</v>
+      </c>
+      <c r="N112" t="s">
+        <v>42</v>
+      </c>
+      <c r="O112">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>184</v>
+      </c>
+      <c r="B113" t="s">
+        <v>150</v>
+      </c>
+      <c r="C113" t="s">
+        <v>151</v>
+      </c>
+      <c r="D113" t="s">
+        <v>41</v>
+      </c>
+      <c r="E113">
+        <v>20</v>
+      </c>
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" t="s">
+        <v>14</v>
+      </c>
+      <c r="H113" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" t="s">
+        <v>12</v>
+      </c>
+      <c r="J113" t="s">
+        <v>14</v>
+      </c>
+      <c r="K113" t="s">
+        <v>14</v>
+      </c>
+      <c r="L113" t="s">
+        <v>14</v>
+      </c>
+      <c r="N113" t="s">
+        <v>42</v>
+      </c>
+      <c r="O113">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>184</v>
+      </c>
+      <c r="B114" t="s">
+        <v>152</v>
+      </c>
+      <c r="C114" t="s">
+        <v>153</v>
+      </c>
+      <c r="D114" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114">
+        <v>20</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" t="s">
+        <v>12</v>
+      </c>
+      <c r="J114" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" t="s">
+        <v>14</v>
+      </c>
+      <c r="L114" t="s">
+        <v>14</v>
+      </c>
+      <c r="N114" t="s">
+        <v>42</v>
+      </c>
+      <c r="O114">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>184</v>
+      </c>
+      <c r="B115" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" t="s">
+        <v>155</v>
+      </c>
+      <c r="D115" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115">
+        <v>255</v>
+      </c>
+      <c r="F115" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" t="s">
+        <v>12</v>
+      </c>
+      <c r="J115" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" t="s">
+        <v>14</v>
+      </c>
+      <c r="L115" t="s">
+        <v>14</v>
+      </c>
+      <c r="N115" t="s">
+        <v>42</v>
+      </c>
+      <c r="O115">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>184</v>
+      </c>
+      <c r="B116" t="s">
+        <v>156</v>
+      </c>
+      <c r="C116" t="s">
+        <v>157</v>
+      </c>
+      <c r="D116" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116">
+        <v>20</v>
+      </c>
+      <c r="F116" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" t="s">
+        <v>12</v>
+      </c>
+      <c r="J116" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" t="s">
+        <v>14</v>
+      </c>
+      <c r="L116" t="s">
+        <v>14</v>
+      </c>
+      <c r="N116" t="s">
+        <v>42</v>
+      </c>
+      <c r="O116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>184</v>
+      </c>
+      <c r="B117" t="s">
+        <v>120</v>
+      </c>
+      <c r="C117" t="s">
+        <v>158</v>
+      </c>
+      <c r="D117" t="s">
+        <v>41</v>
+      </c>
+      <c r="E117">
+        <v>50</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>14</v>
+      </c>
+      <c r="H117" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" t="s">
+        <v>12</v>
+      </c>
+      <c r="J117" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" t="s">
+        <v>14</v>
+      </c>
+      <c r="L117" t="s">
+        <v>14</v>
+      </c>
+      <c r="N117" t="s">
+        <v>42</v>
+      </c>
+      <c r="O117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>184</v>
+      </c>
+      <c r="B118" t="s">
+        <v>163</v>
+      </c>
+      <c r="C118" t="s">
+        <v>164</v>
+      </c>
+      <c r="D118" t="s">
+        <v>62</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" t="s">
+        <v>12</v>
+      </c>
+      <c r="J118" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" t="s">
+        <v>14</v>
+      </c>
+      <c r="L118" t="s">
+        <v>14</v>
+      </c>
+      <c r="M118" t="s">
+        <v>25</v>
+      </c>
+      <c r="N118" t="s">
+        <v>42</v>
+      </c>
+      <c r="O118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>184</v>
+      </c>
+      <c r="B119" t="s">
+        <v>159</v>
+      </c>
+      <c r="C119" t="s">
+        <v>160</v>
+      </c>
+      <c r="D119" t="s">
+        <v>67</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" t="s">
+        <v>12</v>
+      </c>
+      <c r="J119" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s">
+        <v>14</v>
+      </c>
+      <c r="L119" t="s">
+        <v>14</v>
+      </c>
+      <c r="N119" t="s">
+        <v>42</v>
+      </c>
+      <c r="O119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>184</v>
+      </c>
+      <c r="B120" t="s">
+        <v>161</v>
+      </c>
+      <c r="C120" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" t="s">
+        <v>41</v>
+      </c>
+      <c r="E120">
         <v>1000</v>
       </c>
-      <c r="F97" t="s">
-        <v>14</v>
-      </c>
-      <c r="G97" t="s">
-        <v>14</v>
-      </c>
-      <c r="H97" t="s">
-        <v>14</v>
-      </c>
-      <c r="I97" t="s">
-        <v>12</v>
-      </c>
-      <c r="J97" t="s">
-        <v>14</v>
-      </c>
-      <c r="K97" t="s">
-        <v>14</v>
-      </c>
-      <c r="L97" t="s">
-        <v>14</v>
-      </c>
-      <c r="N97" t="s">
-        <v>42</v>
-      </c>
-      <c r="O97">
+      <c r="F120" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" t="s">
+        <v>12</v>
+      </c>
+      <c r="J120" t="s">
+        <v>14</v>
+      </c>
+      <c r="K120" t="s">
+        <v>14</v>
+      </c>
+      <c r="L120" t="s">
+        <v>14</v>
+      </c>
+      <c r="N120" t="s">
+        <v>42</v>
+      </c>
+      <c r="O120">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P120" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1846" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2169B82-A6E7-4710-BEFD-D779E8E2BCB7}"/>
+  <xr:revisionPtr revIDLastSave="1866" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F941DBDC-E14E-4522-A90B-73C738751158}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="196">
   <si>
     <t>Table Name</t>
   </si>
@@ -588,6 +588,30 @@
   </si>
   <si>
     <t>Status Report Risk And Issue Snapshot</t>
+  </si>
+  <si>
+    <t>ApprovedBudget</t>
+  </si>
+  <si>
+    <t>Approved Budget</t>
+  </si>
+  <si>
+    <t>BaselineStartDate</t>
+  </si>
+  <si>
+    <t>Baseline Start Date</t>
+  </si>
+  <si>
+    <t>BaselineEndDate</t>
+  </si>
+  <si>
+    <t>Baseline End Date</t>
+  </si>
+  <si>
+    <t>TechnologyBusinessPartnerId</t>
+  </si>
+  <si>
+    <t>FileUpload</t>
   </si>
 </sst>
 </file>
@@ -1343,6 +1367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1413,7 +1438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1484,7 @@
       </c>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1505,7 +1530,7 @@
       </c>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1551,7 +1576,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1597,7 +1622,7 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1643,7 +1668,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1689,7 +1714,7 @@
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1735,7 +1760,7 @@
       </c>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1781,7 +1806,7 @@
       </c>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1827,7 +1852,7 @@
       </c>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2018,10 +2043,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>67</v>
@@ -2064,10 +2089,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>67</v>
@@ -2110,10 +2135,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>72</v>
@@ -2618,7 +2643,7 @@
         <v>17</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>117</v>
@@ -2650,7 +2675,9 @@
       <c r="L28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M28" s="2"/>
+      <c r="M28" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N28" s="2" t="s">
         <v>42</v>
       </c>
@@ -2810,13 +2837,13 @@
         <v>125</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E32" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>14</v>
@@ -2845,7 +2872,7 @@
       </c>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>18</v>
       </c>
@@ -2893,7 +2920,7 @@
       </c>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>18</v>
       </c>
@@ -2939,7 +2966,7 @@
       </c>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>18</v>
       </c>
@@ -2985,7 +3012,7 @@
       </c>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>18</v>
       </c>
@@ -3031,7 +3058,7 @@
       </c>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>21</v>
       </c>
@@ -3079,7 +3106,7 @@
       </c>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>21</v>
       </c>
@@ -3125,7 +3152,7 @@
       </c>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>21</v>
       </c>
@@ -3173,7 +3200,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>21</v>
       </c>
@@ -3219,7 +3246,7 @@
       </c>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
@@ -3265,7 +3292,7 @@
       </c>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>21</v>
       </c>
@@ -3311,7 +3338,7 @@
       </c>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>21</v>
       </c>
@@ -3357,7 +3384,7 @@
       </c>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>21</v>
       </c>
@@ -3403,7 +3430,7 @@
       </c>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>21</v>
       </c>
@@ -3451,7 +3478,7 @@
       </c>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>21</v>
       </c>
@@ -3497,7 +3524,7 @@
       </c>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>21</v>
       </c>
@@ -3543,7 +3570,7 @@
       </c>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>21</v>
       </c>
@@ -3589,7 +3616,7 @@
       </c>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>21</v>
       </c>
@@ -3635,7 +3662,7 @@
       </c>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>21</v>
       </c>
@@ -3681,7 +3708,7 @@
       </c>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -3725,7 +3752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -3769,7 +3796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>21</v>
       </c>
@@ -3813,7 +3840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>21</v>
       </c>
@@ -3857,7 +3884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>21</v>
       </c>
@@ -3904,7 +3931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -3948,7 +3975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -3992,7 +4019,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -4036,7 +4063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -4083,7 +4110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -4127,7 +4154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -4171,7 +4198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -4215,7 +4242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -4259,7 +4286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -4303,7 +4330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -4347,7 +4374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -4391,7 +4418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4435,7 +4462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4479,7 +4506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>102</v>
       </c>
@@ -4526,7 +4553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>102</v>
       </c>
@@ -4573,7 +4600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>102</v>
       </c>
@@ -4617,7 +4644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>102</v>
       </c>
@@ -4661,7 +4688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>102</v>
       </c>
@@ -4705,7 +4732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -4749,7 +4776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -4793,7 +4820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -4837,7 +4864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -4881,7 +4908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>102</v>
       </c>
@@ -4925,7 +4952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>102</v>
       </c>
@@ -4969,7 +4996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>102</v>
       </c>
@@ -5013,7 +5040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>102</v>
       </c>
@@ -5057,7 +5084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>102</v>
       </c>
@@ -5104,7 +5131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>102</v>
       </c>
@@ -5148,7 +5175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>102</v>
       </c>
@@ -5192,7 +5219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>104</v>
       </c>
@@ -5239,7 +5266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>104</v>
       </c>
@@ -5283,7 +5310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -5327,7 +5354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>104</v>
       </c>
@@ -5371,7 +5398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>106</v>
       </c>
@@ -5418,7 +5445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>106</v>
       </c>
@@ -5462,7 +5489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -5506,7 +5533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -5550,7 +5577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>106</v>
       </c>
@@ -5594,7 +5621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -5641,7 +5668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -5685,7 +5712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -5729,7 +5756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -5773,7 +5800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>108</v>
       </c>
@@ -5817,7 +5844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -5861,7 +5888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -5908,7 +5935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -5952,7 +5979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>108</v>
       </c>
@@ -5996,7 +6023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>167</v>
       </c>
@@ -6040,7 +6067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>167</v>
       </c>
@@ -6084,7 +6111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>167</v>
       </c>
@@ -6128,7 +6155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>167</v>
       </c>
@@ -6172,7 +6199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>183</v>
       </c>
@@ -6219,7 +6246,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>183</v>
       </c>
@@ -6263,7 +6290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>183</v>
       </c>
@@ -6307,7 +6334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>183</v>
       </c>
@@ -6351,7 +6378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>183</v>
       </c>
@@ -6395,7 +6422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>184</v>
       </c>
@@ -6442,7 +6469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>184</v>
       </c>
@@ -6486,7 +6513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>184</v>
       </c>
@@ -6530,7 +6557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>184</v>
       </c>
@@ -6574,7 +6601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>184</v>
       </c>
@@ -6618,7 +6645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>184</v>
       </c>
@@ -6662,7 +6689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>184</v>
       </c>
@@ -6709,7 +6736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>184</v>
       </c>
@@ -6753,7 +6780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>184</v>
       </c>
@@ -6798,7 +6825,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P120" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:P120" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Project"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1866" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F941DBDC-E14E-4522-A90B-73C738751158}"/>
+  <xr:revisionPtr revIDLastSave="1899" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9A6566C-AA1E-448A-A403-ACB0F454881B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="200">
   <si>
     <t>Table Name</t>
   </si>
@@ -612,13 +612,25 @@
   </si>
   <si>
     <t>FileUpload</t>
+  </si>
+  <si>
+    <t>NoSOW</t>
+  </si>
+  <si>
+    <t>If no SOW, SOW File Name is not required</t>
+  </si>
+  <si>
+    <t>ActiveStatus</t>
+  </si>
+  <si>
+    <t>EmployeeId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -633,8 +645,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,6 +661,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFADD8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -674,13 +703,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1367,7 +1406,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1438,15 +1476,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>41</v>
@@ -1484,27 +1522,27 @@
       </c>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
@@ -1513,7 +1551,7 @@
         <v>12</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>14</v>
@@ -1530,21 +1568,21 @@
       </c>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
@@ -1576,21 +1614,21 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="2">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -1622,21 +1660,21 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2">
         <v>50</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="2">
-        <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -1668,21 +1706,21 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="2">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>14</v>
@@ -1691,16 +1729,16 @@
         <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>14</v>
@@ -1714,15 +1752,15 @@
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>41</v>
@@ -1760,15 +1798,15 @@
       </c>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>41</v>
@@ -1783,16 +1821,16 @@
         <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>14</v>
@@ -1806,21 +1844,21 @@
       </c>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>14</v>
@@ -1852,27 +1890,27 @@
       </c>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>12</v>
@@ -1881,7 +1919,7 @@
         <v>12</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>14</v>
@@ -1900,25 +1938,25 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>12</v>
@@ -1942,29 +1980,29 @@
       <c r="O12" s="2">
         <v>12</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>12</v>
@@ -1981,38 +2019,36 @@
       <c r="L13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O13" s="2">
-        <v>6</v>
-      </c>
-      <c r="P13" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="2">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>12</v>
@@ -2034,25 +2070,25 @@
         <v>42</v>
       </c>
       <c r="O14" s="2">
-        <v>6</v>
-      </c>
-      <c r="P14" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="P14" s="2"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
@@ -2080,22 +2116,22 @@
         <v>42</v>
       </c>
       <c r="O15" s="2">
-        <v>6</v>
-      </c>
-      <c r="P15" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="P15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -2126,25 +2162,25 @@
         <v>42</v>
       </c>
       <c r="O16" s="2">
-        <v>6</v>
-      </c>
-      <c r="P16" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="P16" s="2"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>14</v>
@@ -2174,120 +2210,120 @@
       <c r="O17" s="2">
         <v>12</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="2"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O18" s="2">
         <v>12</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="2"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2">
+        <v>255</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O19" s="2">
+        <v>12</v>
+      </c>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="2">
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="2">
-        <v>12</v>
-      </c>
-      <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2">
-        <v>20</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>14</v>
@@ -2314,26 +2350,26 @@
       <c r="O20" s="2">
         <v>6</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>14</v>
@@ -2360,17 +2396,17 @@
       <c r="O21" s="2">
         <v>6</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>41</v>
@@ -2379,7 +2415,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>14</v>
@@ -2406,29 +2442,29 @@
       <c r="O22" s="2">
         <v>6</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>83</v>
+      <c r="B23" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>12</v>
@@ -2450,7 +2486,7 @@
         <v>42</v>
       </c>
       <c r="O23" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P23" s="3"/>
     </row>
@@ -2458,23 +2494,23 @@
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
+      <c r="B24" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>12</v>
@@ -2491,7 +2527,9 @@
       <c r="L24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="2"/>
+      <c r="M24" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N24" s="2" t="s">
         <v>42</v>
       </c>
@@ -2504,17 +2542,17 @@
       <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>110</v>
+      <c r="B25" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E25" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
@@ -2529,7 +2567,7 @@
         <v>12</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>14</v>
@@ -2550,23 +2588,23 @@
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>112</v>
+      <c r="B26" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
@@ -2596,23 +2634,23 @@
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>114</v>
+      <c r="B27" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E27" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>12</v>
@@ -2642,17 +2680,17 @@
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>194</v>
+      <c r="B28" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>14</v>
@@ -2670,19 +2708,17 @@
         <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O28" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P28" s="3"/>
     </row>
@@ -2690,26 +2726,26 @@
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>118</v>
+      <c r="B29" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>12</v>
@@ -2723,270 +2759,268 @@
       <c r="L29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O29" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>120</v>
+      <c r="B30" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O30" s="2">
+        <v>12</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="5">
+        <v>100</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O31" s="5">
+        <v>6</v>
+      </c>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="5">
         <v>50</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O30" s="2">
-        <v>6</v>
-      </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="F32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O32" s="5">
+        <v>6</v>
+      </c>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2">
-        <v>50</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O31" s="2">
-        <v>6</v>
-      </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="B33" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O33" s="5">
+        <v>6</v>
+      </c>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="B34" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="5">
         <v>0</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O32" s="2">
-        <v>12</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="2">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M33" s="2" t="s">
+      <c r="F34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O34" s="5">
+        <v>6</v>
+      </c>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O33" s="2">
-        <v>12</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2">
-        <v>255</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O34" s="2">
-        <v>6</v>
-      </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>91</v>
+      <c r="B35" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="2">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>12</v>
@@ -2995,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>14</v>
@@ -3012,15 +3046,15 @@
       </c>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>126</v>
+        <v>17</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>41</v>
@@ -3029,10 +3063,10 @@
         <v>50</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>12</v>
@@ -3058,33 +3092,33 @@
       </c>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>14</v>
@@ -3095,38 +3129,36 @@
       <c r="L37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="2"/>
+      <c r="N37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O37" s="2">
+        <v>6</v>
+      </c>
+      <c r="P37" s="3"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O37" s="2">
-        <v>12</v>
-      </c>
-      <c r="P37" s="3"/>
-    </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>58</v>
+      <c r="B38" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>12</v>
@@ -3138,29 +3170,31 @@
         <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="2"/>
+      <c r="M38" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O38" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>60</v>
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>62</v>
@@ -3169,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>12</v>
@@ -3190,7 +3224,7 @@
         <v>14</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>42</v>
@@ -3200,15 +3234,15 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>17</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>41</v>
@@ -3217,7 +3251,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>12</v>
@@ -3246,76 +3280,76 @@
       </c>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="2">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O41" s="2">
-        <v>6</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="7">
+        <v>50</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O41" s="7">
+        <v>6</v>
+      </c>
+      <c r="P41" s="8"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>68</v>
+        <v>17</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>12</v>
@@ -3334,22 +3368,22 @@
         <v>42</v>
       </c>
       <c r="O42" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -3361,7 +3395,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>12</v>
@@ -3384,24 +3418,24 @@
       </c>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>14</v>
@@ -3410,7 +3444,7 @@
         <v>14</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>14</v>
@@ -3421,7 +3455,9 @@
       <c r="L44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M44" s="2"/>
+      <c r="M44" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="N44" s="2" t="s">
         <v>42</v>
       </c>
@@ -3430,21 +3466,21 @@
       </c>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
@@ -3467,9 +3503,7 @@
       <c r="L45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
         <v>42</v>
       </c>
@@ -3478,27 +3512,27 @@
       </c>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>12</v>
@@ -3515,7 +3549,9 @@
       <c r="L46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M46" s="2"/>
+      <c r="M46" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N46" s="2" t="s">
         <v>42</v>
       </c>
@@ -3524,27 +3560,27 @@
       </c>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>12</v>
@@ -3570,24 +3606,24 @@
       </c>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E48" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>14</v>
@@ -3616,15 +3652,15 @@
       </c>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>67</v>
@@ -3633,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -3662,739 +3698,752 @@
       </c>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="11">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O50" s="11">
+        <v>12</v>
+      </c>
+      <c r="P50" s="12"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="11">
+        <v>1000</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O51" s="11">
+        <v>12</v>
+      </c>
+      <c r="P51" s="12"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O52" s="11">
+        <v>12</v>
+      </c>
+      <c r="P52" s="12"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="11">
+        <v>20</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O53" s="11">
+        <v>6</v>
+      </c>
+      <c r="P53" s="12"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="11">
+        <v>100</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54" s="11">
+        <v>6</v>
+      </c>
+      <c r="P54" s="12"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="11">
+        <v>50</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55" s="11">
+        <v>6</v>
+      </c>
+      <c r="P55" s="12"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O56" s="11">
+        <v>6</v>
+      </c>
+      <c r="P56" s="12"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A57" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C57" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D57" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E57" s="11">
         <v>0</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O50" s="2">
-        <v>6</v>
-      </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" t="s">
-        <v>12</v>
-      </c>
-      <c r="I51" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" t="s">
-        <v>14</v>
-      </c>
-      <c r="L51" t="s">
-        <v>14</v>
-      </c>
-      <c r="N51" t="s">
-        <v>42</v>
-      </c>
-      <c r="O51">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" t="s">
-        <v>41</v>
-      </c>
-      <c r="E52">
-        <v>50</v>
-      </c>
-      <c r="F52" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" t="s">
-        <v>14</v>
-      </c>
-      <c r="K52" t="s">
-        <v>14</v>
-      </c>
-      <c r="L52" t="s">
-        <v>14</v>
-      </c>
-      <c r="N52" t="s">
-        <v>42</v>
-      </c>
-      <c r="O52">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" t="s">
-        <v>114</v>
-      </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53">
-        <v>100</v>
-      </c>
-      <c r="F53" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>12</v>
-      </c>
-      <c r="H53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" t="s">
-        <v>12</v>
-      </c>
-      <c r="J53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K53" t="s">
-        <v>14</v>
-      </c>
-      <c r="L53" t="s">
-        <v>14</v>
-      </c>
-      <c r="N53" t="s">
-        <v>42</v>
-      </c>
-      <c r="O53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B54" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54">
-        <v>150</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" t="s">
-        <v>12</v>
-      </c>
-      <c r="J54" t="s">
-        <v>14</v>
-      </c>
-      <c r="K54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L54" t="s">
-        <v>14</v>
-      </c>
-      <c r="N54" t="s">
-        <v>42</v>
-      </c>
-      <c r="O54">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" t="s">
-        <v>14</v>
-      </c>
-      <c r="K55" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>14</v>
-      </c>
-      <c r="M55" t="s">
-        <v>25</v>
-      </c>
-      <c r="N55" t="s">
-        <v>42</v>
-      </c>
-      <c r="O55">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C56" t="s">
-        <v>121</v>
-      </c>
-      <c r="D56" t="s">
-        <v>41</v>
-      </c>
-      <c r="E56">
-        <v>50</v>
-      </c>
-      <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" t="s">
-        <v>12</v>
-      </c>
-      <c r="I56" t="s">
-        <v>12</v>
-      </c>
-      <c r="J56" t="s">
-        <v>14</v>
-      </c>
-      <c r="K56" t="s">
-        <v>14</v>
-      </c>
-      <c r="L56" t="s">
-        <v>14</v>
-      </c>
-      <c r="N56" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" t="s">
-        <v>122</v>
-      </c>
-      <c r="C57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D57" t="s">
-        <v>41</v>
-      </c>
-      <c r="E57">
-        <v>50</v>
-      </c>
-      <c r="F57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
-        <v>12</v>
-      </c>
-      <c r="I57" t="s">
-        <v>12</v>
-      </c>
-      <c r="J57" t="s">
-        <v>14</v>
-      </c>
-      <c r="K57" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" t="s">
-        <v>14</v>
-      </c>
-      <c r="N57" t="s">
-        <v>42</v>
-      </c>
-      <c r="O57">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="F57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O57" s="11">
+        <v>6</v>
+      </c>
+      <c r="P57" s="12"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>21</v>
       </c>
       <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" t="s">
+        <v>14</v>
+      </c>
+      <c r="K58" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" t="s">
+        <v>14</v>
+      </c>
+      <c r="N58" t="s">
+        <v>42</v>
+      </c>
+      <c r="O58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+      <c r="D59" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59">
+        <v>50</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" t="s">
+        <v>14</v>
+      </c>
+      <c r="N59" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60">
+        <v>100</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" t="s">
+        <v>14</v>
+      </c>
+      <c r="L60" t="s">
+        <v>14</v>
+      </c>
+      <c r="N60" t="s">
+        <v>42</v>
+      </c>
+      <c r="O60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61">
+        <v>150</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K61" t="s">
+        <v>12</v>
+      </c>
+      <c r="L61" t="s">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
+        <v>42</v>
+      </c>
+      <c r="O61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J62" t="s">
+        <v>14</v>
+      </c>
+      <c r="K62" t="s">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>14</v>
+      </c>
+      <c r="M62" t="s">
+        <v>25</v>
+      </c>
+      <c r="N62" t="s">
+        <v>42</v>
+      </c>
+      <c r="O62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63">
+        <v>50</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J63" t="s">
+        <v>14</v>
+      </c>
+      <c r="K63" t="s">
+        <v>14</v>
+      </c>
+      <c r="L63" t="s">
+        <v>14</v>
+      </c>
+      <c r="N63" t="s">
+        <v>42</v>
+      </c>
+      <c r="O63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D64" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64">
+        <v>50</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J64" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" t="s">
+        <v>14</v>
+      </c>
+      <c r="L64" t="s">
+        <v>14</v>
+      </c>
+      <c r="N64" t="s">
+        <v>42</v>
+      </c>
+      <c r="O64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" t="s">
         <v>124</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C65" t="s">
         <v>125</v>
       </c>
-      <c r="D58" t="s">
-        <v>41</v>
-      </c>
-      <c r="E58">
+      <c r="D65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65">
         <v>255</v>
       </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" t="s">
-        <v>12</v>
-      </c>
-      <c r="J58" t="s">
-        <v>14</v>
-      </c>
-      <c r="K58" t="s">
-        <v>14</v>
-      </c>
-      <c r="L58" t="s">
-        <v>14</v>
-      </c>
-      <c r="N58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O58">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>23</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J65" t="s">
+        <v>14</v>
+      </c>
+      <c r="K65" t="s">
+        <v>14</v>
+      </c>
+      <c r="L65" t="s">
+        <v>14</v>
+      </c>
+      <c r="N65" t="s">
+        <v>42</v>
+      </c>
+      <c r="O65">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>167</v>
+      </c>
+      <c r="B66" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" t="s">
         <v>62</v>
       </c>
-      <c r="E59">
+      <c r="E66">
         <v>0</v>
       </c>
-      <c r="F59" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-      <c r="J59" t="s">
-        <v>14</v>
-      </c>
-      <c r="K59" t="s">
-        <v>14</v>
-      </c>
-      <c r="L59" t="s">
-        <v>14</v>
-      </c>
-      <c r="M59" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O59">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>23</v>
-      </c>
-      <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" t="s">
-        <v>41</v>
-      </c>
-      <c r="E60">
-        <v>255</v>
-      </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>12</v>
-      </c>
-      <c r="I60" t="s">
-        <v>12</v>
-      </c>
-      <c r="J60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K60" t="s">
-        <v>14</v>
-      </c>
-      <c r="L60" t="s">
-        <v>14</v>
-      </c>
-      <c r="N60" t="s">
-        <v>42</v>
-      </c>
-      <c r="O60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61" t="s">
-        <v>41</v>
-      </c>
-      <c r="E61">
-        <v>100</v>
-      </c>
-      <c r="F61" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" t="s">
-        <v>12</v>
-      </c>
-      <c r="I61" t="s">
-        <v>12</v>
-      </c>
-      <c r="J61" t="s">
-        <v>14</v>
-      </c>
-      <c r="K61" t="s">
-        <v>14</v>
-      </c>
-      <c r="L61" t="s">
-        <v>14</v>
-      </c>
-      <c r="N61" t="s">
-        <v>42</v>
-      </c>
-      <c r="O61">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" t="s">
-        <v>127</v>
-      </c>
-      <c r="D62" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62">
-        <v>50</v>
-      </c>
-      <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" t="s">
-        <v>12</v>
-      </c>
-      <c r="I62" t="s">
-        <v>12</v>
-      </c>
-      <c r="J62" t="s">
-        <v>14</v>
-      </c>
-      <c r="K62" t="s">
-        <v>14</v>
-      </c>
-      <c r="L62" t="s">
-        <v>14</v>
-      </c>
-      <c r="N62" t="s">
-        <v>42</v>
-      </c>
-      <c r="O62">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>25</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" t="s">
-        <v>41</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" t="s">
-        <v>12</v>
-      </c>
-      <c r="I63" t="s">
-        <v>12</v>
-      </c>
-      <c r="J63" t="s">
-        <v>14</v>
-      </c>
-      <c r="K63" t="s">
-        <v>14</v>
-      </c>
-      <c r="L63" t="s">
-        <v>14</v>
-      </c>
-      <c r="N63" t="s">
-        <v>42</v>
-      </c>
-      <c r="O63">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>25</v>
-      </c>
-      <c r="B64" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" t="s">
-        <v>41</v>
-      </c>
-      <c r="E64">
-        <v>255</v>
-      </c>
-      <c r="F64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" t="s">
-        <v>12</v>
-      </c>
-      <c r="I64" t="s">
-        <v>12</v>
-      </c>
-      <c r="J64" t="s">
-        <v>14</v>
-      </c>
-      <c r="K64" t="s">
-        <v>14</v>
-      </c>
-      <c r="L64" t="s">
-        <v>14</v>
-      </c>
-      <c r="N64" t="s">
-        <v>42</v>
-      </c>
-      <c r="O64">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>25</v>
-      </c>
-      <c r="B65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" t="s">
-        <v>97</v>
-      </c>
-      <c r="D65" t="s">
-        <v>41</v>
-      </c>
-      <c r="E65">
-        <v>450</v>
-      </c>
-      <c r="F65" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" t="s">
-        <v>12</v>
-      </c>
-      <c r="I65" t="s">
-        <v>12</v>
-      </c>
-      <c r="J65" t="s">
-        <v>14</v>
-      </c>
-      <c r="K65" t="s">
-        <v>14</v>
-      </c>
-      <c r="L65" t="s">
-        <v>14</v>
-      </c>
-      <c r="N65" t="s">
-        <v>42</v>
-      </c>
-      <c r="O65">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>25</v>
-      </c>
-      <c r="B66" t="s">
-        <v>39</v>
-      </c>
-      <c r="C66" t="s">
-        <v>39</v>
-      </c>
-      <c r="D66" t="s">
-        <v>41</v>
-      </c>
-      <c r="E66">
-        <v>255</v>
-      </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H66" t="s">
         <v>12</v>
@@ -4415,21 +4464,21 @@
         <v>42</v>
       </c>
       <c r="O66">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="D67" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4438,7 +4487,7 @@
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H67" t="s">
         <v>12</v>
@@ -4459,27 +4508,27 @@
         <v>42</v>
       </c>
       <c r="O67">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D68" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E68">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G68" t="s">
         <v>14</v>
@@ -4503,21 +4552,21 @@
         <v>42</v>
       </c>
       <c r="O68">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4526,7 +4575,7 @@
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
         <v>12</v>
@@ -4543,25 +4592,22 @@
       <c r="L69" t="s">
         <v>14</v>
       </c>
-      <c r="M69" t="s">
-        <v>17</v>
-      </c>
       <c r="N69" t="s">
         <v>42</v>
       </c>
       <c r="O69">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
         <v>62</v>
@@ -4573,13 +4619,13 @@
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J70" t="s">
         <v>14</v>
@@ -4591,36 +4637,36 @@
         <v>14</v>
       </c>
       <c r="M70" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="N70" t="s">
         <v>42</v>
       </c>
       <c r="O70">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -4644,15 +4690,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D72" t="s">
         <v>41</v>
@@ -4661,7 +4707,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G72" t="s">
         <v>12</v>
@@ -4688,118 +4734,118 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73">
+        <v>255</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73" t="s">
+        <v>14</v>
+      </c>
+      <c r="K73" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" t="s">
+        <v>14</v>
+      </c>
+      <c r="N73" t="s">
+        <v>42</v>
+      </c>
+      <c r="O73">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74">
+        <v>20</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" t="s">
+        <v>14</v>
+      </c>
+      <c r="K74" t="s">
+        <v>14</v>
+      </c>
+      <c r="L74" t="s">
+        <v>14</v>
+      </c>
+      <c r="N74" t="s">
+        <v>42</v>
+      </c>
+      <c r="O74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" t="s">
         <v>120</v>
       </c>
-      <c r="C73" t="s">
-        <v>168</v>
-      </c>
-      <c r="D73" t="s">
-        <v>41</v>
-      </c>
-      <c r="E73">
+      <c r="C75" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75">
         <v>50</v>
       </c>
-      <c r="F73" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" t="s">
-        <v>12</v>
-      </c>
-      <c r="H73" t="s">
-        <v>12</v>
-      </c>
-      <c r="I73" t="s">
-        <v>12</v>
-      </c>
-      <c r="J73" t="s">
-        <v>14</v>
-      </c>
-      <c r="K73" t="s">
-        <v>14</v>
-      </c>
-      <c r="L73" t="s">
-        <v>14</v>
-      </c>
-      <c r="N73" t="s">
-        <v>42</v>
-      </c>
-      <c r="O73">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" t="s">
-        <v>133</v>
-      </c>
-      <c r="D74" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74">
-        <v>2000</v>
-      </c>
-      <c r="F74" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J74" t="s">
-        <v>14</v>
-      </c>
-      <c r="K74" t="s">
-        <v>14</v>
-      </c>
-      <c r="L74" t="s">
-        <v>14</v>
-      </c>
-      <c r="N74" t="s">
-        <v>42</v>
-      </c>
-      <c r="O74">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>102</v>
-      </c>
-      <c r="B75" t="s">
-        <v>134</v>
-      </c>
-      <c r="C75" t="s">
-        <v>135</v>
-      </c>
-      <c r="D75" t="s">
-        <v>41</v>
-      </c>
-      <c r="E75">
-        <v>2000</v>
-      </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I75" t="s">
         <v>12</v>
@@ -4817,30 +4863,30 @@
         <v>42</v>
       </c>
       <c r="O75">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="D76" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H76" t="s">
         <v>12</v>
@@ -4857,6 +4903,9 @@
       <c r="L76" t="s">
         <v>14</v>
       </c>
+      <c r="M76" t="s">
+        <v>25</v>
+      </c>
       <c r="N76" t="s">
         <v>42</v>
       </c>
@@ -4864,24 +4913,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
         <v>14</v>
@@ -4908,21 +4957,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4931,7 +4980,7 @@
         <v>14</v>
       </c>
       <c r="H78" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I78" t="s">
         <v>12</v>
@@ -4949,30 +4998,30 @@
         <v>42</v>
       </c>
       <c r="O78">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E79">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -4989,34 +5038,37 @@
       <c r="L79" t="s">
         <v>14</v>
       </c>
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
       <c r="N79" t="s">
         <v>42</v>
       </c>
       <c r="O79">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -5033,6 +5085,9 @@
       <c r="L80" t="s">
         <v>14</v>
       </c>
+      <c r="M80" t="s">
+        <v>167</v>
+      </c>
       <c r="N80" t="s">
         <v>42</v>
       </c>
@@ -5040,21 +5095,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="C81" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E81">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
@@ -5084,21 +5139,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
@@ -5121,9 +5176,6 @@
       <c r="L82" t="s">
         <v>14</v>
       </c>
-      <c r="M82" t="s">
-        <v>25</v>
-      </c>
       <c r="N82" t="s">
         <v>42</v>
       </c>
@@ -5131,27 +5183,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D83" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -5175,21 +5227,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>41</v>
       </c>
       <c r="E84">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
@@ -5219,341 +5271,335 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85">
+        <v>2000</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" t="s">
+        <v>12</v>
+      </c>
+      <c r="J85" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" t="s">
+        <v>14</v>
+      </c>
+      <c r="L85" t="s">
+        <v>14</v>
+      </c>
+      <c r="N85" t="s">
+        <v>42</v>
+      </c>
+      <c r="O85">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" t="s">
+        <v>136</v>
+      </c>
+      <c r="C86" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" t="s">
+        <v>72</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" t="s">
+        <v>14</v>
+      </c>
+      <c r="K86" t="s">
+        <v>14</v>
+      </c>
+      <c r="L86" t="s">
+        <v>14</v>
+      </c>
+      <c r="N86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" t="s">
+        <v>139</v>
+      </c>
+      <c r="D87" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" t="s">
+        <v>14</v>
+      </c>
+      <c r="K87" t="s">
+        <v>14</v>
+      </c>
+      <c r="L87" t="s">
+        <v>14</v>
+      </c>
+      <c r="N87" t="s">
+        <v>42</v>
+      </c>
+      <c r="O87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" t="s">
+        <v>140</v>
+      </c>
+      <c r="C88" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" t="s">
         <v>62</v>
       </c>
-      <c r="E85">
+      <c r="E88">
         <v>0</v>
       </c>
-      <c r="F85" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" t="s">
-        <v>14</v>
-      </c>
-      <c r="I85" t="s">
-        <v>14</v>
-      </c>
-      <c r="J85" t="s">
-        <v>14</v>
-      </c>
-      <c r="K85" t="s">
-        <v>14</v>
-      </c>
-      <c r="L85" t="s">
-        <v>14</v>
-      </c>
-      <c r="M85" t="s">
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" t="s">
+        <v>12</v>
+      </c>
+      <c r="J88" t="s">
+        <v>14</v>
+      </c>
+      <c r="K88" t="s">
+        <v>14</v>
+      </c>
+      <c r="L88" t="s">
+        <v>14</v>
+      </c>
+      <c r="N88" t="s">
+        <v>42</v>
+      </c>
+      <c r="O88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>102</v>
       </c>
-      <c r="N85" t="s">
-        <v>42</v>
-      </c>
-      <c r="O85">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>104</v>
-      </c>
-      <c r="B86" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" t="s">
-        <v>144</v>
-      </c>
-      <c r="D86" t="s">
-        <v>41</v>
-      </c>
-      <c r="E86">
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89">
         <v>50</v>
       </c>
-      <c r="F86" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" t="s">
-        <v>14</v>
-      </c>
-      <c r="H86" t="s">
-        <v>12</v>
-      </c>
-      <c r="I86" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" t="s">
-        <v>14</v>
-      </c>
-      <c r="K86" t="s">
-        <v>14</v>
-      </c>
-      <c r="L86" t="s">
-        <v>14</v>
-      </c>
-      <c r="N86" t="s">
-        <v>42</v>
-      </c>
-      <c r="O86">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>104</v>
-      </c>
-      <c r="B87" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" t="s">
-        <v>78</v>
-      </c>
-      <c r="D87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E87">
-        <v>20</v>
-      </c>
-      <c r="F87" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" t="s">
-        <v>12</v>
-      </c>
-      <c r="I87" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" t="s">
-        <v>14</v>
-      </c>
-      <c r="K87" t="s">
-        <v>14</v>
-      </c>
-      <c r="L87" t="s">
-        <v>14</v>
-      </c>
-      <c r="N87" t="s">
-        <v>42</v>
-      </c>
-      <c r="O87">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>104</v>
-      </c>
-      <c r="B88" t="s">
-        <v>145</v>
-      </c>
-      <c r="C88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D88" t="s">
-        <v>41</v>
-      </c>
-      <c r="E88">
-        <v>500</v>
-      </c>
-      <c r="F88" t="s">
-        <v>14</v>
-      </c>
-      <c r="G88" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" t="s">
-        <v>12</v>
-      </c>
-      <c r="I88" t="s">
-        <v>12</v>
-      </c>
-      <c r="J88" t="s">
-        <v>14</v>
-      </c>
-      <c r="K88" t="s">
-        <v>14</v>
-      </c>
-      <c r="L88" t="s">
-        <v>14</v>
-      </c>
-      <c r="N88" t="s">
-        <v>42</v>
-      </c>
-      <c r="O88">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>106</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>88</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89" t="s">
+        <v>14</v>
+      </c>
+      <c r="K89" t="s">
+        <v>14</v>
+      </c>
+      <c r="L89" t="s">
+        <v>14</v>
+      </c>
+      <c r="N89" t="s">
+        <v>42</v>
+      </c>
+      <c r="O89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>102</v>
+      </c>
+      <c r="B90" t="s">
+        <v>122</v>
+      </c>
+      <c r="C90" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90">
+        <v>50</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90" t="s">
+        <v>14</v>
+      </c>
+      <c r="K90" t="s">
+        <v>14</v>
+      </c>
+      <c r="L90" t="s">
+        <v>14</v>
+      </c>
+      <c r="N90" t="s">
+        <v>42</v>
+      </c>
+      <c r="O90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" t="s">
+        <v>80</v>
+      </c>
+      <c r="D91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91">
+        <v>100</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" t="s">
+        <v>14</v>
+      </c>
+      <c r="K91" t="s">
+        <v>14</v>
+      </c>
+      <c r="L91" t="s">
+        <v>14</v>
+      </c>
+      <c r="N91" t="s">
+        <v>42</v>
+      </c>
+      <c r="O91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" t="s">
+        <v>173</v>
+      </c>
+      <c r="C92" t="s">
+        <v>174</v>
+      </c>
+      <c r="D92" t="s">
         <v>62</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" t="s">
-        <v>14</v>
-      </c>
-      <c r="H89" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" t="s">
-        <v>14</v>
-      </c>
-      <c r="J89" t="s">
-        <v>14</v>
-      </c>
-      <c r="K89" t="s">
-        <v>14</v>
-      </c>
-      <c r="L89" t="s">
-        <v>14</v>
-      </c>
-      <c r="M89" t="s">
-        <v>17</v>
-      </c>
-      <c r="N89" t="s">
-        <v>42</v>
-      </c>
-      <c r="O89">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>106</v>
-      </c>
-      <c r="B90" t="s">
-        <v>39</v>
-      </c>
-      <c r="C90" t="s">
-        <v>146</v>
-      </c>
-      <c r="D90" t="s">
-        <v>41</v>
-      </c>
-      <c r="E90">
-        <v>255</v>
-      </c>
-      <c r="F90" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" t="s">
-        <v>12</v>
-      </c>
-      <c r="I90" t="s">
-        <v>12</v>
-      </c>
-      <c r="J90" t="s">
-        <v>14</v>
-      </c>
-      <c r="K90" t="s">
-        <v>14</v>
-      </c>
-      <c r="L90" t="s">
-        <v>14</v>
-      </c>
-      <c r="N90" t="s">
-        <v>42</v>
-      </c>
-      <c r="O90">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>106</v>
-      </c>
-      <c r="B91" t="s">
-        <v>65</v>
-      </c>
-      <c r="C91" t="s">
-        <v>147</v>
-      </c>
-      <c r="D91" t="s">
-        <v>67</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" t="s">
-        <v>12</v>
-      </c>
-      <c r="I91" t="s">
-        <v>12</v>
-      </c>
-      <c r="J91" t="s">
-        <v>14</v>
-      </c>
-      <c r="K91" t="s">
-        <v>14</v>
-      </c>
-      <c r="L91" t="s">
-        <v>14</v>
-      </c>
-      <c r="N91" t="s">
-        <v>42</v>
-      </c>
-      <c r="O91">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>106</v>
-      </c>
-      <c r="B92" t="s">
-        <v>68</v>
-      </c>
-      <c r="C92" t="s">
-        <v>148</v>
-      </c>
-      <c r="D92" t="s">
-        <v>67</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H92" t="s">
         <v>12</v>
@@ -5570,6 +5616,9 @@
       <c r="L92" t="s">
         <v>14</v>
       </c>
+      <c r="M92" t="s">
+        <v>25</v>
+      </c>
       <c r="N92" t="s">
         <v>42</v>
       </c>
@@ -5577,338 +5626,341 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" t="s">
+        <v>172</v>
+      </c>
+      <c r="D93" t="s">
+        <v>67</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>12</v>
+      </c>
+      <c r="J93" t="s">
+        <v>14</v>
+      </c>
+      <c r="K93" t="s">
+        <v>14</v>
+      </c>
+      <c r="L93" t="s">
+        <v>14</v>
+      </c>
+      <c r="N93" t="s">
+        <v>42</v>
+      </c>
+      <c r="O93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" t="s">
+        <v>170</v>
+      </c>
+      <c r="D94" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94">
+        <v>1000</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>14</v>
+      </c>
+      <c r="H94" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" t="s">
+        <v>14</v>
+      </c>
+      <c r="K94" t="s">
+        <v>14</v>
+      </c>
+      <c r="L94" t="s">
+        <v>14</v>
+      </c>
+      <c r="N94" t="s">
+        <v>42</v>
+      </c>
+      <c r="O94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>104</v>
+      </c>
+      <c r="B95" t="s">
+        <v>142</v>
+      </c>
+      <c r="C95" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" t="s">
+        <v>62</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>14</v>
+      </c>
+      <c r="H95" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" t="s">
+        <v>14</v>
+      </c>
+      <c r="J95" t="s">
+        <v>14</v>
+      </c>
+      <c r="K95" t="s">
+        <v>14</v>
+      </c>
+      <c r="L95" t="s">
+        <v>14</v>
+      </c>
+      <c r="M95" t="s">
+        <v>102</v>
+      </c>
+      <c r="N95" t="s">
+        <v>42</v>
+      </c>
+      <c r="O95">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s">
+        <v>144</v>
+      </c>
+      <c r="D96" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96">
+        <v>50</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" t="s">
+        <v>14</v>
+      </c>
+      <c r="K96" t="s">
+        <v>14</v>
+      </c>
+      <c r="L96" t="s">
+        <v>14</v>
+      </c>
+      <c r="N96" t="s">
+        <v>42</v>
+      </c>
+      <c r="O96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" t="s">
         <v>120</v>
       </c>
-      <c r="C93" t="s">
-        <v>149</v>
-      </c>
-      <c r="D93" t="s">
-        <v>41</v>
-      </c>
-      <c r="E93">
-        <v>50</v>
-      </c>
-      <c r="F93" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" t="s">
-        <v>12</v>
-      </c>
-      <c r="I93" t="s">
-        <v>12</v>
-      </c>
-      <c r="J93" t="s">
-        <v>14</v>
-      </c>
-      <c r="K93" t="s">
-        <v>14</v>
-      </c>
-      <c r="L93" t="s">
-        <v>14</v>
-      </c>
-      <c r="N93" t="s">
-        <v>42</v>
-      </c>
-      <c r="O93">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B94" t="s">
-        <v>87</v>
-      </c>
-      <c r="C94" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C97" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97">
+        <v>20</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>14</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" t="s">
+        <v>14</v>
+      </c>
+      <c r="L97" t="s">
+        <v>14</v>
+      </c>
+      <c r="N97" t="s">
+        <v>42</v>
+      </c>
+      <c r="O97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" t="s">
+        <v>145</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98">
+        <v>500</v>
+      </c>
+      <c r="F98" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" t="s">
+        <v>14</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" t="s">
+        <v>12</v>
+      </c>
+      <c r="J98" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" t="s">
+        <v>14</v>
+      </c>
+      <c r="L98" t="s">
+        <v>14</v>
+      </c>
+      <c r="N98" t="s">
+        <v>42</v>
+      </c>
+      <c r="O98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>142</v>
+      </c>
+      <c r="C99" t="s">
+        <v>143</v>
+      </c>
+      <c r="D99" t="s">
         <v>62</v>
       </c>
-      <c r="E94">
+      <c r="E99">
         <v>0</v>
       </c>
-      <c r="F94" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" t="s">
-        <v>14</v>
-      </c>
-      <c r="I94" t="s">
-        <v>14</v>
-      </c>
-      <c r="J94" t="s">
-        <v>14</v>
-      </c>
-      <c r="K94" t="s">
-        <v>14</v>
-      </c>
-      <c r="L94" t="s">
-        <v>14</v>
-      </c>
-      <c r="M94" t="s">
-        <v>17</v>
-      </c>
-      <c r="N94" t="s">
-        <v>42</v>
-      </c>
-      <c r="O94">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>108</v>
-      </c>
-      <c r="B95" t="s">
-        <v>150</v>
-      </c>
-      <c r="C95" t="s">
-        <v>151</v>
-      </c>
-      <c r="D95" t="s">
-        <v>41</v>
-      </c>
-      <c r="E95">
-        <v>20</v>
-      </c>
-      <c r="F95" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" t="s">
-        <v>12</v>
-      </c>
-      <c r="H95" t="s">
-        <v>12</v>
-      </c>
-      <c r="I95" t="s">
-        <v>12</v>
-      </c>
-      <c r="J95" t="s">
-        <v>14</v>
-      </c>
-      <c r="K95" t="s">
-        <v>14</v>
-      </c>
-      <c r="L95" t="s">
-        <v>14</v>
-      </c>
-      <c r="N95" t="s">
-        <v>42</v>
-      </c>
-      <c r="O95">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>108</v>
-      </c>
-      <c r="B96" t="s">
-        <v>152</v>
-      </c>
-      <c r="C96" t="s">
-        <v>153</v>
-      </c>
-      <c r="D96" t="s">
-        <v>41</v>
-      </c>
-      <c r="E96">
-        <v>20</v>
-      </c>
-      <c r="F96" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" t="s">
-        <v>12</v>
-      </c>
-      <c r="H96" t="s">
-        <v>12</v>
-      </c>
-      <c r="I96" t="s">
-        <v>12</v>
-      </c>
-      <c r="J96" t="s">
-        <v>14</v>
-      </c>
-      <c r="K96" t="s">
-        <v>14</v>
-      </c>
-      <c r="L96" t="s">
-        <v>14</v>
-      </c>
-      <c r="N96" t="s">
-        <v>42</v>
-      </c>
-      <c r="O96">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>108</v>
-      </c>
-      <c r="B97" t="s">
-        <v>154</v>
-      </c>
-      <c r="C97" t="s">
-        <v>155</v>
-      </c>
-      <c r="D97" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97">
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>14</v>
+      </c>
+      <c r="H99" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" t="s">
+        <v>14</v>
+      </c>
+      <c r="J99" t="s">
+        <v>14</v>
+      </c>
+      <c r="K99" t="s">
+        <v>14</v>
+      </c>
+      <c r="L99" t="s">
+        <v>14</v>
+      </c>
+      <c r="M99" t="s">
+        <v>102</v>
+      </c>
+      <c r="N99" t="s">
+        <v>42</v>
+      </c>
+      <c r="O99">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B100" t="s">
+        <v>39</v>
+      </c>
+      <c r="C100" t="s">
+        <v>146</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100">
         <v>255</v>
       </c>
-      <c r="F97" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" t="s">
-        <v>12</v>
-      </c>
-      <c r="H97" t="s">
-        <v>12</v>
-      </c>
-      <c r="I97" t="s">
-        <v>12</v>
-      </c>
-      <c r="J97" t="s">
-        <v>14</v>
-      </c>
-      <c r="K97" t="s">
-        <v>14</v>
-      </c>
-      <c r="L97" t="s">
-        <v>14</v>
-      </c>
-      <c r="N97" t="s">
-        <v>42</v>
-      </c>
-      <c r="O97">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>108</v>
-      </c>
-      <c r="B98" t="s">
-        <v>156</v>
-      </c>
-      <c r="C98" t="s">
-        <v>157</v>
-      </c>
-      <c r="D98" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98">
-        <v>20</v>
-      </c>
-      <c r="F98" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" t="s">
-        <v>12</v>
-      </c>
-      <c r="H98" t="s">
-        <v>12</v>
-      </c>
-      <c r="I98" t="s">
-        <v>12</v>
-      </c>
-      <c r="J98" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" t="s">
-        <v>14</v>
-      </c>
-      <c r="L98" t="s">
-        <v>14</v>
-      </c>
-      <c r="N98" t="s">
-        <v>42</v>
-      </c>
-      <c r="O98">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>108</v>
-      </c>
-      <c r="B99" t="s">
-        <v>120</v>
-      </c>
-      <c r="C99" t="s">
-        <v>158</v>
-      </c>
-      <c r="D99" t="s">
-        <v>41</v>
-      </c>
-      <c r="E99">
-        <v>50</v>
-      </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" t="s">
-        <v>12</v>
-      </c>
-      <c r="H99" t="s">
-        <v>12</v>
-      </c>
-      <c r="I99" t="s">
-        <v>12</v>
-      </c>
-      <c r="J99" t="s">
-        <v>14</v>
-      </c>
-      <c r="K99" t="s">
-        <v>14</v>
-      </c>
-      <c r="L99" t="s">
-        <v>14</v>
-      </c>
-      <c r="N99" t="s">
-        <v>42</v>
-      </c>
-      <c r="O99">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100" t="s">
-        <v>163</v>
-      </c>
-      <c r="C100" t="s">
-        <v>164</v>
-      </c>
-      <c r="D100" t="s">
-        <v>62</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -5925,25 +5977,22 @@
       <c r="L100" t="s">
         <v>14</v>
       </c>
-      <c r="M100" t="s">
-        <v>25</v>
-      </c>
       <c r="N100" t="s">
         <v>42</v>
       </c>
       <c r="O100">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="C101" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D101" t="s">
         <v>67</v>
@@ -5979,30 +6028,30 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="B102" t="s">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E102">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G102" t="s">
         <v>14</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I102" t="s">
         <v>12</v>
@@ -6020,30 +6069,30 @@
         <v>42</v>
       </c>
       <c r="O102">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B103" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="C103" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D103" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s">
         <v>12</v>
@@ -6067,15 +6116,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B104" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="C104" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="D104" t="s">
         <v>62</v>
@@ -6087,13 +6136,13 @@
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J104" t="s">
         <v>14</v>
@@ -6104,28 +6153,31 @@
       <c r="L104" t="s">
         <v>14</v>
       </c>
+      <c r="M104" t="s">
+        <v>102</v>
+      </c>
       <c r="N104" t="s">
         <v>42</v>
       </c>
       <c r="O104">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="C105" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D105" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
@@ -6155,21 +6207,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="D106" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
@@ -6199,153 +6251,150 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B107" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107">
+        <v>255</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" t="s">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J107" t="s">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s">
+        <v>14</v>
+      </c>
+      <c r="L107" t="s">
+        <v>14</v>
+      </c>
+      <c r="N107" t="s">
+        <v>42</v>
+      </c>
+      <c r="O107">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>184</v>
+      </c>
+      <c r="B108" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" t="s">
+        <v>157</v>
+      </c>
+      <c r="D108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108">
+        <v>20</v>
+      </c>
+      <c r="F108" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" t="s">
+        <v>12</v>
+      </c>
+      <c r="J108" t="s">
+        <v>14</v>
+      </c>
+      <c r="K108" t="s">
+        <v>14</v>
+      </c>
+      <c r="L108" t="s">
+        <v>14</v>
+      </c>
+      <c r="N108" t="s">
+        <v>42</v>
+      </c>
+      <c r="O108">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>184</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" t="s">
+        <v>158</v>
+      </c>
+      <c r="D109" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109">
+        <v>50</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s">
+        <v>14</v>
+      </c>
+      <c r="L109" t="s">
+        <v>14</v>
+      </c>
+      <c r="N109" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>184</v>
+      </c>
+      <c r="B110" t="s">
+        <v>163</v>
+      </c>
+      <c r="C110" t="s">
+        <v>164</v>
+      </c>
+      <c r="D110" t="s">
         <v>62</v>
-      </c>
-      <c r="E107">
-        <v>0</v>
-      </c>
-      <c r="F107" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" t="s">
-        <v>14</v>
-      </c>
-      <c r="H107" t="s">
-        <v>14</v>
-      </c>
-      <c r="I107" t="s">
-        <v>14</v>
-      </c>
-      <c r="J107" t="s">
-        <v>14</v>
-      </c>
-      <c r="K107" t="s">
-        <v>14</v>
-      </c>
-      <c r="L107" t="s">
-        <v>14</v>
-      </c>
-      <c r="M107" t="s">
-        <v>102</v>
-      </c>
-      <c r="N107" t="s">
-        <v>42</v>
-      </c>
-      <c r="O107">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>183</v>
-      </c>
-      <c r="B108" t="s">
-        <v>39</v>
-      </c>
-      <c r="C108" t="s">
-        <v>146</v>
-      </c>
-      <c r="D108" t="s">
-        <v>41</v>
-      </c>
-      <c r="E108">
-        <v>255</v>
-      </c>
-      <c r="F108" t="s">
-        <v>12</v>
-      </c>
-      <c r="G108" t="s">
-        <v>14</v>
-      </c>
-      <c r="H108" t="s">
-        <v>12</v>
-      </c>
-      <c r="I108" t="s">
-        <v>12</v>
-      </c>
-      <c r="J108" t="s">
-        <v>14</v>
-      </c>
-      <c r="K108" t="s">
-        <v>14</v>
-      </c>
-      <c r="L108" t="s">
-        <v>14</v>
-      </c>
-      <c r="N108" t="s">
-        <v>42</v>
-      </c>
-      <c r="O108">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>183</v>
-      </c>
-      <c r="B109" t="s">
-        <v>65</v>
-      </c>
-      <c r="C109" t="s">
-        <v>147</v>
-      </c>
-      <c r="D109" t="s">
-        <v>67</v>
-      </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-      <c r="F109" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" t="s">
-        <v>12</v>
-      </c>
-      <c r="J109" t="s">
-        <v>14</v>
-      </c>
-      <c r="K109" t="s">
-        <v>14</v>
-      </c>
-      <c r="L109" t="s">
-        <v>14</v>
-      </c>
-      <c r="N109" t="s">
-        <v>42</v>
-      </c>
-      <c r="O109">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>183</v>
-      </c>
-      <c r="B110" t="s">
-        <v>68</v>
-      </c>
-      <c r="C110" t="s">
-        <v>148</v>
-      </c>
-      <c r="D110" t="s">
-        <v>67</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6371,6 +6420,9 @@
       <c r="L110" t="s">
         <v>14</v>
       </c>
+      <c r="M110" t="s">
+        <v>25</v>
+      </c>
       <c r="N110" t="s">
         <v>42</v>
       </c>
@@ -6378,21 +6430,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="C111" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D111" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E111">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F111" t="s">
         <v>12</v>
@@ -6422,415 +6474,424 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>184</v>
       </c>
       <c r="B112" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C112" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D112" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112">
+        <v>1000</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" t="s">
+        <v>12</v>
+      </c>
+      <c r="J112" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" t="s">
+        <v>14</v>
+      </c>
+      <c r="L112" t="s">
+        <v>14</v>
+      </c>
+      <c r="N112" t="s">
+        <v>42</v>
+      </c>
+      <c r="O112">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E112">
+      <c r="E113" s="11">
         <v>0</v>
       </c>
-      <c r="F112" t="s">
-        <v>12</v>
-      </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
-        <v>14</v>
-      </c>
-      <c r="I112" t="s">
-        <v>14</v>
-      </c>
-      <c r="J112" t="s">
-        <v>14</v>
-      </c>
-      <c r="K112" t="s">
-        <v>14</v>
-      </c>
-      <c r="L112" t="s">
-        <v>14</v>
-      </c>
-      <c r="M112" t="s">
-        <v>102</v>
-      </c>
-      <c r="N112" t="s">
-        <v>42</v>
-      </c>
-      <c r="O112">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>184</v>
-      </c>
-      <c r="B113" t="s">
-        <v>150</v>
-      </c>
-      <c r="C113" t="s">
-        <v>151</v>
-      </c>
-      <c r="D113" t="s">
-        <v>41</v>
-      </c>
-      <c r="E113">
-        <v>20</v>
-      </c>
-      <c r="F113" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" t="s">
-        <v>12</v>
-      </c>
-      <c r="I113" t="s">
-        <v>12</v>
-      </c>
-      <c r="J113" t="s">
-        <v>14</v>
-      </c>
-      <c r="K113" t="s">
-        <v>14</v>
-      </c>
-      <c r="L113" t="s">
-        <v>14</v>
-      </c>
-      <c r="N113" t="s">
-        <v>42</v>
-      </c>
-      <c r="O113">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>184</v>
-      </c>
-      <c r="B114" t="s">
-        <v>152</v>
-      </c>
-      <c r="C114" t="s">
-        <v>153</v>
-      </c>
-      <c r="D114" t="s">
-        <v>41</v>
-      </c>
-      <c r="E114">
-        <v>20</v>
-      </c>
-      <c r="F114" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" t="s">
-        <v>12</v>
-      </c>
-      <c r="I114" t="s">
-        <v>12</v>
-      </c>
-      <c r="J114" t="s">
-        <v>14</v>
-      </c>
-      <c r="K114" t="s">
-        <v>14</v>
-      </c>
-      <c r="L114" t="s">
-        <v>14</v>
-      </c>
-      <c r="N114" t="s">
-        <v>42</v>
-      </c>
-      <c r="O114">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>184</v>
-      </c>
-      <c r="B115" t="s">
-        <v>154</v>
-      </c>
-      <c r="C115" t="s">
-        <v>155</v>
-      </c>
-      <c r="D115" t="s">
-        <v>41</v>
-      </c>
-      <c r="E115">
+      <c r="F113" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M113" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O113" s="11">
+        <v>12</v>
+      </c>
+      <c r="P113" s="12"/>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A114" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114" s="11">
         <v>255</v>
       </c>
-      <c r="F115" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" t="s">
-        <v>14</v>
-      </c>
-      <c r="H115" t="s">
-        <v>12</v>
-      </c>
-      <c r="I115" t="s">
-        <v>12</v>
-      </c>
-      <c r="J115" t="s">
-        <v>14</v>
-      </c>
-      <c r="K115" t="s">
-        <v>14</v>
-      </c>
-      <c r="L115" t="s">
-        <v>14</v>
-      </c>
-      <c r="N115" t="s">
-        <v>42</v>
-      </c>
-      <c r="O115">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>184</v>
-      </c>
-      <c r="B116" t="s">
-        <v>156</v>
-      </c>
-      <c r="C116" t="s">
-        <v>157</v>
-      </c>
-      <c r="D116" t="s">
-        <v>41</v>
-      </c>
-      <c r="E116">
-        <v>20</v>
-      </c>
-      <c r="F116" t="s">
-        <v>12</v>
-      </c>
-      <c r="G116" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" t="s">
-        <v>12</v>
-      </c>
-      <c r="I116" t="s">
-        <v>12</v>
-      </c>
-      <c r="J116" t="s">
-        <v>14</v>
-      </c>
-      <c r="K116" t="s">
-        <v>14</v>
-      </c>
-      <c r="L116" t="s">
-        <v>14</v>
-      </c>
-      <c r="N116" t="s">
-        <v>42</v>
-      </c>
-      <c r="O116">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="F114" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L114" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M114" t="s">
+        <v>25</v>
+      </c>
+      <c r="N114" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O114" s="11">
+        <v>6</v>
+      </c>
+      <c r="P114" s="12"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A115" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115" s="11">
+        <v>100</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L115" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M115" s="11"/>
+      <c r="N115" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O115" s="11">
+        <v>6</v>
+      </c>
+      <c r="P115" s="12"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A116" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" s="11">
+        <v>50</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M116" s="11"/>
+      <c r="N116" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O116" s="11">
+        <v>6</v>
+      </c>
+      <c r="P116" s="12"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C117" t="s">
-        <v>158</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>14</v>
+      </c>
+      <c r="H117" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" t="s">
+        <v>14</v>
+      </c>
+      <c r="J117" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" t="s">
+        <v>14</v>
+      </c>
+      <c r="L117" t="s">
+        <v>14</v>
+      </c>
+      <c r="M117" t="s">
+        <v>21</v>
+      </c>
+      <c r="N117" t="s">
+        <v>42</v>
+      </c>
+      <c r="O117">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>23</v>
+      </c>
+      <c r="B118" t="s">
+        <v>89</v>
+      </c>
+      <c r="C118" t="s">
+        <v>90</v>
+      </c>
+      <c r="D118" t="s">
+        <v>41</v>
+      </c>
+      <c r="E118">
+        <v>255</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" t="s">
+        <v>12</v>
+      </c>
+      <c r="J118" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" t="s">
+        <v>14</v>
+      </c>
+      <c r="L118" t="s">
+        <v>14</v>
+      </c>
+      <c r="N118" t="s">
+        <v>42</v>
+      </c>
+      <c r="O118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B119" t="s">
+        <v>91</v>
+      </c>
+      <c r="C119" t="s">
+        <v>92</v>
+      </c>
+      <c r="D119" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119">
+        <v>100</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" t="s">
+        <v>12</v>
+      </c>
+      <c r="J119" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s">
+        <v>14</v>
+      </c>
+      <c r="L119" t="s">
+        <v>14</v>
+      </c>
+      <c r="N119" t="s">
+        <v>42</v>
+      </c>
+      <c r="O119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E120" s="2">
         <v>50</v>
       </c>
-      <c r="F117" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" t="s">
-        <v>14</v>
-      </c>
-      <c r="H117" t="s">
-        <v>12</v>
-      </c>
-      <c r="I117" t="s">
-        <v>12</v>
-      </c>
-      <c r="J117" t="s">
-        <v>14</v>
-      </c>
-      <c r="K117" t="s">
-        <v>14</v>
-      </c>
-      <c r="L117" t="s">
-        <v>14</v>
-      </c>
-      <c r="N117" t="s">
-        <v>42</v>
-      </c>
-      <c r="O117">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>184</v>
-      </c>
-      <c r="B118" t="s">
-        <v>163</v>
-      </c>
-      <c r="C118" t="s">
-        <v>164</v>
-      </c>
-      <c r="D118" t="s">
-        <v>62</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
-        <v>12</v>
-      </c>
-      <c r="I118" t="s">
-        <v>12</v>
-      </c>
-      <c r="J118" t="s">
-        <v>14</v>
-      </c>
-      <c r="K118" t="s">
-        <v>14</v>
-      </c>
-      <c r="L118" t="s">
-        <v>14</v>
-      </c>
-      <c r="M118" t="s">
-        <v>25</v>
-      </c>
-      <c r="N118" t="s">
-        <v>42</v>
-      </c>
-      <c r="O118">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>184</v>
-      </c>
-      <c r="B119" t="s">
-        <v>159</v>
-      </c>
-      <c r="C119" t="s">
-        <v>160</v>
-      </c>
-      <c r="D119" t="s">
-        <v>67</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119" t="s">
-        <v>12</v>
-      </c>
-      <c r="I119" t="s">
-        <v>12</v>
-      </c>
-      <c r="J119" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" t="s">
-        <v>14</v>
-      </c>
-      <c r="L119" t="s">
-        <v>14</v>
-      </c>
-      <c r="N119" t="s">
-        <v>42</v>
-      </c>
-      <c r="O119">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>184</v>
-      </c>
-      <c r="B120" t="s">
-        <v>161</v>
-      </c>
-      <c r="C120" t="s">
-        <v>162</v>
-      </c>
-      <c r="D120" t="s">
-        <v>41</v>
-      </c>
-      <c r="E120">
-        <v>1000</v>
-      </c>
-      <c r="F120" t="s">
-        <v>14</v>
-      </c>
-      <c r="G120" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" t="s">
-        <v>14</v>
-      </c>
-      <c r="I120" t="s">
-        <v>12</v>
-      </c>
-      <c r="J120" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" t="s">
-        <v>14</v>
-      </c>
-      <c r="L120" t="s">
-        <v>14</v>
-      </c>
-      <c r="N120" t="s">
-        <v>42</v>
-      </c>
-      <c r="O120">
-        <v>12</v>
-      </c>
+      <c r="F120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M120" s="2"/>
+      <c r="N120" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O120" s="2">
+        <v>6</v>
+      </c>
+      <c r="P120" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P120" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Project"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P120">
+      <sortCondition ref="A1:A120"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1899" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9A6566C-AA1E-448A-A403-ACB0F454881B}"/>
+  <xr:revisionPtr revIDLastSave="1912" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF836984-39AF-49C5-B2C3-113B9CB997B0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,9 +329,6 @@
     <t>User Id</t>
   </si>
   <si>
-    <t>Sub-detail / list</t>
-  </si>
-  <si>
     <t>StatusReport</t>
   </si>
   <si>
@@ -624,6 +621,9 @@
   </si>
   <si>
     <t>EmployeeId</t>
+  </si>
+  <si>
+    <t>Sub-detail list</t>
   </si>
 </sst>
 </file>
@@ -703,7 +703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -717,9 +717,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1170,7 +1169,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>199</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -1216,7 +1215,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>199</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
@@ -1261,16 +1260,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
         <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>103</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1281,16 +1280,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
         <v>104</v>
-      </c>
-      <c r="B10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>105</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1301,16 +1300,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
         <v>106</v>
-      </c>
-      <c r="B11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>107</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -1321,16 +1320,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
         <v>108</v>
-      </c>
-      <c r="B12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>109</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1341,16 +1340,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1361,16 +1360,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B14" t="s">
-        <v>101</v>
+        <v>182</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -1381,16 +1380,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
+        <v>183</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -2214,7 +2213,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>87</v>
@@ -2223,7 +2222,7 @@
         <v>88</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -2262,13 +2261,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>41</v>
@@ -2308,13 +2307,13 @@
     </row>
     <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>67</v>
@@ -2354,13 +2353,13 @@
     </row>
     <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>67</v>
@@ -2400,13 +2399,13 @@
     </row>
     <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>41</v>
@@ -2501,7 +2500,7 @@
         <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
@@ -2589,10 +2588,10 @@
         <v>17</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>67</v>
@@ -2635,10 +2634,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>67</v>
@@ -2681,10 +2680,10 @@
         <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>72</v>
@@ -2779,7 +2778,7 @@
         <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -3005,10 +3004,10 @@
         <v>17</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>41</v>
@@ -3051,10 +3050,10 @@
         <v>17</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>41</v>
@@ -3097,10 +3096,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>41</v>
@@ -3143,16 +3142,16 @@
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>14</v>
@@ -3191,13 +3190,13 @@
         <v>17</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -3239,10 +3238,10 @@
         <v>17</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>41</v>
@@ -3285,10 +3284,10 @@
         <v>17</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>41</v>
@@ -3331,13 +3330,13 @@
         <v>17</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -3377,10 +3376,10 @@
         <v>17</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>57</v>
@@ -3429,7 +3428,7 @@
         <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -3523,7 +3522,7 @@
         <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -3699,384 +3698,377 @@
       <c r="P49" s="3"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A50" s="11" t="s">
+      <c r="A50" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" t="s">
         <v>71</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" t="s">
         <v>72</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50">
         <v>0</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O50" s="11">
-        <v>12</v>
-      </c>
-      <c r="P50" s="12"/>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" t="s">
+        <v>42</v>
+      </c>
+      <c r="O50">
+        <v>12</v>
+      </c>
+      <c r="P50" s="11"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
+      <c r="A51" t="s">
         <v>21</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51" s="11">
+      <c r="D51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51">
         <v>1000</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O51" s="11">
-        <v>12</v>
-      </c>
-      <c r="P51" s="12"/>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" t="s">
+        <v>14</v>
+      </c>
+      <c r="N51" t="s">
+        <v>42</v>
+      </c>
+      <c r="O51">
+        <v>12</v>
+      </c>
+      <c r="P51" s="11"/>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52" s="11" t="s">
+      <c r="A52" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="11">
+      <c r="D52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52">
         <v>0</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L52" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M52" s="11" t="s">
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" t="s">
         <v>25</v>
       </c>
-      <c r="N52" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O52" s="11">
-        <v>12</v>
-      </c>
-      <c r="P52" s="12"/>
+      <c r="N52" t="s">
+        <v>42</v>
+      </c>
+      <c r="O52">
+        <v>12</v>
+      </c>
+      <c r="P52" s="11"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" s="11" t="s">
+      <c r="A53" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" t="s">
         <v>78</v>
       </c>
-      <c r="D53" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="11">
+      <c r="D53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O53" s="11">
-        <v>6</v>
-      </c>
-      <c r="P53" s="12"/>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" t="s">
+        <v>14</v>
+      </c>
+      <c r="N53" t="s">
+        <v>42</v>
+      </c>
+      <c r="O53">
+        <v>6</v>
+      </c>
+      <c r="P53" s="11"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54" s="11" t="s">
+      <c r="A54" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" s="11">
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O54" s="11">
-        <v>6</v>
-      </c>
-      <c r="P54" s="12"/>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" t="s">
+        <v>14</v>
+      </c>
+      <c r="N54" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54">
+        <v>6</v>
+      </c>
+      <c r="P54" s="11"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55" s="11" t="s">
+      <c r="A55" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" t="s">
         <v>82</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55" s="11">
+      <c r="D55" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55">
         <v>50</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O55" s="11">
-        <v>6</v>
-      </c>
-      <c r="P55" s="12"/>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
+        <v>14</v>
+      </c>
+      <c r="N55" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55">
+        <v>6</v>
+      </c>
+      <c r="P55" s="11"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56" s="11" t="s">
+      <c r="A56" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" t="s">
         <v>84</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56">
         <v>0</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56" s="11">
-        <v>6</v>
-      </c>
-      <c r="P56" s="12"/>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" t="s">
+        <v>14</v>
+      </c>
+      <c r="N56" t="s">
+        <v>42</v>
+      </c>
+      <c r="O56">
+        <v>6</v>
+      </c>
+      <c r="P56" s="11"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A57" s="11" t="s">
+      <c r="A57" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E57">
         <v>0</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O57" s="11">
-        <v>6</v>
-      </c>
-      <c r="P57" s="12"/>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" t="s">
+        <v>14</v>
+      </c>
+      <c r="N57" t="s">
+        <v>42</v>
+      </c>
+      <c r="O57">
+        <v>6</v>
+      </c>
+      <c r="P57" s="11"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>21</v>
       </c>
       <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" t="s">
-        <v>111</v>
       </c>
       <c r="D58" t="s">
         <v>41</v>
@@ -4117,10 +4109,10 @@
         <v>21</v>
       </c>
       <c r="B59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
       </c>
       <c r="D59" t="s">
         <v>41</v>
@@ -4161,10 +4153,10 @@
         <v>21</v>
       </c>
       <c r="B60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" t="s">
-        <v>115</v>
       </c>
       <c r="D60" t="s">
         <v>41</v>
@@ -4205,10 +4197,10 @@
         <v>21</v>
       </c>
       <c r="B61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" t="s">
-        <v>117</v>
       </c>
       <c r="D61" t="s">
         <v>41</v>
@@ -4249,13 +4241,13 @@
         <v>21</v>
       </c>
       <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" t="s">
         <v>118</v>
       </c>
-      <c r="C62" t="s">
-        <v>119</v>
-      </c>
-      <c r="D62" t="s">
-        <v>62</v>
+      <c r="D62" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4296,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" t="s">
         <v>120</v>
-      </c>
-      <c r="C63" t="s">
-        <v>121</v>
       </c>
       <c r="D63" t="s">
         <v>41</v>
@@ -4340,10 +4332,10 @@
         <v>21</v>
       </c>
       <c r="B64" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" t="s">
         <v>122</v>
-      </c>
-      <c r="C64" t="s">
-        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>41</v>
@@ -4384,10 +4376,10 @@
         <v>21</v>
       </c>
       <c r="B65" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" t="s">
         <v>124</v>
-      </c>
-      <c r="C65" t="s">
-        <v>125</v>
       </c>
       <c r="D65" t="s">
         <v>41</v>
@@ -4425,13 +4417,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" t="s">
         <v>176</v>
-      </c>
-      <c r="C66" t="s">
-        <v>177</v>
       </c>
       <c r="D66" t="s">
         <v>62</v>
@@ -4469,13 +4461,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" t="s">
+        <v>177</v>
+      </c>
+      <c r="C67" t="s">
         <v>178</v>
-      </c>
-      <c r="C67" t="s">
-        <v>179</v>
       </c>
       <c r="D67" t="s">
         <v>62</v>
@@ -4513,13 +4505,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B68" t="s">
         <v>65</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D68" t="s">
         <v>67</v>
@@ -4557,13 +4549,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B69" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" t="s">
         <v>181</v>
-      </c>
-      <c r="C69" t="s">
-        <v>182</v>
       </c>
       <c r="D69" t="s">
         <v>67</v>
@@ -4601,7 +4593,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" t="s">
         <v>87</v>
@@ -4609,8 +4601,8 @@
       <c r="C70" t="s">
         <v>88</v>
       </c>
-      <c r="D70" t="s">
-        <v>62</v>
+      <c r="D70" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4648,13 +4640,13 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" t="s">
         <v>150</v>
-      </c>
-      <c r="C71" t="s">
-        <v>151</v>
       </c>
       <c r="D71" t="s">
         <v>41</v>
@@ -4692,13 +4684,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" t="s">
         <v>152</v>
-      </c>
-      <c r="C72" t="s">
-        <v>153</v>
       </c>
       <c r="D72" t="s">
         <v>41</v>
@@ -4736,13 +4728,13 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C73" t="s">
         <v>154</v>
-      </c>
-      <c r="C73" t="s">
-        <v>155</v>
       </c>
       <c r="D73" t="s">
         <v>41</v>
@@ -4780,13 +4772,13 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
         <v>156</v>
-      </c>
-      <c r="C74" t="s">
-        <v>157</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
@@ -4824,13 +4816,13 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D75" t="s">
         <v>41</v>
@@ -4868,16 +4860,16 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" t="s">
         <v>163</v>
       </c>
-      <c r="C76" t="s">
-        <v>164</v>
-      </c>
-      <c r="D76" t="s">
-        <v>62</v>
+      <c r="D76" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4915,13 +4907,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" t="s">
         <v>159</v>
-      </c>
-      <c r="C77" t="s">
-        <v>160</v>
       </c>
       <c r="D77" t="s">
         <v>67</v>
@@ -4959,13 +4951,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" t="s">
         <v>161</v>
-      </c>
-      <c r="C78" t="s">
-        <v>162</v>
       </c>
       <c r="D78" t="s">
         <v>41</v>
@@ -5003,7 +4995,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
         <v>87</v>
@@ -5011,8 +5003,8 @@
       <c r="C79" t="s">
         <v>88</v>
       </c>
-      <c r="D79" t="s">
-        <v>62</v>
+      <c r="D79" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5050,16 +5042,16 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" t="s">
         <v>165</v>
       </c>
-      <c r="C80" t="s">
-        <v>166</v>
-      </c>
-      <c r="D80" t="s">
-        <v>62</v>
+      <c r="D80" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5086,7 +5078,7 @@
         <v>14</v>
       </c>
       <c r="M80" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N80" t="s">
         <v>42</v>
@@ -5097,13 +5089,13 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81" t="s">
+        <v>127</v>
+      </c>
+      <c r="C81" t="s">
         <v>128</v>
-      </c>
-      <c r="C81" t="s">
-        <v>129</v>
       </c>
       <c r="D81" t="s">
         <v>67</v>
@@ -5141,13 +5133,13 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" t="s">
         <v>130</v>
-      </c>
-      <c r="C82" t="s">
-        <v>131</v>
       </c>
       <c r="D82" t="s">
         <v>41</v>
@@ -5185,13 +5177,13 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D83" t="s">
         <v>41</v>
@@ -5229,13 +5221,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B84" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" t="s">
         <v>132</v>
-      </c>
-      <c r="C84" t="s">
-        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>41</v>
@@ -5273,13 +5265,13 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B85" t="s">
+        <v>133</v>
+      </c>
+      <c r="C85" t="s">
         <v>134</v>
-      </c>
-      <c r="C85" t="s">
-        <v>135</v>
       </c>
       <c r="D85" t="s">
         <v>41</v>
@@ -5317,13 +5309,13 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B86" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" t="s">
         <v>136</v>
-      </c>
-      <c r="C86" t="s">
-        <v>137</v>
       </c>
       <c r="D86" t="s">
         <v>72</v>
@@ -5361,13 +5353,13 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
+        <v>137</v>
+      </c>
+      <c r="C87" t="s">
         <v>138</v>
-      </c>
-      <c r="C87" t="s">
-        <v>139</v>
       </c>
       <c r="D87" t="s">
         <v>72</v>
@@ -5405,13 +5397,13 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B88" t="s">
+        <v>139</v>
+      </c>
+      <c r="C88" t="s">
         <v>140</v>
-      </c>
-      <c r="C88" t="s">
-        <v>141</v>
       </c>
       <c r="D88" t="s">
         <v>62</v>
@@ -5449,13 +5441,13 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B89" t="s">
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D89" t="s">
         <v>41</v>
@@ -5493,13 +5485,13 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
+        <v>121</v>
+      </c>
+      <c r="C90" t="s">
         <v>122</v>
-      </c>
-      <c r="C90" t="s">
-        <v>123</v>
       </c>
       <c r="D90" t="s">
         <v>41</v>
@@ -5537,7 +5529,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
         <v>79</v>
@@ -5581,16 +5573,16 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B92" t="s">
+        <v>172</v>
+      </c>
+      <c r="C92" t="s">
         <v>173</v>
       </c>
-      <c r="C92" t="s">
-        <v>174</v>
-      </c>
-      <c r="D92" t="s">
-        <v>62</v>
+      <c r="D92" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5628,13 +5620,13 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" t="s">
         <v>171</v>
-      </c>
-      <c r="C93" t="s">
-        <v>172</v>
       </c>
       <c r="D93" t="s">
         <v>67</v>
@@ -5672,13 +5664,13 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94" t="s">
+        <v>168</v>
+      </c>
+      <c r="C94" t="s">
         <v>169</v>
-      </c>
-      <c r="C94" t="s">
-        <v>170</v>
       </c>
       <c r="D94" t="s">
         <v>41</v>
@@ -5716,16 +5708,16 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B95" t="s">
+        <v>141</v>
+      </c>
+      <c r="C95" t="s">
         <v>142</v>
       </c>
-      <c r="C95" t="s">
-        <v>143</v>
-      </c>
-      <c r="D95" t="s">
-        <v>62</v>
+      <c r="D95" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5752,7 +5744,7 @@
         <v>14</v>
       </c>
       <c r="M95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N95" t="s">
         <v>42</v>
@@ -5763,13 +5755,13 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s">
         <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
         <v>41</v>
@@ -5807,10 +5799,10 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C97" t="s">
         <v>78</v>
@@ -5851,13 +5843,13 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
         <v>41</v>
@@ -5895,16 +5887,16 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B99" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" t="s">
         <v>142</v>
       </c>
-      <c r="C99" t="s">
-        <v>143</v>
-      </c>
-      <c r="D99" t="s">
-        <v>62</v>
+      <c r="D99" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5931,7 +5923,7 @@
         <v>14</v>
       </c>
       <c r="M99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N99" t="s">
         <v>42</v>
@@ -5942,13 +5934,13 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B100" t="s">
         <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s">
         <v>41</v>
@@ -5986,13 +5978,13 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B101" t="s">
         <v>65</v>
       </c>
       <c r="C101" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
         <v>67</v>
@@ -6030,13 +6022,13 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
         <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D102" t="s">
         <v>67</v>
@@ -6074,13 +6066,13 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B103" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C103" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D103" t="s">
         <v>41</v>
@@ -6118,16 +6110,16 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B104" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" t="s">
         <v>142</v>
       </c>
-      <c r="C104" t="s">
-        <v>143</v>
-      </c>
-      <c r="D104" t="s">
-        <v>62</v>
+      <c r="D104" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6154,7 +6146,7 @@
         <v>14</v>
       </c>
       <c r="M104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N104" t="s">
         <v>42</v>
@@ -6165,13 +6157,13 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
+        <v>149</v>
+      </c>
+      <c r="C105" t="s">
         <v>150</v>
-      </c>
-      <c r="C105" t="s">
-        <v>151</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -6209,13 +6201,13 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B106" t="s">
+        <v>151</v>
+      </c>
+      <c r="C106" t="s">
         <v>152</v>
-      </c>
-      <c r="C106" t="s">
-        <v>153</v>
       </c>
       <c r="D106" t="s">
         <v>41</v>
@@ -6253,13 +6245,13 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B107" t="s">
+        <v>153</v>
+      </c>
+      <c r="C107" t="s">
         <v>154</v>
-      </c>
-      <c r="C107" t="s">
-        <v>155</v>
       </c>
       <c r="D107" t="s">
         <v>41</v>
@@ -6297,13 +6289,13 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B108" t="s">
+        <v>155</v>
+      </c>
+      <c r="C108" t="s">
         <v>156</v>
-      </c>
-      <c r="C108" t="s">
-        <v>157</v>
       </c>
       <c r="D108" t="s">
         <v>41</v>
@@ -6341,13 +6333,13 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C109" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D109" t="s">
         <v>41</v>
@@ -6385,16 +6377,16 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B110" t="s">
+        <v>162</v>
+      </c>
+      <c r="C110" t="s">
         <v>163</v>
       </c>
-      <c r="C110" t="s">
-        <v>164</v>
-      </c>
-      <c r="D110" t="s">
-        <v>62</v>
+      <c r="D110" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6432,13 +6424,13 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B111" t="s">
+        <v>158</v>
+      </c>
+      <c r="C111" t="s">
         <v>159</v>
-      </c>
-      <c r="C111" t="s">
-        <v>160</v>
       </c>
       <c r="D111" t="s">
         <v>67</v>
@@ -6476,13 +6468,13 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B112" t="s">
+        <v>160</v>
+      </c>
+      <c r="C112" t="s">
         <v>161</v>
-      </c>
-      <c r="C112" t="s">
-        <v>162</v>
       </c>
       <c r="D112" t="s">
         <v>41</v>
@@ -6519,192 +6511,190 @@
       </c>
     </row>
     <row r="113" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="11" t="s">
+      <c r="A113" t="s">
         <v>18</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" t="s">
         <v>87</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" t="s">
         <v>88</v>
       </c>
-      <c r="D113" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E113" s="11">
+      <c r="D113" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E113">
         <v>0</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M113" s="11" t="s">
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" t="s">
+        <v>14</v>
+      </c>
+      <c r="H113" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" t="s">
+        <v>14</v>
+      </c>
+      <c r="J113" t="s">
+        <v>14</v>
+      </c>
+      <c r="K113" t="s">
+        <v>14</v>
+      </c>
+      <c r="L113" t="s">
+        <v>14</v>
+      </c>
+      <c r="M113" t="s">
         <v>17</v>
       </c>
-      <c r="N113" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O113" s="11">
-        <v>12</v>
-      </c>
-      <c r="P113" s="12"/>
+      <c r="N113" t="s">
+        <v>42</v>
+      </c>
+      <c r="O113">
+        <v>12</v>
+      </c>
+      <c r="P113" s="11"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A114" s="11" t="s">
+      <c r="A114" t="s">
         <v>18</v>
       </c>
-      <c r="B114" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C114" s="11" t="s">
+      <c r="B114" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C114" t="s">
         <v>90</v>
       </c>
-      <c r="D114" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E114" s="11">
-        <v>255</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I114" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K114" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L114" s="11" t="s">
+      <c r="D114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" t="s">
+        <v>12</v>
+      </c>
+      <c r="J114" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" t="s">
+        <v>14</v>
+      </c>
+      <c r="L114" t="s">
         <v>14</v>
       </c>
       <c r="M114" t="s">
         <v>25</v>
       </c>
-      <c r="N114" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O114" s="11">
-        <v>6</v>
-      </c>
-      <c r="P114" s="12"/>
+      <c r="N114" t="s">
+        <v>42</v>
+      </c>
+      <c r="O114">
+        <v>6</v>
+      </c>
+      <c r="P114" s="11"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A115" s="11" t="s">
+      <c r="A115" t="s">
         <v>18</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" t="s">
         <v>91</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" t="s">
         <v>92</v>
       </c>
-      <c r="D115" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E115" s="11">
+      <c r="D115" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115">
         <v>100</v>
       </c>
-      <c r="F115" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H115" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I115" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J115" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K115" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L115" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M115" s="11"/>
-      <c r="N115" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O115" s="11">
-        <v>6</v>
-      </c>
-      <c r="P115" s="12"/>
+      <c r="F115" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" t="s">
+        <v>12</v>
+      </c>
+      <c r="J115" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" t="s">
+        <v>14</v>
+      </c>
+      <c r="L115" t="s">
+        <v>14</v>
+      </c>
+      <c r="N115" t="s">
+        <v>42</v>
+      </c>
+      <c r="O115">
+        <v>6</v>
+      </c>
+      <c r="P115" s="11"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A116" s="11" t="s">
+      <c r="A116" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C116" t="s">
         <v>126</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E116" s="11">
+      <c r="D116" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116">
         <v>50</v>
       </c>
-      <c r="F116" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G116" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I116" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J116" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K116" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L116" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M116" s="11"/>
-      <c r="N116" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O116" s="11">
-        <v>6</v>
-      </c>
-      <c r="P116" s="12"/>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" t="s">
+        <v>12</v>
+      </c>
+      <c r="J116" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" t="s">
+        <v>14</v>
+      </c>
+      <c r="L116" t="s">
+        <v>14</v>
+      </c>
+      <c r="N116" t="s">
+        <v>42</v>
+      </c>
+      <c r="O116">
+        <v>6</v>
+      </c>
+      <c r="P116" s="11"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
@@ -6716,8 +6706,8 @@
       <c r="C117" t="s">
         <v>17</v>
       </c>
-      <c r="D117" t="s">
-        <v>62</v>
+      <c r="D117" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6846,10 +6836,10 @@
         <v>23</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>41</v>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1912" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF836984-39AF-49C5-B2C3-113B9CB997B0}"/>
+  <xr:revisionPtr revIDLastSave="1930" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D5D307-77B7-41F8-8391-445C601D9DD3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Column" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$109</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="186">
   <si>
     <t>Table Name</t>
   </si>
@@ -224,24 +224,12 @@
     <t>StartDate</t>
   </si>
   <si>
-    <t>Project Start Date</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
     <t>TargetEndDate</t>
   </si>
   <si>
-    <t>Target Completion Date</t>
-  </si>
-  <si>
-    <t>EstimatedBudget</t>
-  </si>
-  <si>
-    <t>Estimated Budget in Currency</t>
-  </si>
-  <si>
     <t>Decimal</t>
   </si>
   <si>
@@ -257,9 +245,6 @@
     <t>Assigned Project Manager</t>
   </si>
   <si>
-    <t>HealthStatus</t>
-  </si>
-  <si>
     <t>RAG Status (Red, Amber, Green)</t>
   </si>
   <si>
@@ -272,30 +257,12 @@
     <t>ScheduleStatus</t>
   </si>
   <si>
-    <t>Schedule Status (e.g. Delayed)</t>
-  </si>
-  <si>
-    <t>LastReviewDate</t>
-  </si>
-  <si>
-    <t>Date of Last Review</t>
-  </si>
-  <si>
-    <t>LastUpdatedDate</t>
-  </si>
-  <si>
-    <t>Date of Last Update</t>
-  </si>
-  <si>
     <t>ProjectId</t>
   </si>
   <si>
     <t>Reference to Project</t>
   </si>
   <si>
-    <t>MemberName</t>
-  </si>
-  <si>
     <t>Full Name of the Member</t>
   </si>
   <si>
@@ -371,9 +338,6 @@
     <t>Demand Type (e.g. AI Solution, Data &amp; Analytics)</t>
   </si>
   <si>
-    <t>TechnologyBusinessPartner</t>
-  </si>
-  <si>
     <t>Technology Business Partner (Auto-assigned from BU)</t>
   </si>
   <si>
@@ -429,12 +393,6 @@
   </si>
   <si>
     <t>Next Steps</t>
-  </si>
-  <si>
-    <t>BaselineBudget</t>
-  </si>
-  <si>
-    <t>Baseline Budget in Currency</t>
   </si>
   <si>
     <t>ActualSpend</t>
@@ -703,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -711,10 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1169,7 +1124,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -1215,7 +1170,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
@@ -1260,16 +1215,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1280,16 +1235,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1300,16 +1255,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -1320,16 +1275,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1340,16 +1295,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1360,16 +1315,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -1380,16 +1335,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -1405,12 +1360,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="50.08984375" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" customWidth="1"/>
     <col min="5" max="5" width="12.1796875" customWidth="1"/>
     <col min="6" max="6" width="11.453125" customWidth="1"/>
@@ -1940,10 +1895,10 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>41</v>
@@ -1986,10 +1941,10 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>41</v>
@@ -2032,10 +1987,10 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>41</v>
@@ -2124,10 +2079,10 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>41</v>
@@ -2170,10 +2125,10 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>41</v>
@@ -2213,13 +2168,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>41</v>
@@ -2261,13 +2216,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>41</v>
@@ -2305,18 +2260,18 @@
       </c>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -2351,18 +2306,18 @@
       </c>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -2397,15 +2352,15 @@
       </c>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>41</v>
@@ -2443,7 +2398,7 @@
       </c>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -2588,13 +2543,13 @@
         <v>17</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -2634,13 +2589,13 @@
         <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
@@ -2680,13 +2635,13 @@
         <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2726,10 +2681,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>41</v>
@@ -2767,15 +2722,15 @@
       </c>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>41</v>
@@ -2816,207 +2771,209 @@
       <c r="P30" s="3"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="B31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O31" s="2">
+        <v>6</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O31" s="5">
+      <c r="C32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="2">
+        <v>50</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O32" s="2">
         <v>6</v>
       </c>
-      <c r="P31" s="5"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="5">
-        <v>50</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O32" s="5">
+      <c r="B33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2">
+        <v>100</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O33" s="2">
         <v>6</v>
       </c>
-      <c r="P32" s="5"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="B34" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2">
         <v>0</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O33" s="5">
+      <c r="F34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O34" s="2">
         <v>6</v>
       </c>
-      <c r="P33" s="5"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O34" s="5">
-        <v>6</v>
-      </c>
-      <c r="P34" s="5"/>
+      <c r="P34" s="3"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>12</v>
@@ -3028,7 +2985,7 @@
         <v>12</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>14</v>
@@ -3036,7 +2993,9 @@
       <c r="L35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N35" s="2" t="s">
         <v>42</v>
       </c>
@@ -3049,11 +3008,11 @@
       <c r="A36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>111</v>
+      <c r="B36" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>41</v>
@@ -3062,7 +3021,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>12</v>
@@ -3096,25 +3055,25 @@
         <v>17</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="E37" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>12</v>
@@ -3133,7 +3092,7 @@
         <v>42</v>
       </c>
       <c r="O37" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P37" s="3"/>
     </row>
@@ -3142,13 +3101,13 @@
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -3160,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>12</v>
@@ -3169,31 +3128,29 @@
         <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M38" s="2"/>
       <c r="N38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O38" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P38" s="3"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>41</v>
@@ -3202,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>14</v>
@@ -3223,34 +3180,34 @@
         <v>14</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O39" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>197</v>
+        <v>21</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="2">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>12</v>
@@ -3275,80 +3232,82 @@
         <v>42</v>
       </c>
       <c r="O40" s="2">
+        <v>12</v>
+      </c>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O41" s="2">
         <v>6</v>
       </c>
-      <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E41" s="7">
-        <v>50</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O41" s="7">
-        <v>6</v>
-      </c>
-      <c r="P41" s="8"/>
+      <c r="P41" s="3"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>194</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>12</v>
@@ -3367,34 +3326,34 @@
         <v>42</v>
       </c>
       <c r="O42" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P42" s="3"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>12</v>
@@ -3413,7 +3372,7 @@
         <v>42</v>
       </c>
       <c r="O43" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P43" s="3"/>
     </row>
@@ -3421,14 +3380,14 @@
       <c r="A44" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>87</v>
+      <c r="B44" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -3440,10 +3399,10 @@
         <v>14</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>14</v>
@@ -3454,14 +3413,12 @@
       <c r="L44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="M44" s="2"/>
       <c r="N44" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O44" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P44" s="3"/>
     </row>
@@ -3469,23 +3426,23 @@
       <c r="A45" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>58</v>
+      <c r="B45" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>12</v>
@@ -3515,26 +3472,26 @@
       <c r="A46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>60</v>
+      <c r="B46" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E46" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>12</v>
@@ -3548,32 +3505,30 @@
       <c r="L46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M46" s="2"/>
       <c r="N46" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O46" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>63</v>
+      <c r="B47" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>12</v>
@@ -3596,12 +3551,14 @@
       <c r="L47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M47" s="2"/>
+      <c r="M47" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N47" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O47" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P47" s="3"/>
     </row>
@@ -3609,23 +3566,23 @@
       <c r="A48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>65</v>
+      <c r="B48" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>12</v>
@@ -3634,7 +3591,7 @@
         <v>12</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>14</v>
@@ -3655,23 +3612,23 @@
       <c r="A49" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>68</v>
+      <c r="B49" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E49" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>12</v>
@@ -3698,299 +3655,306 @@
       <c r="P49" s="3"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" t="s">
-        <v>71</v>
-      </c>
-      <c r="D50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50">
+      <c r="B50" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="2">
+        <v>100</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O50" s="2">
+        <v>6</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="2">
         <v>0</v>
       </c>
-      <c r="F50" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" t="s">
-        <v>12</v>
-      </c>
-      <c r="I50" t="s">
-        <v>12</v>
-      </c>
-      <c r="J50" t="s">
-        <v>14</v>
-      </c>
-      <c r="K50" t="s">
-        <v>14</v>
-      </c>
-      <c r="L50" t="s">
-        <v>14</v>
-      </c>
-      <c r="N50" t="s">
-        <v>42</v>
-      </c>
-      <c r="O50">
-        <v>12</v>
-      </c>
-      <c r="P50" s="11"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="F51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O51" s="2">
+        <v>6</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51">
-        <v>1000</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" t="s">
-        <v>14</v>
-      </c>
-      <c r="L51" t="s">
-        <v>14</v>
-      </c>
-      <c r="N51" t="s">
-        <v>42</v>
-      </c>
-      <c r="O51">
-        <v>12</v>
-      </c>
-      <c r="P51" s="11"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="B52" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O52" s="2">
+        <v>6</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B52" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E52">
+      <c r="B53" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="2">
+        <v>50</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O53" s="2">
+        <v>6</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" s="2">
         <v>0</v>
       </c>
-      <c r="F52" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" t="s">
-        <v>14</v>
-      </c>
-      <c r="K52" t="s">
-        <v>14</v>
-      </c>
-      <c r="L52" t="s">
-        <v>14</v>
-      </c>
-      <c r="M52" t="s">
-        <v>25</v>
-      </c>
-      <c r="N52" t="s">
-        <v>42</v>
-      </c>
-      <c r="O52">
-        <v>12</v>
-      </c>
-      <c r="P52" s="11"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="F54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54" s="2">
+        <v>12</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53">
-        <v>20</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" t="s">
-        <v>12</v>
-      </c>
-      <c r="J53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K53" t="s">
-        <v>14</v>
-      </c>
-      <c r="L53" t="s">
-        <v>14</v>
-      </c>
-      <c r="N53" t="s">
-        <v>42</v>
-      </c>
-      <c r="O53">
-        <v>6</v>
-      </c>
-      <c r="P53" s="11"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B54" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54">
-        <v>100</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" t="s">
-        <v>12</v>
-      </c>
-      <c r="J54" t="s">
-        <v>14</v>
-      </c>
-      <c r="K54" t="s">
-        <v>14</v>
-      </c>
-      <c r="L54" t="s">
-        <v>14</v>
-      </c>
-      <c r="N54" t="s">
-        <v>42</v>
-      </c>
-      <c r="O54">
-        <v>6</v>
-      </c>
-      <c r="P54" s="11"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55">
-        <v>50</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" t="s">
-        <v>14</v>
-      </c>
-      <c r="K55" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>14</v>
-      </c>
-      <c r="N55" t="s">
-        <v>42</v>
-      </c>
-      <c r="O55">
-        <v>6</v>
-      </c>
-      <c r="P55" s="11"/>
+      <c r="B55" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55" s="2">
+        <v>12</v>
+      </c>
+      <c r="P55" s="3"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
         <v>12</v>
@@ -4013,29 +3977,28 @@
       <c r="O56">
         <v>6</v>
       </c>
-      <c r="P56" s="11"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H57" t="s">
         <v>12</v>
@@ -4058,29 +4021,28 @@
       <c r="O57">
         <v>6</v>
       </c>
-      <c r="P57" s="11"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E58">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
         <v>12</v>
@@ -4106,25 +4068,25 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E59">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
         <v>12</v>
@@ -4150,31 +4112,31 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E60">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I60" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J60" t="s">
         <v>14</v>
@@ -4185,34 +4147,37 @@
       <c r="L60" t="s">
         <v>14</v>
       </c>
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
       <c r="N60" t="s">
         <v>42</v>
       </c>
       <c r="O60">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s">
         <v>41</v>
       </c>
       <c r="E61">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H61" t="s">
         <v>12</v>
@@ -4224,7 +4189,7 @@
         <v>14</v>
       </c>
       <c r="K61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L61" t="s">
         <v>14</v>
@@ -4238,22 +4203,22 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D62" t="s">
         <v>41</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G62" t="s">
         <v>12</v>
@@ -4272,9 +4237,6 @@
       </c>
       <c r="L62" t="s">
         <v>14</v>
-      </c>
-      <c r="M62" t="s">
-        <v>25</v>
       </c>
       <c r="N62" t="s">
         <v>42</v>
@@ -4285,22 +4247,22 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s">
         <v>41</v>
       </c>
       <c r="E63">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G63" t="s">
         <v>12</v>
@@ -4324,30 +4286,30 @@
         <v>42</v>
       </c>
       <c r="O63">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="D64" t="s">
         <v>41</v>
       </c>
       <c r="E64">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H64" t="s">
         <v>12</v>
@@ -4373,28 +4335,28 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s">
         <v>41</v>
       </c>
       <c r="E65">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I65" t="s">
         <v>12</v>
@@ -4412,21 +4374,21 @@
         <v>42</v>
       </c>
       <c r="O65">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
-      </c>
-      <c r="D66" t="s">
-        <v>62</v>
+        <v>149</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4452,6 +4414,9 @@
       <c r="L66" t="s">
         <v>14</v>
       </c>
+      <c r="M66" t="s">
+        <v>25</v>
+      </c>
       <c r="N66" t="s">
         <v>42</v>
       </c>
@@ -4461,16 +4426,16 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4479,7 +4444,7 @@
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s">
         <v>12</v>
@@ -4505,28 +4470,28 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="C68" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F68" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
         <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I68" t="s">
         <v>12</v>
@@ -4544,21 +4509,21 @@
         <v>42</v>
       </c>
       <c r="O68">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>181</v>
-      </c>
-      <c r="D69" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4567,7 +4532,7 @@
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H69" t="s">
         <v>12</v>
@@ -4584,22 +4549,25 @@
       <c r="L69" t="s">
         <v>14</v>
       </c>
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
       <c r="N69" t="s">
         <v>42</v>
       </c>
       <c r="O69">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>41</v>
@@ -4611,13 +4579,13 @@
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J70" t="s">
         <v>14</v>
@@ -4629,36 +4597,36 @@
         <v>14</v>
       </c>
       <c r="M70" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="N70" t="s">
         <v>42</v>
       </c>
       <c r="O70">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -4684,13 +4652,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="D72" t="s">
         <v>41</v>
@@ -4699,7 +4667,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s">
         <v>12</v>
@@ -4728,19 +4696,19 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" t="s">
         <v>107</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>153</v>
       </c>
-      <c r="C73" t="s">
-        <v>154</v>
-      </c>
       <c r="D73" t="s">
         <v>41</v>
       </c>
       <c r="E73">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
@@ -4767,33 +4735,33 @@
         <v>42</v>
       </c>
       <c r="O73">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
       </c>
       <c r="E74">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="F74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
         <v>12</v>
@@ -4811,33 +4779,33 @@
         <v>42</v>
       </c>
       <c r="O74">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D75" t="s">
         <v>41</v>
       </c>
       <c r="E75">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H75" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I75" t="s">
         <v>12</v>
@@ -4855,30 +4823,30 @@
         <v>42</v>
       </c>
       <c r="O75">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="C76" t="s">
-        <v>163</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>41</v>
+        <v>124</v>
+      </c>
+      <c r="D76" t="s">
+        <v>68</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s">
         <v>12</v>
@@ -4894,9 +4862,6 @@
       </c>
       <c r="L76" t="s">
         <v>14</v>
-      </c>
-      <c r="M76" t="s">
-        <v>25</v>
       </c>
       <c r="N76" t="s">
         <v>42</v>
@@ -4907,22 +4872,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s">
         <v>14</v>
@@ -4951,19 +4916,19 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C78" t="s">
         <v>160</v>
       </c>
-      <c r="C78" t="s">
-        <v>161</v>
-      </c>
       <c r="D78" t="s">
         <v>41</v>
       </c>
       <c r="E78">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4972,7 +4937,7 @@
         <v>14</v>
       </c>
       <c r="H78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I78" t="s">
         <v>12</v>
@@ -4990,30 +4955,30 @@
         <v>42</v>
       </c>
       <c r="O78">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79" t="s">
         <v>41</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F79" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -5030,37 +4995,34 @@
       <c r="L79" t="s">
         <v>14</v>
       </c>
-      <c r="M79" t="s">
-        <v>17</v>
-      </c>
       <c r="N79" t="s">
         <v>42</v>
       </c>
       <c r="O79">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="C80" t="s">
-        <v>165</v>
-      </c>
-      <c r="D80" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" t="s">
         <v>41</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -5076,9 +5038,6 @@
       </c>
       <c r="L80" t="s">
         <v>14</v>
-      </c>
-      <c r="M80" t="s">
-        <v>166</v>
       </c>
       <c r="N80" t="s">
         <v>42</v>
@@ -5089,16 +5048,16 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
-      </c>
-      <c r="D81" t="s">
-        <v>67</v>
+        <v>159</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5107,7 +5066,7 @@
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -5133,25 +5092,25 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E82">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -5177,28 +5136,28 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C83" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
         <v>41</v>
       </c>
       <c r="E83">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I83" t="s">
         <v>12</v>
@@ -5216,27 +5175,27 @@
         <v>42</v>
       </c>
       <c r="O83">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
-      </c>
-      <c r="D84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E84">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -5245,7 +5204,7 @@
         <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J84" t="s">
         <v>14</v>
@@ -5255,6 +5214,9 @@
       </c>
       <c r="L84" t="s">
         <v>14</v>
+      </c>
+      <c r="M84" t="s">
+        <v>90</v>
       </c>
       <c r="N84" t="s">
         <v>42</v>
@@ -5265,28 +5227,28 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
         <v>41</v>
       </c>
       <c r="E85">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="F85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
       </c>
       <c r="H85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I85" t="s">
         <v>12</v>
@@ -5304,27 +5266,27 @@
         <v>42</v>
       </c>
       <c r="O85">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
         <v>14</v>
@@ -5353,19 +5315,19 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F87" t="s">
         <v>14</v>
@@ -5392,36 +5354,36 @@
         <v>42</v>
       </c>
       <c r="O87">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>140</v>
-      </c>
-      <c r="D88" t="s">
-        <v>62</v>
+        <v>128</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I88" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J88" t="s">
         <v>14</v>
@@ -5432,31 +5394,34 @@
       <c r="L88" t="s">
         <v>14</v>
       </c>
+      <c r="M88" t="s">
+        <v>90</v>
+      </c>
       <c r="N88" t="s">
         <v>42</v>
       </c>
       <c r="O88">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
         <v>41</v>
       </c>
       <c r="E89">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G89" t="s">
         <v>14</v>
@@ -5480,27 +5445,27 @@
         <v>42</v>
       </c>
       <c r="O89">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E90">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -5529,22 +5494,22 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="B91" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C91" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E91">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G91" t="s">
         <v>14</v>
@@ -5573,25 +5538,25 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="C92" t="s">
-        <v>173</v>
-      </c>
-      <c r="D92" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" t="s">
         <v>41</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F92" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s">
         <v>12</v>
@@ -5607,9 +5572,6 @@
       </c>
       <c r="L92" t="s">
         <v>14</v>
-      </c>
-      <c r="M92" t="s">
-        <v>25</v>
       </c>
       <c r="N92" t="s">
         <v>42</v>
@@ -5620,31 +5582,31 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
-      </c>
-      <c r="D93" t="s">
-        <v>67</v>
+        <v>128</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G93" t="s">
         <v>14</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I93" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J93" t="s">
         <v>14</v>
@@ -5655,37 +5617,40 @@
       <c r="L93" t="s">
         <v>14</v>
       </c>
+      <c r="M93" t="s">
+        <v>90</v>
+      </c>
       <c r="N93" t="s">
         <v>42</v>
       </c>
       <c r="O93">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C94" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
         <v>41</v>
       </c>
       <c r="E94">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I94" t="s">
         <v>12</v>
@@ -5703,24 +5668,24 @@
         <v>42</v>
       </c>
       <c r="O94">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="B95" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C95" t="s">
-        <v>142</v>
-      </c>
-      <c r="D95" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D95" t="s">
         <v>41</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -5729,10 +5694,10 @@
         <v>14</v>
       </c>
       <c r="H95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J95" t="s">
         <v>14</v>
@@ -5743,31 +5708,28 @@
       <c r="L95" t="s">
         <v>14</v>
       </c>
-      <c r="M95" t="s">
-        <v>101</v>
-      </c>
       <c r="N95" t="s">
         <v>42</v>
       </c>
       <c r="O95">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D96" t="s">
         <v>41</v>
       </c>
       <c r="E96">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
@@ -5794,18 +5756,18 @@
         <v>42</v>
       </c>
       <c r="O96">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="B97" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C97" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="D97" t="s">
         <v>41</v>
@@ -5841,24 +5803,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="B98" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D98" t="s">
         <v>41</v>
       </c>
       <c r="E98">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G98" t="s">
         <v>14</v>
@@ -5882,18 +5844,18 @@
         <v>42</v>
       </c>
       <c r="O98">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>41</v>
@@ -5908,10 +5870,10 @@
         <v>14</v>
       </c>
       <c r="H99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J99" t="s">
         <v>14</v>
@@ -5923,30 +5885,30 @@
         <v>14</v>
       </c>
       <c r="M99" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="N99" t="s">
         <v>42</v>
       </c>
       <c r="O99">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B100" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="C100" t="s">
         <v>145</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E100">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
@@ -5973,33 +5935,33 @@
         <v>42</v>
       </c>
       <c r="O100">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B101" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D101" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F101" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s">
         <v>14</v>
       </c>
       <c r="H101" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I101" t="s">
         <v>12</v>
@@ -6017,21 +5979,21 @@
         <v>42</v>
       </c>
       <c r="O101">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="B102" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D102" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6043,10 +6005,10 @@
         <v>14</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I102" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J102" t="s">
         <v>14</v>
@@ -6057,28 +6019,32 @@
       <c r="L102" t="s">
         <v>14</v>
       </c>
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
       <c r="N102" t="s">
         <v>42</v>
       </c>
       <c r="O102">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="P102" s="8"/>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>182</v>
-      </c>
-      <c r="B103" t="s">
-        <v>119</v>
+        <v>18</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
-      </c>
-      <c r="D103" t="s">
+        <v>79</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E103">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
@@ -6100,6 +6066,9 @@
       </c>
       <c r="L103" t="s">
         <v>14</v>
+      </c>
+      <c r="M103" t="s">
+        <v>25</v>
       </c>
       <c r="N103" t="s">
         <v>42</v>
@@ -6107,22 +6076,23 @@
       <c r="O103">
         <v>6</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P103" s="8"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="B104" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="C104" t="s">
-        <v>142</v>
-      </c>
-      <c r="D104" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D104" t="s">
         <v>41</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
@@ -6131,10 +6101,10 @@
         <v>14</v>
       </c>
       <c r="H104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J104" t="s">
         <v>14</v>
@@ -6145,34 +6115,32 @@
       <c r="L104" t="s">
         <v>14</v>
       </c>
-      <c r="M104" t="s">
-        <v>101</v>
-      </c>
       <c r="N104" t="s">
         <v>42</v>
       </c>
       <c r="O104">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="P104" s="8"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="B105" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="C105" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
       </c>
       <c r="E105">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F105" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s">
         <v>14</v>
@@ -6198,22 +6166,23 @@
       <c r="O105">
         <v>6</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P105" s="8"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="B106" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>152</v>
-      </c>
-      <c r="D106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E106">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
@@ -6222,10 +6191,10 @@
         <v>14</v>
       </c>
       <c r="H106" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J106" t="s">
         <v>14</v>
@@ -6236,72 +6205,79 @@
       <c r="L106" t="s">
         <v>14</v>
       </c>
+      <c r="M106" t="s">
+        <v>21</v>
+      </c>
       <c r="N106" t="s">
         <v>42</v>
       </c>
       <c r="O106">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" t="s">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J107" t="s">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s">
+        <v>14</v>
+      </c>
+      <c r="L107" t="s">
+        <v>14</v>
+      </c>
+      <c r="M107" t="s">
+        <v>25</v>
+      </c>
+      <c r="N107" t="s">
+        <v>42</v>
+      </c>
+      <c r="O107">
         <v>6</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>183</v>
-      </c>
-      <c r="B107" t="s">
-        <v>153</v>
-      </c>
-      <c r="C107" t="s">
-        <v>154</v>
-      </c>
-      <c r="D107" t="s">
-        <v>41</v>
-      </c>
-      <c r="E107">
-        <v>255</v>
-      </c>
-      <c r="F107" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" t="s">
-        <v>14</v>
-      </c>
-      <c r="H107" t="s">
-        <v>12</v>
-      </c>
-      <c r="I107" t="s">
-        <v>12</v>
-      </c>
-      <c r="J107" t="s">
-        <v>14</v>
-      </c>
-      <c r="K107" t="s">
-        <v>14</v>
-      </c>
-      <c r="L107" t="s">
-        <v>14</v>
-      </c>
-      <c r="N107" t="s">
-        <v>42</v>
-      </c>
-      <c r="O107">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P107" s="8"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C108" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="D108" t="s">
         <v>41</v>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
@@ -6331,556 +6307,56 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>183</v>
-      </c>
-      <c r="B109" t="s">
-        <v>119</v>
-      </c>
-      <c r="C109" t="s">
-        <v>157</v>
-      </c>
-      <c r="D109" t="s">
-        <v>41</v>
-      </c>
-      <c r="E109">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" s="2">
         <v>50</v>
       </c>
-      <c r="F109" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" t="s">
-        <v>12</v>
-      </c>
-      <c r="J109" t="s">
-        <v>14</v>
-      </c>
-      <c r="K109" t="s">
-        <v>14</v>
-      </c>
-      <c r="L109" t="s">
-        <v>14</v>
-      </c>
-      <c r="N109" t="s">
-        <v>42</v>
-      </c>
-      <c r="O109">
+      <c r="F109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M109" s="2"/>
+      <c r="N109" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>183</v>
-      </c>
-      <c r="B110" t="s">
-        <v>162</v>
-      </c>
-      <c r="C110" t="s">
-        <v>163</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
-        <v>12</v>
-      </c>
-      <c r="I110" t="s">
-        <v>12</v>
-      </c>
-      <c r="J110" t="s">
-        <v>14</v>
-      </c>
-      <c r="K110" t="s">
-        <v>14</v>
-      </c>
-      <c r="L110" t="s">
-        <v>14</v>
-      </c>
-      <c r="M110" t="s">
-        <v>25</v>
-      </c>
-      <c r="N110" t="s">
-        <v>42</v>
-      </c>
-      <c r="O110">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>183</v>
-      </c>
-      <c r="B111" t="s">
-        <v>158</v>
-      </c>
-      <c r="C111" t="s">
-        <v>159</v>
-      </c>
-      <c r="D111" t="s">
-        <v>67</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" t="s">
-        <v>12</v>
-      </c>
-      <c r="I111" t="s">
-        <v>12</v>
-      </c>
-      <c r="J111" t="s">
-        <v>14</v>
-      </c>
-      <c r="K111" t="s">
-        <v>14</v>
-      </c>
-      <c r="L111" t="s">
-        <v>14</v>
-      </c>
-      <c r="N111" t="s">
-        <v>42</v>
-      </c>
-      <c r="O111">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>183</v>
-      </c>
-      <c r="B112" t="s">
-        <v>160</v>
-      </c>
-      <c r="C112" t="s">
-        <v>161</v>
-      </c>
-      <c r="D112" t="s">
-        <v>41</v>
-      </c>
-      <c r="E112">
-        <v>1000</v>
-      </c>
-      <c r="F112" t="s">
-        <v>14</v>
-      </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
-        <v>14</v>
-      </c>
-      <c r="I112" t="s">
-        <v>12</v>
-      </c>
-      <c r="J112" t="s">
-        <v>14</v>
-      </c>
-      <c r="K112" t="s">
-        <v>14</v>
-      </c>
-      <c r="L112" t="s">
-        <v>14</v>
-      </c>
-      <c r="N112" t="s">
-        <v>42</v>
-      </c>
-      <c r="O112">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>18</v>
-      </c>
-      <c r="B113" t="s">
-        <v>87</v>
-      </c>
-      <c r="C113" t="s">
-        <v>88</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-      <c r="F113" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" t="s">
-        <v>14</v>
-      </c>
-      <c r="I113" t="s">
-        <v>14</v>
-      </c>
-      <c r="J113" t="s">
-        <v>14</v>
-      </c>
-      <c r="K113" t="s">
-        <v>14</v>
-      </c>
-      <c r="L113" t="s">
-        <v>14</v>
-      </c>
-      <c r="M113" t="s">
-        <v>17</v>
-      </c>
-      <c r="N113" t="s">
-        <v>42</v>
-      </c>
-      <c r="O113">
-        <v>12</v>
-      </c>
-      <c r="P113" s="11"/>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>18</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C114" t="s">
-        <v>90</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E114">
-        <v>0</v>
-      </c>
-      <c r="F114" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" t="s">
-        <v>12</v>
-      </c>
-      <c r="I114" t="s">
-        <v>12</v>
-      </c>
-      <c r="J114" t="s">
-        <v>14</v>
-      </c>
-      <c r="K114" t="s">
-        <v>14</v>
-      </c>
-      <c r="L114" t="s">
-        <v>14</v>
-      </c>
-      <c r="M114" t="s">
-        <v>25</v>
-      </c>
-      <c r="N114" t="s">
-        <v>42</v>
-      </c>
-      <c r="O114">
-        <v>6</v>
-      </c>
-      <c r="P114" s="11"/>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>18</v>
-      </c>
-      <c r="B115" t="s">
-        <v>91</v>
-      </c>
-      <c r="C115" t="s">
-        <v>92</v>
-      </c>
-      <c r="D115" t="s">
-        <v>41</v>
-      </c>
-      <c r="E115">
-        <v>100</v>
-      </c>
-      <c r="F115" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" t="s">
-        <v>14</v>
-      </c>
-      <c r="H115" t="s">
-        <v>12</v>
-      </c>
-      <c r="I115" t="s">
-        <v>12</v>
-      </c>
-      <c r="J115" t="s">
-        <v>14</v>
-      </c>
-      <c r="K115" t="s">
-        <v>14</v>
-      </c>
-      <c r="L115" t="s">
-        <v>14</v>
-      </c>
-      <c r="N115" t="s">
-        <v>42</v>
-      </c>
-      <c r="O115">
-        <v>6</v>
-      </c>
-      <c r="P115" s="11"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>18</v>
-      </c>
-      <c r="B116" t="s">
-        <v>125</v>
-      </c>
-      <c r="C116" t="s">
-        <v>126</v>
-      </c>
-      <c r="D116" t="s">
-        <v>41</v>
-      </c>
-      <c r="E116">
-        <v>50</v>
-      </c>
-      <c r="F116" t="s">
-        <v>14</v>
-      </c>
-      <c r="G116" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" t="s">
-        <v>12</v>
-      </c>
-      <c r="I116" t="s">
-        <v>12</v>
-      </c>
-      <c r="J116" t="s">
-        <v>14</v>
-      </c>
-      <c r="K116" t="s">
-        <v>14</v>
-      </c>
-      <c r="L116" t="s">
-        <v>14</v>
-      </c>
-      <c r="N116" t="s">
-        <v>42</v>
-      </c>
-      <c r="O116">
-        <v>6</v>
-      </c>
-      <c r="P116" s="11"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>23</v>
-      </c>
-      <c r="B117" t="s">
-        <v>93</v>
-      </c>
-      <c r="C117" t="s">
-        <v>17</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" t="s">
-        <v>14</v>
-      </c>
-      <c r="H117" t="s">
-        <v>14</v>
-      </c>
-      <c r="I117" t="s">
-        <v>14</v>
-      </c>
-      <c r="J117" t="s">
-        <v>14</v>
-      </c>
-      <c r="K117" t="s">
-        <v>14</v>
-      </c>
-      <c r="L117" t="s">
-        <v>14</v>
-      </c>
-      <c r="M117" t="s">
-        <v>21</v>
-      </c>
-      <c r="N117" t="s">
-        <v>42</v>
-      </c>
-      <c r="O117">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>23</v>
-      </c>
-      <c r="B118" t="s">
-        <v>89</v>
-      </c>
-      <c r="C118" t="s">
-        <v>90</v>
-      </c>
-      <c r="D118" t="s">
-        <v>41</v>
-      </c>
-      <c r="E118">
-        <v>255</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
-        <v>12</v>
-      </c>
-      <c r="I118" t="s">
-        <v>12</v>
-      </c>
-      <c r="J118" t="s">
-        <v>14</v>
-      </c>
-      <c r="K118" t="s">
-        <v>14</v>
-      </c>
-      <c r="L118" t="s">
-        <v>14</v>
-      </c>
-      <c r="N118" t="s">
-        <v>42</v>
-      </c>
-      <c r="O118">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>23</v>
-      </c>
-      <c r="B119" t="s">
-        <v>91</v>
-      </c>
-      <c r="C119" t="s">
-        <v>92</v>
-      </c>
-      <c r="D119" t="s">
-        <v>41</v>
-      </c>
-      <c r="E119">
-        <v>100</v>
-      </c>
-      <c r="F119" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119" t="s">
-        <v>12</v>
-      </c>
-      <c r="I119" t="s">
-        <v>12</v>
-      </c>
-      <c r="J119" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" t="s">
-        <v>14</v>
-      </c>
-      <c r="L119" t="s">
-        <v>14</v>
-      </c>
-      <c r="N119" t="s">
-        <v>42</v>
-      </c>
-      <c r="O119">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A120" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E120" s="2">
-        <v>50</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M120" s="2"/>
-      <c r="N120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O120" s="2">
-        <v>6</v>
-      </c>
-      <c r="P120" s="2"/>
+      <c r="P109" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P120" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P120">
-      <sortCondition ref="A1:A120"/>
+  <autoFilter ref="A1:P109" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P109">
+      <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1930" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D5D307-77B7-41F8-8391-445C601D9DD3}"/>
+  <xr:revisionPtr revIDLastSave="1950" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE9ED967-44E3-4167-8C59-E088698B2B69}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Column" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$110</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="188">
   <si>
     <t>Table Name</t>
   </si>
@@ -582,6 +582,12 @@
   </si>
   <si>
     <t>Sub-detail list</t>
+  </si>
+  <si>
+    <t>ProjectMilestone</t>
+  </si>
+  <si>
+    <t>MilestoneId</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1258,13 +1264,13 @@
         <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>185</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -1275,16 +1281,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1295,16 +1301,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
+        <v>96</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1315,16 +1321,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>185</v>
+        <v>152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -1335,21 +1341,41 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1360,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2171,31 +2197,31 @@
         <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>14</v>
@@ -2203,9 +2229,7 @@
       <c r="L18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
         <v>42</v>
       </c>
@@ -2216,105 +2240,109 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O19" s="2">
+        <v>12</v>
+      </c>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2">
         <v>255</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="2">
-        <v>12</v>
-      </c>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O20" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P20" s="2"/>
     </row>
     <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>66</v>
@@ -2354,19 +2382,19 @@
     </row>
     <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>12</v>
@@ -2400,25 +2428,25 @@
     </row>
     <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>58</v>
+        <v>186</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E23" s="2">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>12</v>
@@ -2440,25 +2468,25 @@
         <v>42</v>
       </c>
       <c r="O23" s="2">
-        <v>12</v>
-      </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
@@ -2481,14 +2509,12 @@
       <c r="L24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O24" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P24" s="3"/>
     </row>
@@ -2497,16 +2523,16 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E25" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
@@ -2529,7 +2555,9 @@
       <c r="L25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M25" s="2"/>
+      <c r="M25" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N25" s="2" t="s">
         <v>42</v>
       </c>
@@ -2543,22 +2571,22 @@
         <v>17</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
@@ -2589,10 +2617,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>66</v>
@@ -2635,19 +2663,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>14</v>
@@ -2672,7 +2700,7 @@
         <v>42</v>
       </c>
       <c r="O28" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P28" s="3"/>
     </row>
@@ -2681,16 +2709,16 @@
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E29" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>14</v>
@@ -2699,7 +2727,7 @@
         <v>14</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>12</v>
@@ -2722,30 +2750,30 @@
       </c>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>12</v>
@@ -2759,9 +2787,7 @@
       <c r="L30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
         <v>42</v>
       </c>
@@ -2770,21 +2796,21 @@
       </c>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E31" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>12</v>
@@ -2799,7 +2825,7 @@
         <v>12</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>14</v>
@@ -2807,12 +2833,14 @@
       <c r="L31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N31" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O31" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P31" s="3"/>
     </row>
@@ -2821,16 +2849,16 @@
         <v>17</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
@@ -2845,7 +2873,7 @@
         <v>12</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>14</v>
@@ -2867,16 +2895,16 @@
         <v>17</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>12</v>
@@ -2913,22 +2941,22 @@
         <v>17</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>12</v>
@@ -2940,14 +2968,12 @@
         <v>14</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
         <v>42</v>
       </c>
@@ -2961,10 +2987,10 @@
         <v>17</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>41</v>
@@ -2976,7 +3002,7 @@
         <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>12</v>
@@ -2988,7 +3014,7 @@
         <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>14</v>
@@ -3008,17 +3034,17 @@
       <c r="A36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>183</v>
+      <c r="B36" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>14</v>
@@ -3041,7 +3067,9 @@
       <c r="L36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M36" s="2"/>
+      <c r="M36" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N36" s="2" t="s">
         <v>42</v>
       </c>
@@ -3054,26 +3082,26 @@
       <c r="A37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>111</v>
+      <c r="B37" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>12</v>
@@ -3092,7 +3120,7 @@
         <v>42</v>
       </c>
       <c r="O37" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P37" s="3"/>
     </row>
@@ -3101,13 +3129,13 @@
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -3144,22 +3172,22 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>14</v>
@@ -3168,7 +3196,7 @@
         <v>14</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>14</v>
@@ -3179,9 +3207,7 @@
       <c r="L39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2" t="s">
         <v>42</v>
       </c>
@@ -3190,33 +3216,33 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>58</v>
+      <c r="B40" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="2">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>14</v>
@@ -3227,7 +3253,9 @@
       <c r="L40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M40" s="2"/>
+      <c r="M40" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="N40" s="2" t="s">
         <v>42</v>
       </c>
@@ -3236,21 +3264,21 @@
       </c>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E41" s="2">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>12</v>
@@ -3273,14 +3301,12 @@
       <c r="L41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O41" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P41" s="3"/>
     </row>
@@ -3289,16 +3315,16 @@
         <v>21</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E42" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>12</v>
@@ -3321,7 +3347,9 @@
       <c r="L42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M42" s="2"/>
+      <c r="M42" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="N42" s="2" t="s">
         <v>42</v>
       </c>
@@ -3335,22 +3363,22 @@
         <v>21</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>12</v>
@@ -3381,10 +3409,10 @@
         <v>21</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>66</v>
@@ -3427,19 +3455,19 @@
         <v>21</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>14</v>
@@ -3464,7 +3492,7 @@
         <v>42</v>
       </c>
       <c r="O45" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P45" s="3"/>
     </row>
@@ -3473,16 +3501,16 @@
         <v>21</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>14</v>
@@ -3491,7 +3519,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>12</v>
@@ -3514,30 +3542,30 @@
       </c>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>12</v>
@@ -3551,9 +3579,7 @@
       <c r="L47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2" t="s">
         <v>42</v>
       </c>
@@ -3562,21 +3588,21 @@
       </c>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
@@ -3591,7 +3617,7 @@
         <v>12</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>14</v>
@@ -3599,12 +3625,14 @@
       <c r="L48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M48" s="2"/>
+      <c r="M48" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N48" s="2" t="s">
         <v>42</v>
       </c>
       <c r="O48" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P48" s="3"/>
     </row>
@@ -3613,16 +3641,16 @@
         <v>21</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E49" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>12</v>
@@ -3637,7 +3665,7 @@
         <v>12</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>14</v>
@@ -3659,16 +3687,16 @@
         <v>21</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E50" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>12</v>
@@ -3705,22 +3733,22 @@
         <v>21</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>12</v>
@@ -3732,14 +3760,12 @@
         <v>14</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
         <v>42</v>
       </c>
@@ -3753,10 +3779,10 @@
         <v>21</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>41</v>
@@ -3768,7 +3794,7 @@
         <v>14</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>12</v>
@@ -3780,7 +3806,7 @@
         <v>14</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>14</v>
@@ -3800,17 +3826,17 @@
       <c r="A53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>183</v>
+      <c r="B53" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E53" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>14</v>
@@ -3833,7 +3859,9 @@
       <c r="L53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M53" s="2"/>
+      <c r="M53" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="N53" s="2" t="s">
         <v>42</v>
       </c>
@@ -3846,26 +3874,26 @@
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>111</v>
+      <c r="B54" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="E54" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>12</v>
@@ -3884,7 +3912,7 @@
         <v>42</v>
       </c>
       <c r="O54" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P54" s="3"/>
     </row>
@@ -3893,13 +3921,13 @@
         <v>21</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="E55" s="2">
         <v>0</v>
@@ -3935,58 +3963,60 @@
       <c r="P55" s="3"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>152</v>
-      </c>
-      <c r="B56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" t="s">
-        <v>162</v>
-      </c>
-      <c r="D56" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56">
+      <c r="A56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="2">
         <v>0</v>
       </c>
-      <c r="F56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" t="s">
-        <v>12</v>
-      </c>
-      <c r="I56" t="s">
-        <v>12</v>
-      </c>
-      <c r="J56" t="s">
-        <v>14</v>
-      </c>
-      <c r="K56" t="s">
-        <v>14</v>
-      </c>
-      <c r="L56" t="s">
-        <v>14</v>
-      </c>
-      <c r="N56" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56">
-        <v>6</v>
-      </c>
+      <c r="F56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O56" s="2">
+        <v>12</v>
+      </c>
+      <c r="P56" s="3"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>152</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D57" t="s">
         <v>62</v>
@@ -4027,13 +4057,13 @@
         <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D58" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4042,7 +4072,7 @@
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H58" t="s">
         <v>12</v>
@@ -4071,10 +4101,10 @@
         <v>152</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D59" t="s">
         <v>66</v>
@@ -4112,16 +4142,16 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>41</v>
+        <v>167</v>
+      </c>
+      <c r="D60" t="s">
+        <v>66</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4133,10 +4163,10 @@
         <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J60" t="s">
         <v>14</v>
@@ -4147,14 +4177,11 @@
       <c r="L60" t="s">
         <v>14</v>
       </c>
-      <c r="M60" t="s">
-        <v>17</v>
-      </c>
       <c r="N60" t="s">
         <v>42</v>
       </c>
       <c r="O60">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -4162,28 +4189,28 @@
         <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E61">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J61" t="s">
         <v>14</v>
@@ -4194,11 +4221,14 @@
       <c r="L61" t="s">
         <v>14</v>
       </c>
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
       <c r="N61" t="s">
         <v>42</v>
       </c>
       <c r="O61">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
@@ -4206,10 +4236,10 @@
         <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
         <v>41</v>
@@ -4250,16 +4280,16 @@
         <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D63" t="s">
         <v>41</v>
       </c>
       <c r="E63">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -4286,7 +4316,7 @@
         <v>42</v>
       </c>
       <c r="O63">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
@@ -4294,16 +4324,16 @@
         <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D64" t="s">
         <v>41</v>
       </c>
       <c r="E64">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -4330,7 +4360,7 @@
         <v>42</v>
       </c>
       <c r="O64">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
@@ -4338,16 +4368,16 @@
         <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
         <v>41</v>
       </c>
       <c r="E65">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
@@ -4382,16 +4412,16 @@
         <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" t="s">
         <v>41</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
@@ -4413,9 +4443,6 @@
       </c>
       <c r="L66" t="s">
         <v>14</v>
-      </c>
-      <c r="M66" t="s">
-        <v>25</v>
       </c>
       <c r="N66" t="s">
         <v>42</v>
@@ -4429,13 +4456,13 @@
         <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D67" t="s">
-        <v>66</v>
+        <v>149</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4444,7 +4471,7 @@
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H67" t="s">
         <v>12</v>
@@ -4460,6 +4487,9 @@
       </c>
       <c r="L67" t="s">
         <v>14</v>
+      </c>
+      <c r="M67" t="s">
+        <v>25</v>
       </c>
       <c r="N67" t="s">
         <v>42</v>
@@ -4473,25 +4503,25 @@
         <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E68">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G68" t="s">
         <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I68" t="s">
         <v>12</v>
@@ -4509,33 +4539,33 @@
         <v>42</v>
       </c>
       <c r="O68">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
-      </c>
-      <c r="D69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" t="s">
         <v>41</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I69" t="s">
         <v>12</v>
@@ -4548,9 +4578,6 @@
       </c>
       <c r="L69" t="s">
         <v>14</v>
-      </c>
-      <c r="M69" t="s">
-        <v>17</v>
       </c>
       <c r="N69" t="s">
         <v>42</v>
@@ -4564,10 +4591,10 @@
         <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>41</v>
@@ -4597,13 +4624,13 @@
         <v>14</v>
       </c>
       <c r="M70" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="N70" t="s">
         <v>42</v>
       </c>
       <c r="O70">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
@@ -4611,22 +4638,22 @@
         <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" t="s">
-        <v>66</v>
+        <v>151</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -4642,6 +4669,9 @@
       </c>
       <c r="L71" t="s">
         <v>14</v>
+      </c>
+      <c r="M71" t="s">
+        <v>152</v>
       </c>
       <c r="N71" t="s">
         <v>42</v>
@@ -4655,22 +4685,22 @@
         <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -4699,19 +4729,19 @@
         <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="D73" t="s">
         <v>41</v>
       </c>
       <c r="E73">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
         <v>12</v>
@@ -4743,25 +4773,25 @@
         <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
       </c>
       <c r="E74">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I74" t="s">
         <v>12</v>
@@ -4779,7 +4809,7 @@
         <v>42</v>
       </c>
       <c r="O74">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
@@ -4787,10 +4817,10 @@
         <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D75" t="s">
         <v>41</v>
@@ -4831,16 +4861,16 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
@@ -4849,7 +4879,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I76" t="s">
         <v>12</v>
@@ -4867,7 +4897,7 @@
         <v>42</v>
       </c>
       <c r="O76">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -4875,13 +4905,13 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4919,16 +4949,16 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="C78" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E78">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4963,10 +4993,10 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
         <v>41</v>
@@ -5007,16 +5037,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C80" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D80" t="s">
         <v>41</v>
       </c>
       <c r="E80">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
@@ -5051,22 +5081,22 @@
         <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="C81" t="s">
-        <v>159</v>
-      </c>
-      <c r="D81" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" t="s">
         <v>41</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -5095,13 +5125,13 @@
         <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C82" t="s">
-        <v>157</v>
-      </c>
-      <c r="D82" t="s">
-        <v>66</v>
+        <v>159</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5110,7 +5140,7 @@
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -5139,16 +5169,16 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C83" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
@@ -5157,7 +5187,7 @@
         <v>14</v>
       </c>
       <c r="H83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I83" t="s">
         <v>12</v>
@@ -5175,27 +5205,27 @@
         <v>42</v>
       </c>
       <c r="O83">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>128</v>
-      </c>
-      <c r="D84" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" t="s">
         <v>41</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -5204,7 +5234,7 @@
         <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J84" t="s">
         <v>14</v>
@@ -5214,9 +5244,6 @@
       </c>
       <c r="L84" t="s">
         <v>14</v>
-      </c>
-      <c r="M84" t="s">
-        <v>90</v>
       </c>
       <c r="N84" t="s">
         <v>42</v>
@@ -5230,16 +5257,16 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
-      </c>
-      <c r="D85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E85">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
@@ -5248,10 +5275,10 @@
         <v>14</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J85" t="s">
         <v>14</v>
@@ -5262,11 +5289,14 @@
       <c r="L85" t="s">
         <v>14</v>
       </c>
+      <c r="M85" t="s">
+        <v>90</v>
+      </c>
       <c r="N85" t="s">
         <v>42</v>
       </c>
       <c r="O85">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
@@ -5274,16 +5304,16 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>41</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
@@ -5318,19 +5348,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
         <v>41</v>
       </c>
       <c r="E87">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
@@ -5354,36 +5384,36 @@
         <v>42</v>
       </c>
       <c r="O87">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
-      </c>
-      <c r="D88" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D88" t="s">
         <v>41</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F88" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J88" t="s">
         <v>14</v>
@@ -5393,9 +5423,6 @@
       </c>
       <c r="L88" t="s">
         <v>14</v>
-      </c>
-      <c r="M88" t="s">
-        <v>90</v>
       </c>
       <c r="N88" t="s">
         <v>42</v>
@@ -5409,16 +5436,16 @@
         <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
-      </c>
-      <c r="D89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E89">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
@@ -5427,10 +5454,10 @@
         <v>14</v>
       </c>
       <c r="H89" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I89" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J89" t="s">
         <v>14</v>
@@ -5440,6 +5467,9 @@
       </c>
       <c r="L89" t="s">
         <v>14</v>
+      </c>
+      <c r="M89" t="s">
+        <v>90</v>
       </c>
       <c r="N89" t="s">
         <v>42</v>
@@ -5453,16 +5483,16 @@
         <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
@@ -5489,7 +5519,7 @@
         <v>42</v>
       </c>
       <c r="O90">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
@@ -5497,10 +5527,10 @@
         <v>168</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>66</v>
@@ -5541,16 +5571,16 @@
         <v>168</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E92">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
@@ -5582,19 +5612,19 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
-      </c>
-      <c r="D93" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" t="s">
         <v>41</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
@@ -5603,10 +5633,10 @@
         <v>14</v>
       </c>
       <c r="H93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J93" t="s">
         <v>14</v>
@@ -5617,14 +5647,11 @@
       <c r="L93" t="s">
         <v>14</v>
       </c>
-      <c r="M93" t="s">
-        <v>90</v>
-      </c>
       <c r="N93" t="s">
         <v>42</v>
       </c>
       <c r="O93">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
@@ -5632,16 +5659,16 @@
         <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>136</v>
-      </c>
-      <c r="D94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
@@ -5650,10 +5677,10 @@
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J94" t="s">
         <v>14</v>
@@ -5664,11 +5691,14 @@
       <c r="L94" t="s">
         <v>14</v>
       </c>
+      <c r="M94" t="s">
+        <v>90</v>
+      </c>
       <c r="N94" t="s">
         <v>42</v>
       </c>
       <c r="O94">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
@@ -5676,10 +5706,10 @@
         <v>169</v>
       </c>
       <c r="B95" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D95" t="s">
         <v>41</v>
@@ -5720,16 +5750,16 @@
         <v>169</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D96" t="s">
         <v>41</v>
       </c>
       <c r="E96">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
@@ -5756,7 +5786,7 @@
         <v>42</v>
       </c>
       <c r="O96">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.35">
@@ -5764,16 +5794,16 @@
         <v>169</v>
       </c>
       <c r="B97" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C97" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D97" t="s">
         <v>41</v>
       </c>
       <c r="E97">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F97" t="s">
         <v>12</v>
@@ -5800,7 +5830,7 @@
         <v>42</v>
       </c>
       <c r="O97">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.35">
@@ -5808,16 +5838,16 @@
         <v>169</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D98" t="s">
         <v>41</v>
       </c>
       <c r="E98">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -5852,16 +5882,16 @@
         <v>169</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C99" t="s">
-        <v>149</v>
-      </c>
-      <c r="D99" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D99" t="s">
         <v>41</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -5883,9 +5913,6 @@
       </c>
       <c r="L99" t="s">
         <v>14</v>
-      </c>
-      <c r="M99" t="s">
-        <v>25</v>
       </c>
       <c r="N99" t="s">
         <v>42</v>
@@ -5899,13 +5926,13 @@
         <v>169</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
-      </c>
-      <c r="D100" t="s">
-        <v>66</v>
+        <v>149</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5930,6 +5957,9 @@
       </c>
       <c r="L100" t="s">
         <v>14</v>
+      </c>
+      <c r="M100" t="s">
+        <v>25</v>
       </c>
       <c r="N100" t="s">
         <v>42</v>
@@ -5943,63 +5973,63 @@
         <v>169</v>
       </c>
       <c r="B101" t="s">
+        <v>144</v>
+      </c>
+      <c r="C101" t="s">
+        <v>145</v>
+      </c>
+      <c r="D101" t="s">
+        <v>66</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" t="s">
+        <v>14</v>
+      </c>
+      <c r="K101" t="s">
+        <v>14</v>
+      </c>
+      <c r="L101" t="s">
+        <v>14</v>
+      </c>
+      <c r="N101" t="s">
+        <v>42</v>
+      </c>
+      <c r="O101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>169</v>
+      </c>
+      <c r="B102" t="s">
         <v>146</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>147</v>
       </c>
-      <c r="D101" t="s">
-        <v>41</v>
-      </c>
-      <c r="E101">
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102">
         <v>1000</v>
       </c>
-      <c r="F101" t="s">
-        <v>14</v>
-      </c>
-      <c r="G101" t="s">
-        <v>14</v>
-      </c>
-      <c r="H101" t="s">
-        <v>14</v>
-      </c>
-      <c r="I101" t="s">
-        <v>12</v>
-      </c>
-      <c r="J101" t="s">
-        <v>14</v>
-      </c>
-      <c r="K101" t="s">
-        <v>14</v>
-      </c>
-      <c r="L101" t="s">
-        <v>14</v>
-      </c>
-      <c r="N101" t="s">
-        <v>42</v>
-      </c>
-      <c r="O101">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>18</v>
-      </c>
-      <c r="B102" t="s">
-        <v>77</v>
-      </c>
-      <c r="C102" t="s">
-        <v>78</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E102">
-        <v>0</v>
-      </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s">
         <v>14</v>
@@ -6008,7 +6038,7 @@
         <v>14</v>
       </c>
       <c r="I102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J102" t="s">
         <v>14</v>
@@ -6019,26 +6049,22 @@
       <c r="L102" t="s">
         <v>14</v>
       </c>
-      <c r="M102" t="s">
-        <v>17</v>
-      </c>
       <c r="N102" t="s">
         <v>42</v>
       </c>
       <c r="O102">
         <v>12</v>
       </c>
-      <c r="P102" s="8"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>18</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>184</v>
+      <c r="B103" t="s">
+        <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>41</v>
@@ -6053,10 +6079,10 @@
         <v>14</v>
       </c>
       <c r="H103" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I103" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J103" t="s">
         <v>14</v>
@@ -6068,13 +6094,13 @@
         <v>14</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N103" t="s">
         <v>42</v>
       </c>
       <c r="O103">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P103" s="8"/>
     </row>
@@ -6082,17 +6108,17 @@
       <c r="A104" t="s">
         <v>18</v>
       </c>
-      <c r="B104" t="s">
-        <v>80</v>
+      <c r="B104" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="C104" t="s">
-        <v>81</v>
-      </c>
-      <c r="D104" t="s">
+        <v>79</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E104">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
@@ -6114,6 +6140,9 @@
       </c>
       <c r="L104" t="s">
         <v>14</v>
+      </c>
+      <c r="M104" t="s">
+        <v>25</v>
       </c>
       <c r="N104" t="s">
         <v>42</v>
@@ -6128,19 +6157,19 @@
         <v>18</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="C105" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
       </c>
       <c r="E105">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G105" t="s">
         <v>14</v>
@@ -6170,31 +6199,31 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
-      </c>
-      <c r="D106" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
         <v>41</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F106" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
       </c>
       <c r="H106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J106" t="s">
         <v>14</v>
@@ -6205,25 +6234,23 @@
       <c r="L106" t="s">
         <v>14</v>
       </c>
-      <c r="M106" t="s">
-        <v>21</v>
-      </c>
       <c r="N106" t="s">
         <v>42</v>
       </c>
       <c r="O106">
-        <v>12</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P106" s="8"/>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>23</v>
       </c>
-      <c r="B107" s="9" t="s">
-        <v>184</v>
+      <c r="B107" t="s">
+        <v>82</v>
       </c>
       <c r="C107" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>41</v>
@@ -6238,10 +6265,10 @@
         <v>14</v>
       </c>
       <c r="H107" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I107" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J107" t="s">
         <v>14</v>
@@ -6253,31 +6280,30 @@
         <v>14</v>
       </c>
       <c r="M107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N107" t="s">
         <v>42</v>
       </c>
       <c r="O107">
-        <v>6</v>
-      </c>
-      <c r="P107" s="8"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>23</v>
       </c>
-      <c r="B108" t="s">
-        <v>80</v>
+      <c r="B108" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="C108" t="s">
-        <v>81</v>
-      </c>
-      <c r="D108" t="s">
+        <v>79</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E108">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
@@ -6299,6 +6325,9 @@
       </c>
       <c r="L108" t="s">
         <v>14</v>
+      </c>
+      <c r="M108" t="s">
+        <v>25</v>
       </c>
       <c r="N108" t="s">
         <v>42</v>
@@ -6306,57 +6335,102 @@
       <c r="O108">
         <v>6</v>
       </c>
+      <c r="P108" s="8"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A109" s="2" t="s">
+      <c r="A109" t="s">
         <v>23</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109">
+        <v>100</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s">
+        <v>14</v>
+      </c>
+      <c r="L109" t="s">
+        <v>14</v>
+      </c>
+      <c r="N109" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E109" s="2">
+      <c r="D110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110" s="2">
         <v>50</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O109" s="2">
+      <c r="F110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O110" s="2">
         <v>6</v>
       </c>
-      <c r="P109" s="2"/>
+      <c r="P110" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P109" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P109">
-      <sortCondition ref="A1:A109"/>
+  <autoFilter ref="A1:P110" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P110">
+      <sortCondition ref="A1:A110"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documents/ODMS DatabaseStructure.xlsx
+++ b/Documents/ODMS DatabaseStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1950" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE9ED967-44E3-4167-8C59-E088698B2B69}"/>
+  <xr:revisionPtr revIDLastSave="1994" documentId="13_ncr:1_{CC27A729-14E2-47A1-8678-68A27D4B14DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FF4B1F-3A46-4DAB-B310-F05204DEB3CF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Column" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Column!$A$1:$P$112</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="188">
   <si>
     <t>Table Name</t>
   </si>
@@ -386,15 +386,9 @@
     <t>Accomplishments</t>
   </si>
   <si>
-    <t>Accomplishments This Week</t>
-  </si>
-  <si>
     <t>NextSteps</t>
   </si>
   <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
     <t>ActualSpend</t>
   </si>
   <si>
@@ -588,6 +582,12 @@
   </si>
   <si>
     <t>MilestoneId</t>
+  </si>
+  <si>
+    <t>Accomplishment</t>
+  </si>
+  <si>
+    <t>NextStep</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1130,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -1176,7 +1176,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
@@ -1244,7 +1244,7 @@
         <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
         <v>92</v>
@@ -1281,13 +1281,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -1304,7 +1304,7 @@
         <v>96</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
         <v>96</v>
@@ -1321,16 +1321,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -1341,16 +1341,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -1361,21 +1361,61 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1386,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P110"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2200,7 +2240,7 @@
         <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>41</v>
@@ -2240,7 +2280,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>77</v>
@@ -2288,10 +2328,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>94</v>
@@ -2336,13 +2376,13 @@
     </row>
     <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>66</v>
@@ -2382,13 +2422,13 @@
     </row>
     <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>66</v>
@@ -2428,13 +2468,13 @@
     </row>
     <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>41</v>
@@ -2617,10 +2657,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>66</v>
@@ -2663,10 +2703,10 @@
         <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>66</v>
@@ -2709,10 +2749,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>68</v>
@@ -2987,7 +3027,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>104</v>
@@ -3083,7 +3123,7 @@
         <v>17</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>108</v>
@@ -3135,7 +3175,7 @@
         <v>112</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -3175,10 +3215,10 @@
         <v>17</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>57</v>
@@ -3409,10 +3449,10 @@
         <v>21</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>66</v>
@@ -3455,10 +3495,10 @@
         <v>21</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>66</v>
@@ -3501,10 +3541,10 @@
         <v>21</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>68</v>
@@ -3779,7 +3819,7 @@
         <v>21</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>104</v>
@@ -3875,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>108</v>
@@ -3927,7 +3967,7 @@
         <v>112</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E55" s="2">
         <v>0</v>
@@ -3967,10 +4007,10 @@
         <v>21</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>57</v>
@@ -4010,13 +4050,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D57" t="s">
         <v>62</v>
@@ -4054,13 +4094,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D58" t="s">
         <v>62</v>
@@ -4098,13 +4138,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D59" t="s">
         <v>66</v>
@@ -4142,13 +4182,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D60" t="s">
         <v>66</v>
@@ -4236,10 +4276,10 @@
         <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
         <v>41</v>
@@ -4280,10 +4320,10 @@
         <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D63" t="s">
         <v>41</v>
@@ -4324,10 +4364,10 @@
         <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
         <v>41</v>
@@ -4368,10 +4408,10 @@
         <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D65" t="s">
         <v>41</v>
@@ -4415,7 +4455,7 @@
         <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D66" t="s">
         <v>41</v>
@@ -4456,10 +4496,10 @@
         <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>41</v>
@@ -4503,10 +4543,10 @@
         <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D68" t="s">
         <v>66</v>
@@ -4547,10 +4587,10 @@
         <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
         <v>41</v>
@@ -4638,10 +4678,10 @@
         <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>41</v>
@@ -4671,7 +4711,7 @@
         <v>14</v>
       </c>
       <c r="M71" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N71" t="s">
         <v>42</v>
@@ -4776,7 +4816,7 @@
         <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
         <v>41</v>
@@ -4817,16 +4857,16 @@
         <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E75">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
@@ -4835,7 +4875,7 @@
         <v>14</v>
       </c>
       <c r="H75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I75" t="s">
         <v>12</v>
@@ -4853,7 +4893,7 @@
         <v>42</v>
       </c>
       <c r="O75">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
@@ -4861,16 +4901,16 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E76">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
@@ -4879,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I76" t="s">
         <v>12</v>
@@ -4897,7 +4937,7 @@
         <v>42</v>
       </c>
       <c r="O76">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -4905,16 +4945,16 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D77" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
@@ -4949,16 +4989,16 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4993,16 +5033,16 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="D79" t="s">
         <v>41</v>
       </c>
       <c r="E79">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
@@ -5037,22 +5077,22 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
-      </c>
-      <c r="D80" t="s">
+        <v>157</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -5081,16 +5121,16 @@
         <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E81">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
@@ -5125,25 +5165,25 @@
         <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D82" t="s">
         <v>41</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I82" t="s">
         <v>12</v>
@@ -5161,21 +5201,21 @@
         <v>42</v>
       </c>
       <c r="O82">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" t="s">
         <v>90</v>
       </c>
-      <c r="B83" t="s">
-        <v>156</v>
-      </c>
-      <c r="C83" t="s">
-        <v>157</v>
-      </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5187,7 +5227,7 @@
         <v>14</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I83" t="s">
         <v>12</v>
@@ -5201,37 +5241,40 @@
       <c r="L83" t="s">
         <v>14</v>
       </c>
+      <c r="M83" t="s">
+        <v>90</v>
+      </c>
       <c r="N83" t="s">
         <v>42</v>
       </c>
       <c r="O83">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="B84" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="D84" t="s">
         <v>41</v>
       </c>
       <c r="E84">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I84" t="s">
         <v>12</v>
@@ -5254,22 +5297,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="B85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C85" t="s">
-        <v>128</v>
-      </c>
-      <c r="D85" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" t="s">
         <v>41</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
@@ -5278,7 +5321,7 @@
         <v>14</v>
       </c>
       <c r="I85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J85" t="s">
         <v>14</v>
@@ -5301,25 +5344,25 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="D86" t="s">
         <v>41</v>
       </c>
       <c r="E86">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H86" t="s">
         <v>12</v>
@@ -5340,7 +5383,7 @@
         <v>42</v>
       </c>
       <c r="O86">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
@@ -5348,16 +5391,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
-      </c>
-      <c r="D87" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
@@ -5366,10 +5409,10 @@
         <v>14</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I87" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J87" t="s">
         <v>14</v>
@@ -5380,11 +5423,14 @@
       <c r="L87" t="s">
         <v>14</v>
       </c>
+      <c r="M87" t="s">
+        <v>90</v>
+      </c>
       <c r="N87" t="s">
         <v>42</v>
       </c>
       <c r="O87">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
@@ -5392,19 +5438,19 @@
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D88" t="s">
         <v>41</v>
       </c>
       <c r="E88">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
@@ -5428,24 +5474,24 @@
         <v>42</v>
       </c>
       <c r="O88">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D89" t="s">
         <v>41</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
@@ -5454,10 +5500,10 @@
         <v>14</v>
       </c>
       <c r="H89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J89" t="s">
         <v>14</v>
@@ -5468,34 +5514,31 @@
       <c r="L89" t="s">
         <v>14</v>
       </c>
-      <c r="M89" t="s">
-        <v>90</v>
-      </c>
       <c r="N89" t="s">
         <v>42</v>
       </c>
       <c r="O89">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
         <v>41</v>
       </c>
       <c r="E90">
-        <v>255</v>
+        <v>500</v>
       </c>
       <c r="F90" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -5524,16 +5567,16 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
-      </c>
-      <c r="D91" t="s">
-        <v>66</v>
+        <v>126</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5545,10 +5588,10 @@
         <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I91" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J91" t="s">
         <v>14</v>
@@ -5559,28 +5602,31 @@
       <c r="L91" t="s">
         <v>14</v>
       </c>
+      <c r="M91" t="s">
+        <v>90</v>
+      </c>
       <c r="N91" t="s">
         <v>42</v>
       </c>
       <c r="O91">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B92" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
@@ -5607,24 +5653,24 @@
         <v>42</v>
       </c>
       <c r="O92">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E93">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
@@ -5656,16 +5702,16 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>41</v>
+        <v>131</v>
+      </c>
+      <c r="D94" t="s">
+        <v>66</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5677,10 +5723,10 @@
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J94" t="s">
         <v>14</v>
@@ -5691,31 +5737,28 @@
       <c r="L94" t="s">
         <v>14</v>
       </c>
-      <c r="M94" t="s">
-        <v>90</v>
-      </c>
       <c r="N94" t="s">
         <v>42</v>
       </c>
       <c r="O94">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
         <v>41</v>
       </c>
       <c r="E95">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -5747,19 +5790,19 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B96" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
-      </c>
-      <c r="D96" t="s">
+        <v>126</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
@@ -5768,10 +5811,10 @@
         <v>14</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I96" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J96" t="s">
         <v>14</v>
@@ -5782,28 +5825,31 @@
       <c r="L96" t="s">
         <v>14</v>
       </c>
+      <c r="M96" t="s">
+        <v>90</v>
+      </c>
       <c r="N96" t="s">
         <v>42</v>
       </c>
       <c r="O96">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>41</v>
       </c>
       <c r="E97">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F97" t="s">
         <v>12</v>
@@ -5830,18 +5876,18 @@
         <v>42</v>
       </c>
       <c r="O97">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B98" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C98" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
         <v>41</v>
@@ -5879,19 +5925,19 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="C99" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D99" t="s">
         <v>41</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -5918,24 +5964,24 @@
         <v>42</v>
       </c>
       <c r="O99">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C100" t="s">
-        <v>149</v>
-      </c>
-      <c r="D100" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D100" t="s">
         <v>41</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
@@ -5957,9 +6003,6 @@
       </c>
       <c r="L100" t="s">
         <v>14</v>
-      </c>
-      <c r="M100" t="s">
-        <v>25</v>
       </c>
       <c r="N100" t="s">
         <v>42</v>
@@ -5970,19 +6013,19 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B101" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
@@ -6014,7 +6057,7 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B102" t="s">
         <v>146</v>
@@ -6022,20 +6065,20 @@
       <c r="C102" t="s">
         <v>147</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E102">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G102" t="s">
         <v>14</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I102" t="s">
         <v>12</v>
@@ -6049,25 +6092,28 @@
       <c r="L102" t="s">
         <v>14</v>
       </c>
+      <c r="M102" t="s">
+        <v>25</v>
+      </c>
       <c r="N102" t="s">
         <v>42</v>
       </c>
       <c r="O102">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="B103" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="C103" t="s">
-        <v>78</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>41</v>
+        <v>143</v>
+      </c>
+      <c r="D103" t="s">
+        <v>66</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6079,10 +6125,10 @@
         <v>14</v>
       </c>
       <c r="H103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J103" t="s">
         <v>14</v>
@@ -6093,41 +6139,37 @@
       <c r="L103" t="s">
         <v>14</v>
       </c>
-      <c r="M103" t="s">
-        <v>17</v>
-      </c>
       <c r="N103" t="s">
         <v>42</v>
       </c>
       <c r="O103">
-        <v>12</v>
-      </c>
-      <c r="P103" s="8"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>18</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>184</v>
+        <v>167</v>
+      </c>
+      <c r="B104" t="s">
+        <v>144</v>
       </c>
       <c r="C104" t="s">
-        <v>79</v>
-      </c>
-      <c r="D104" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D104" t="s">
         <v>41</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s">
         <v>14</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I104" t="s">
         <v>12</v>
@@ -6141,32 +6183,28 @@
       <c r="L104" t="s">
         <v>14</v>
       </c>
-      <c r="M104" t="s">
-        <v>25</v>
-      </c>
       <c r="N104" t="s">
         <v>42</v>
       </c>
       <c r="O104">
-        <v>6</v>
-      </c>
-      <c r="P104" s="8"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>18</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C105" t="s">
-        <v>81</v>
-      </c>
-      <c r="D105" t="s">
+        <v>78</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E105">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
@@ -6175,10 +6213,10 @@
         <v>14</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I105" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J105" t="s">
         <v>14</v>
@@ -6189,11 +6227,14 @@
       <c r="L105" t="s">
         <v>14</v>
       </c>
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
       <c r="N105" t="s">
         <v>42</v>
       </c>
       <c r="O105">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P105" s="8"/>
     </row>
@@ -6201,20 +6242,20 @@
       <c r="A106" t="s">
         <v>18</v>
       </c>
-      <c r="B106" t="s">
-        <v>113</v>
+      <c r="B106" s="9" t="s">
+        <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
+        <v>79</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E106">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
@@ -6233,6 +6274,9 @@
       </c>
       <c r="L106" t="s">
         <v>14</v>
+      </c>
+      <c r="M106" t="s">
+        <v>25</v>
       </c>
       <c r="N106" t="s">
         <v>42</v>
@@ -6244,19 +6288,19 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B107" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
-      </c>
-      <c r="D107" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D107" t="s">
         <v>41</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
@@ -6265,10 +6309,10 @@
         <v>14</v>
       </c>
       <c r="H107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J107" t="s">
         <v>14</v>
@@ -6279,34 +6323,32 @@
       <c r="L107" t="s">
         <v>14</v>
       </c>
-      <c r="M107" t="s">
-        <v>21</v>
-      </c>
       <c r="N107" t="s">
         <v>42</v>
       </c>
       <c r="O107">
-        <v>12</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P107" s="8"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>23</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>184</v>
+        <v>18</v>
+      </c>
+      <c r="B108" t="s">
+        <v>113</v>
       </c>
       <c r="C108" t="s">
-        <v>79</v>
-      </c>
-      <c r="D108" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" t="s">
         <v>41</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F108" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
@@ -6325,9 +6367,6 @@
       </c>
       <c r="L108" t="s">
         <v>14</v>
-      </c>
-      <c r="M108" t="s">
-        <v>25</v>
       </c>
       <c r="N108" t="s">
         <v>42</v>
@@ -6342,95 +6381,190 @@
         <v>23</v>
       </c>
       <c r="B109" t="s">
+        <v>82</v>
+      </c>
+      <c r="C109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s">
+        <v>14</v>
+      </c>
+      <c r="I109" t="s">
+        <v>14</v>
+      </c>
+      <c r="J109" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s">
+        <v>14</v>
+      </c>
+      <c r="L109" t="s">
+        <v>14</v>
+      </c>
+      <c r="M109" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C110" t="s">
+        <v>79</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" t="s">
+        <v>12</v>
+      </c>
+      <c r="J110" t="s">
+        <v>14</v>
+      </c>
+      <c r="K110" t="s">
+        <v>14</v>
+      </c>
+      <c r="L110" t="s">
+        <v>14</v>
+      </c>
+      <c r="M110" t="s">
+        <v>25</v>
+      </c>
+      <c r="N110" t="s">
+        <v>42</v>
+      </c>
+      <c r="O110">
+        <v>6</v>
+      </c>
+      <c r="P110" s="8"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111" t="s">
         <v>80</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C111" t="s">
         <v>81</v>
       </c>
-      <c r="D109" t="s">
-        <v>41</v>
-      </c>
-      <c r="E109">
+      <c r="D111" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111">
         <v>100</v>
       </c>
-      <c r="F109" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" t="s">
-        <v>12</v>
-      </c>
-      <c r="J109" t="s">
-        <v>14</v>
-      </c>
-      <c r="K109" t="s">
-        <v>14</v>
-      </c>
-      <c r="L109" t="s">
-        <v>14</v>
-      </c>
-      <c r="N109" t="s">
-        <v>42</v>
-      </c>
-      <c r="O109">
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" t="s">
+        <v>12</v>
+      </c>
+      <c r="J111" t="s">
+        <v>14</v>
+      </c>
+      <c r="K111" t="s">
+        <v>14</v>
+      </c>
+      <c r="L111" t="s">
+        <v>14</v>
+      </c>
+      <c r="N111" t="s">
+        <v>42</v>
+      </c>
+      <c r="O111">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E110" s="2">
+      <c r="D112" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112" s="2">
         <v>50</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O110" s="2">
+      <c r="F112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O112" s="2">
         <v>6</v>
       </c>
-      <c r="P110" s="2"/>
+      <c r="P112" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P110" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P110">
-      <sortCondition ref="A1:A110"/>
+  <autoFilter ref="A1:P112" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P112">
+      <sortCondition ref="A1:A112"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
